--- a/Excel/Allplanttaglist.xlsx
+++ b/Excel/Allplanttaglist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RS Consultancy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel-Files\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01841C5E-D123-4758-B05C-62FBC79D2921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA3BC78-0B4B-441F-89DD-B1D9A90043B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{0DFC0680-056B-49A9-993E-B17935078FFA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12170" uniqueCount="4169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12175" uniqueCount="4174">
   <si>
     <t>omkamal</t>
   </si>
@@ -12541,6 +12541,21 @@
   </si>
   <si>
     <t>ACDB2_CB_STAT</t>
+  </si>
+  <si>
+    <t>INV1_PR</t>
+  </si>
+  <si>
+    <t>INV2_PR</t>
+  </si>
+  <si>
+    <t>INV3_PR</t>
+  </si>
+  <si>
+    <t>INV4_PR</t>
+  </si>
+  <si>
+    <t>INV5_PR</t>
   </si>
 </sst>
 </file>
@@ -41191,6 +41206,9 @@
       <c r="Q565" t="s">
         <v>3885</v>
       </c>
+      <c r="S565" t="s">
+        <v>4169</v>
+      </c>
     </row>
     <row r="566" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C566" t="s">
@@ -41223,6 +41241,9 @@
       <c r="Q566" t="s">
         <v>3886</v>
       </c>
+      <c r="S566" t="s">
+        <v>4170</v>
+      </c>
     </row>
     <row r="567" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C567" t="s">
@@ -41255,6 +41276,9 @@
       <c r="Q567" t="s">
         <v>3887</v>
       </c>
+      <c r="S567" t="s">
+        <v>4171</v>
+      </c>
     </row>
     <row r="568" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C568" t="s">
@@ -41287,6 +41311,9 @@
       <c r="Q568" t="s">
         <v>3888</v>
       </c>
+      <c r="S568" t="s">
+        <v>4172</v>
+      </c>
     </row>
     <row r="569" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C569" t="s">
@@ -41318,6 +41345,9 @@
       </c>
       <c r="Q569" t="s">
         <v>3889</v>
+      </c>
+      <c r="S569" t="s">
+        <v>4173</v>
       </c>
     </row>
     <row r="570" spans="3:19" x14ac:dyDescent="0.25">

--- a/Excel/Allplanttaglist.xlsx
+++ b/Excel/Allplanttaglist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel-Files\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7249E0-AF0C-441A-842A-DC635A73A144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D08D582-07FF-409E-9471-588AFD781940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{0DFC0680-056B-49A9-993E-B17935078FFA}"/>
   </bookViews>
@@ -12558,9 +12558,6 @@
     <t>INV5_PR</t>
   </si>
   <si>
-    <t>csvpl</t>
-  </si>
-  <si>
     <t>ACDB2_LL_AVG_KV</t>
   </si>
   <si>
@@ -13858,6 +13855,9 @@
   </si>
   <si>
     <t>ACDB2_CB</t>
+  </si>
+  <si>
+    <t>acvpl</t>
   </si>
 </sst>
 </file>
@@ -14292,7 +14292,7 @@
         <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>4174</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -17206,7 +17206,7 @@
         <v>2239</v>
       </c>
       <c r="T48" t="s">
-        <v>4175</v>
+        <v>4174</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -27947,7 +27947,7 @@
         <v>1086</v>
       </c>
       <c r="T227" t="s">
-        <v>4176</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="228" spans="1:20" x14ac:dyDescent="0.25">
@@ -28003,7 +28003,7 @@
         <v>1087</v>
       </c>
       <c r="T228" t="s">
-        <v>4177</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="229" spans="1:20" x14ac:dyDescent="0.25">
@@ -28059,7 +28059,7 @@
         <v>1088</v>
       </c>
       <c r="T229" t="s">
-        <v>4178</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="230" spans="1:20" x14ac:dyDescent="0.25">
@@ -28115,7 +28115,7 @@
         <v>1089</v>
       </c>
       <c r="T230" t="s">
-        <v>4179</v>
+        <v>4178</v>
       </c>
     </row>
     <row r="231" spans="1:20" x14ac:dyDescent="0.25">
@@ -28171,7 +28171,7 @@
         <v>1090</v>
       </c>
       <c r="T231" t="s">
-        <v>4180</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="232" spans="1:20" x14ac:dyDescent="0.25">
@@ -28227,7 +28227,7 @@
         <v>1091</v>
       </c>
       <c r="T232" t="s">
-        <v>4181</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="233" spans="1:20" x14ac:dyDescent="0.25">
@@ -28283,7 +28283,7 @@
         <v>1092</v>
       </c>
       <c r="T233" t="s">
-        <v>4182</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="234" spans="1:20" x14ac:dyDescent="0.25">
@@ -28339,7 +28339,7 @@
         <v>1093</v>
       </c>
       <c r="T234" t="s">
-        <v>4183</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="235" spans="1:20" x14ac:dyDescent="0.25">
@@ -28395,7 +28395,7 @@
         <v>1094</v>
       </c>
       <c r="T235" t="s">
-        <v>4184</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="236" spans="1:20" x14ac:dyDescent="0.25">
@@ -28451,7 +28451,7 @@
         <v>1095</v>
       </c>
       <c r="T236" t="s">
-        <v>4185</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="237" spans="1:20" x14ac:dyDescent="0.25">
@@ -28507,7 +28507,7 @@
         <v>1097</v>
       </c>
       <c r="T237" t="s">
-        <v>4186</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="238" spans="1:20" x14ac:dyDescent="0.25">
@@ -28563,7 +28563,7 @@
         <v>1098</v>
       </c>
       <c r="T238" t="s">
-        <v>4187</v>
+        <v>4186</v>
       </c>
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.25">
@@ -28619,7 +28619,7 @@
         <v>1099</v>
       </c>
       <c r="T239" t="s">
-        <v>4188</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="240" spans="1:20" x14ac:dyDescent="0.25">
@@ -28675,7 +28675,7 @@
         <v>1100</v>
       </c>
       <c r="T240" t="s">
-        <v>4189</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="241" spans="1:20" x14ac:dyDescent="0.25">
@@ -28731,7 +28731,7 @@
         <v>1101</v>
       </c>
       <c r="T241" t="s">
-        <v>4190</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="242" spans="1:20" x14ac:dyDescent="0.25">
@@ -28787,7 +28787,7 @@
         <v>1102</v>
       </c>
       <c r="T242" t="s">
-        <v>4191</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="243" spans="1:20" x14ac:dyDescent="0.25">
@@ -28843,7 +28843,7 @@
         <v>1103</v>
       </c>
       <c r="T243" t="s">
-        <v>4192</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.25">
@@ -28899,7 +28899,7 @@
         <v>1104</v>
       </c>
       <c r="T244" t="s">
-        <v>4193</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="245" spans="1:20" x14ac:dyDescent="0.25">
@@ -28955,7 +28955,7 @@
         <v>1105</v>
       </c>
       <c r="T245" t="s">
-        <v>4194</v>
+        <v>4193</v>
       </c>
     </row>
     <row r="246" spans="1:20" x14ac:dyDescent="0.25">
@@ -29011,7 +29011,7 @@
         <v>1106</v>
       </c>
       <c r="T246" t="s">
-        <v>4195</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="247" spans="1:20" x14ac:dyDescent="0.25">
@@ -29067,7 +29067,7 @@
         <v>1107</v>
       </c>
       <c r="T247" t="s">
-        <v>4196</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="248" spans="1:20" x14ac:dyDescent="0.25">
@@ -29123,7 +29123,7 @@
         <v>1108</v>
       </c>
       <c r="T248" t="s">
-        <v>4197</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="249" spans="1:20" x14ac:dyDescent="0.25">
@@ -29179,7 +29179,7 @@
         <v>1109</v>
       </c>
       <c r="T249" t="s">
-        <v>4198</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="250" spans="1:20" x14ac:dyDescent="0.25">
@@ -29235,7 +29235,7 @@
         <v>1110</v>
       </c>
       <c r="T250" t="s">
-        <v>4199</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="251" spans="1:20" x14ac:dyDescent="0.25">
@@ -29291,7 +29291,7 @@
         <v>1111</v>
       </c>
       <c r="T251" t="s">
-        <v>4200</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="252" spans="1:20" x14ac:dyDescent="0.25">
@@ -29347,7 +29347,7 @@
         <v>1112</v>
       </c>
       <c r="T252" t="s">
-        <v>4201</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="253" spans="1:20" x14ac:dyDescent="0.25">
@@ -29403,7 +29403,7 @@
         <v>1113</v>
       </c>
       <c r="T253" t="s">
-        <v>4202</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="254" spans="1:20" x14ac:dyDescent="0.25">
@@ -29459,7 +29459,7 @@
         <v>1114</v>
       </c>
       <c r="T254" t="s">
-        <v>4203</v>
+        <v>4202</v>
       </c>
     </row>
     <row r="255" spans="1:20" x14ac:dyDescent="0.25">
@@ -29515,7 +29515,7 @@
         <v>1115</v>
       </c>
       <c r="T255" t="s">
-        <v>4204</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="256" spans="1:20" x14ac:dyDescent="0.25">
@@ -29571,7 +29571,7 @@
         <v>1116</v>
       </c>
       <c r="T256" t="s">
-        <v>4205</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="257" spans="1:20" x14ac:dyDescent="0.25">
@@ -29627,7 +29627,7 @@
         <v>1117</v>
       </c>
       <c r="T257" t="s">
-        <v>4206</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="258" spans="1:20" x14ac:dyDescent="0.25">
@@ -29683,7 +29683,7 @@
         <v>1118</v>
       </c>
       <c r="T258" t="s">
-        <v>4207</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="259" spans="1:20" x14ac:dyDescent="0.25">
@@ -29739,7 +29739,7 @@
         <v>1119</v>
       </c>
       <c r="T259" t="s">
-        <v>4208</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="260" spans="1:20" x14ac:dyDescent="0.25">
@@ -29795,7 +29795,7 @@
         <v>1120</v>
       </c>
       <c r="T260" t="s">
-        <v>4209</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="261" spans="1:20" x14ac:dyDescent="0.25">
@@ -29851,7 +29851,7 @@
         <v>1121</v>
       </c>
       <c r="T261" t="s">
-        <v>4210</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="262" spans="1:20" x14ac:dyDescent="0.25">
@@ -29907,7 +29907,7 @@
         <v>1122</v>
       </c>
       <c r="T262" t="s">
-        <v>4211</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="263" spans="1:20" x14ac:dyDescent="0.25">
@@ -29963,7 +29963,7 @@
         <v>1123</v>
       </c>
       <c r="T263" t="s">
-        <v>4212</v>
+        <v>4211</v>
       </c>
     </row>
     <row r="264" spans="1:20" x14ac:dyDescent="0.25">
@@ -30019,7 +30019,7 @@
         <v>1124</v>
       </c>
       <c r="T264" t="s">
-        <v>4213</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="265" spans="1:20" x14ac:dyDescent="0.25">
@@ -30075,7 +30075,7 @@
         <v>1125</v>
       </c>
       <c r="T265" t="s">
-        <v>4214</v>
+        <v>4213</v>
       </c>
     </row>
     <row r="266" spans="1:20" x14ac:dyDescent="0.25">
@@ -30131,7 +30131,7 @@
         <v>1126</v>
       </c>
       <c r="T266" t="s">
-        <v>4215</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="267" spans="1:20" x14ac:dyDescent="0.25">
@@ -30187,7 +30187,7 @@
         <v>1127</v>
       </c>
       <c r="T267" t="s">
-        <v>4216</v>
+        <v>4215</v>
       </c>
     </row>
     <row r="268" spans="1:20" x14ac:dyDescent="0.25">
@@ -30243,7 +30243,7 @@
         <v>1128</v>
       </c>
       <c r="T268" t="s">
-        <v>4217</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="269" spans="1:20" x14ac:dyDescent="0.25">
@@ -30299,7 +30299,7 @@
         <v>1129</v>
       </c>
       <c r="T269" t="s">
-        <v>4218</v>
+        <v>4217</v>
       </c>
     </row>
     <row r="270" spans="1:20" x14ac:dyDescent="0.25">
@@ -30355,7 +30355,7 @@
         <v>1130</v>
       </c>
       <c r="T270" t="s">
-        <v>4219</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="271" spans="1:20" x14ac:dyDescent="0.25">
@@ -30411,7 +30411,7 @@
         <v>1131</v>
       </c>
       <c r="T271" t="s">
-        <v>4220</v>
+        <v>4219</v>
       </c>
     </row>
     <row r="272" spans="1:20" x14ac:dyDescent="0.25">
@@ -30467,7 +30467,7 @@
         <v>1132</v>
       </c>
       <c r="T272" t="s">
-        <v>4221</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="273" spans="1:20" x14ac:dyDescent="0.25">
@@ -30523,7 +30523,7 @@
         <v>1133</v>
       </c>
       <c r="T273" t="s">
-        <v>4222</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="274" spans="1:20" x14ac:dyDescent="0.25">
@@ -30579,7 +30579,7 @@
         <v>1134</v>
       </c>
       <c r="T274" t="s">
-        <v>4223</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="275" spans="1:20" x14ac:dyDescent="0.25">
@@ -30635,7 +30635,7 @@
         <v>1135</v>
       </c>
       <c r="T275" t="s">
-        <v>4224</v>
+        <v>4223</v>
       </c>
     </row>
     <row r="276" spans="1:20" x14ac:dyDescent="0.25">
@@ -30691,7 +30691,7 @@
         <v>1136</v>
       </c>
       <c r="T276" t="s">
-        <v>4225</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="277" spans="1:20" x14ac:dyDescent="0.25">
@@ -30747,7 +30747,7 @@
         <v>1137</v>
       </c>
       <c r="T277" t="s">
-        <v>4226</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="278" spans="1:20" x14ac:dyDescent="0.25">
@@ -30803,7 +30803,7 @@
         <v>1138</v>
       </c>
       <c r="T278" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="279" spans="1:20" x14ac:dyDescent="0.25">
@@ -30859,7 +30859,7 @@
         <v>1139</v>
       </c>
       <c r="T279" t="s">
-        <v>4228</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="280" spans="1:20" x14ac:dyDescent="0.25">
@@ -30915,7 +30915,7 @@
         <v>1140</v>
       </c>
       <c r="T280" t="s">
-        <v>4229</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="281" spans="1:20" x14ac:dyDescent="0.25">
@@ -30971,7 +30971,7 @@
         <v>1141</v>
       </c>
       <c r="T281" t="s">
-        <v>4230</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="282" spans="1:20" x14ac:dyDescent="0.25">
@@ -31027,7 +31027,7 @@
         <v>1142</v>
       </c>
       <c r="T282" t="s">
-        <v>4231</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="283" spans="1:20" x14ac:dyDescent="0.25">
@@ -31083,7 +31083,7 @@
         <v>1143</v>
       </c>
       <c r="T283" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="284" spans="1:20" x14ac:dyDescent="0.25">
@@ -31136,7 +31136,7 @@
         <v>1144</v>
       </c>
       <c r="T284" t="s">
-        <v>4233</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="285" spans="1:20" x14ac:dyDescent="0.25">
@@ -31189,7 +31189,7 @@
         <v>1145</v>
       </c>
       <c r="T285" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="286" spans="1:20" x14ac:dyDescent="0.25">
@@ -31242,7 +31242,7 @@
         <v>1146</v>
       </c>
       <c r="T286" t="s">
-        <v>4235</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="287" spans="1:20" x14ac:dyDescent="0.25">
@@ -31295,7 +31295,7 @@
         <v>1147</v>
       </c>
       <c r="T287" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="288" spans="1:20" x14ac:dyDescent="0.25">
@@ -31348,7 +31348,7 @@
         <v>1148</v>
       </c>
       <c r="T288" t="s">
-        <v>4237</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="289" spans="1:20" x14ac:dyDescent="0.25">
@@ -31401,7 +31401,7 @@
         <v>1149</v>
       </c>
       <c r="T289" t="s">
-        <v>4238</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="290" spans="1:20" x14ac:dyDescent="0.25">
@@ -31454,7 +31454,7 @@
         <v>1150</v>
       </c>
       <c r="T290" t="s">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="291" spans="1:20" x14ac:dyDescent="0.25">
@@ -31507,7 +31507,7 @@
         <v>1151</v>
       </c>
       <c r="T291" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="292" spans="1:20" x14ac:dyDescent="0.25">
@@ -31560,7 +31560,7 @@
         <v>1152</v>
       </c>
       <c r="T292" t="s">
-        <v>4241</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="293" spans="1:20" x14ac:dyDescent="0.25">
@@ -31613,7 +31613,7 @@
         <v>1153</v>
       </c>
       <c r="T293" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="294" spans="1:20" x14ac:dyDescent="0.25">
@@ -31666,7 +31666,7 @@
         <v>1154</v>
       </c>
       <c r="T294" t="s">
-        <v>4243</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="295" spans="1:20" x14ac:dyDescent="0.25">
@@ -31719,7 +31719,7 @@
         <v>1155</v>
       </c>
       <c r="T295" t="s">
-        <v>4244</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="296" spans="1:20" x14ac:dyDescent="0.25">
@@ -31772,7 +31772,7 @@
         <v>1156</v>
       </c>
       <c r="T296" t="s">
-        <v>4245</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="297" spans="1:20" x14ac:dyDescent="0.25">
@@ -31825,7 +31825,7 @@
         <v>1157</v>
       </c>
       <c r="T297" t="s">
-        <v>4246</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="298" spans="1:20" x14ac:dyDescent="0.25">
@@ -31878,7 +31878,7 @@
         <v>1158</v>
       </c>
       <c r="T298" t="s">
-        <v>4247</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="299" spans="1:20" x14ac:dyDescent="0.25">
@@ -31931,7 +31931,7 @@
         <v>1159</v>
       </c>
       <c r="T299" t="s">
-        <v>4248</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="300" spans="1:20" x14ac:dyDescent="0.25">
@@ -31984,7 +31984,7 @@
         <v>1160</v>
       </c>
       <c r="T300" t="s">
-        <v>4249</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="301" spans="1:20" x14ac:dyDescent="0.25">
@@ -32037,7 +32037,7 @@
         <v>1161</v>
       </c>
       <c r="T301" t="s">
-        <v>4250</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="302" spans="1:20" x14ac:dyDescent="0.25">
@@ -32090,7 +32090,7 @@
         <v>1162</v>
       </c>
       <c r="T302" t="s">
-        <v>4251</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="303" spans="1:20" x14ac:dyDescent="0.25">
@@ -32143,7 +32143,7 @@
         <v>1163</v>
       </c>
       <c r="T303" t="s">
-        <v>4252</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="304" spans="1:20" x14ac:dyDescent="0.25">
@@ -32196,7 +32196,7 @@
         <v>1164</v>
       </c>
       <c r="T304" t="s">
-        <v>4253</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="305" spans="1:20" x14ac:dyDescent="0.25">
@@ -32249,7 +32249,7 @@
         <v>1165</v>
       </c>
       <c r="T305" t="s">
-        <v>4254</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="306" spans="1:20" x14ac:dyDescent="0.25">
@@ -32302,7 +32302,7 @@
         <v>1166</v>
       </c>
       <c r="T306" t="s">
-        <v>4255</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="307" spans="1:20" x14ac:dyDescent="0.25">
@@ -32355,7 +32355,7 @@
         <v>1167</v>
       </c>
       <c r="T307" t="s">
-        <v>4256</v>
+        <v>4255</v>
       </c>
     </row>
     <row r="308" spans="1:20" x14ac:dyDescent="0.25">
@@ -32408,7 +32408,7 @@
         <v>1168</v>
       </c>
       <c r="T308" t="s">
-        <v>4257</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="309" spans="1:20" x14ac:dyDescent="0.25">
@@ -32461,7 +32461,7 @@
         <v>1169</v>
       </c>
       <c r="T309" t="s">
-        <v>4258</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="310" spans="1:20" x14ac:dyDescent="0.25">
@@ -32514,7 +32514,7 @@
         <v>1170</v>
       </c>
       <c r="T310" t="s">
-        <v>4259</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="311" spans="1:20" x14ac:dyDescent="0.25">
@@ -32567,7 +32567,7 @@
         <v>1171</v>
       </c>
       <c r="T311" t="s">
-        <v>4260</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="312" spans="1:20" x14ac:dyDescent="0.25">
@@ -32620,7 +32620,7 @@
         <v>1172</v>
       </c>
       <c r="T312" t="s">
-        <v>4261</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="313" spans="1:20" x14ac:dyDescent="0.25">
@@ -32673,7 +32673,7 @@
         <v>1173</v>
       </c>
       <c r="T313" t="s">
-        <v>4262</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="314" spans="1:20" x14ac:dyDescent="0.25">
@@ -32726,7 +32726,7 @@
         <v>1174</v>
       </c>
       <c r="T314" t="s">
-        <v>4263</v>
+        <v>4262</v>
       </c>
     </row>
     <row r="315" spans="1:20" x14ac:dyDescent="0.25">
@@ -32779,7 +32779,7 @@
         <v>1175</v>
       </c>
       <c r="T315" t="s">
-        <v>4264</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="316" spans="1:20" x14ac:dyDescent="0.25">
@@ -32832,7 +32832,7 @@
         <v>1176</v>
       </c>
       <c r="T316" t="s">
-        <v>4265</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="317" spans="1:20" x14ac:dyDescent="0.25">
@@ -32885,7 +32885,7 @@
         <v>1177</v>
       </c>
       <c r="T317" t="s">
-        <v>4266</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="318" spans="1:20" x14ac:dyDescent="0.25">
@@ -32938,7 +32938,7 @@
         <v>1178</v>
       </c>
       <c r="T318" t="s">
-        <v>4267</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="319" spans="1:20" x14ac:dyDescent="0.25">
@@ -32991,7 +32991,7 @@
         <v>1179</v>
       </c>
       <c r="T319" t="s">
-        <v>4268</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="320" spans="1:20" x14ac:dyDescent="0.25">
@@ -33044,7 +33044,7 @@
         <v>1180</v>
       </c>
       <c r="T320" t="s">
-        <v>4269</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="321" spans="1:20" x14ac:dyDescent="0.25">
@@ -33097,7 +33097,7 @@
         <v>1181</v>
       </c>
       <c r="T321" t="s">
-        <v>4270</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="322" spans="1:20" x14ac:dyDescent="0.25">
@@ -33150,7 +33150,7 @@
         <v>500</v>
       </c>
       <c r="T322" t="s">
-        <v>4271</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="323" spans="1:20" x14ac:dyDescent="0.25">
@@ -33203,7 +33203,7 @@
         <v>1182</v>
       </c>
       <c r="T323" t="s">
-        <v>4272</v>
+        <v>4271</v>
       </c>
     </row>
     <row r="324" spans="1:20" x14ac:dyDescent="0.25">
@@ -33256,7 +33256,7 @@
         <v>1183</v>
       </c>
       <c r="T324" t="s">
-        <v>4273</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="325" spans="1:20" x14ac:dyDescent="0.25">
@@ -33309,7 +33309,7 @@
         <v>1184</v>
       </c>
       <c r="T325" t="s">
-        <v>4274</v>
+        <v>4273</v>
       </c>
     </row>
     <row r="326" spans="1:20" x14ac:dyDescent="0.25">
@@ -33362,7 +33362,7 @@
         <v>1185</v>
       </c>
       <c r="T326" t="s">
-        <v>4275</v>
+        <v>4274</v>
       </c>
     </row>
     <row r="327" spans="1:20" x14ac:dyDescent="0.25">
@@ -33415,7 +33415,7 @@
         <v>1186</v>
       </c>
       <c r="T327" t="s">
-        <v>4276</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="328" spans="1:20" x14ac:dyDescent="0.25">
@@ -33468,7 +33468,7 @@
         <v>1187</v>
       </c>
       <c r="T328" t="s">
-        <v>4277</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="329" spans="1:20" x14ac:dyDescent="0.25">
@@ -33521,7 +33521,7 @@
         <v>1188</v>
       </c>
       <c r="T329" t="s">
-        <v>4278</v>
+        <v>4277</v>
       </c>
     </row>
     <row r="330" spans="1:20" x14ac:dyDescent="0.25">
@@ -33574,7 +33574,7 @@
         <v>1189</v>
       </c>
       <c r="T330" t="s">
-        <v>4279</v>
+        <v>4278</v>
       </c>
     </row>
     <row r="331" spans="1:20" x14ac:dyDescent="0.25">
@@ -33627,7 +33627,7 @@
         <v>1190</v>
       </c>
       <c r="T331" t="s">
-        <v>4280</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="332" spans="1:20" x14ac:dyDescent="0.25">
@@ -33680,7 +33680,7 @@
         <v>1191</v>
       </c>
       <c r="T332" t="s">
-        <v>4281</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="333" spans="1:20" x14ac:dyDescent="0.25">
@@ -33730,7 +33730,7 @@
         <v>1192</v>
       </c>
       <c r="T333" t="s">
-        <v>4282</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="334" spans="1:20" x14ac:dyDescent="0.25">
@@ -33780,7 +33780,7 @@
         <v>1193</v>
       </c>
       <c r="T334" t="s">
-        <v>4283</v>
+        <v>4282</v>
       </c>
     </row>
     <row r="335" spans="1:20" x14ac:dyDescent="0.25">
@@ -33830,7 +33830,7 @@
         <v>1194</v>
       </c>
       <c r="T335" t="s">
-        <v>4284</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="336" spans="1:20" x14ac:dyDescent="0.25">
@@ -33880,7 +33880,7 @@
         <v>1195</v>
       </c>
       <c r="T336" t="s">
-        <v>4285</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="337" spans="3:20" x14ac:dyDescent="0.25">
@@ -33930,7 +33930,7 @@
         <v>1196</v>
       </c>
       <c r="T337" t="s">
-        <v>4286</v>
+        <v>4285</v>
       </c>
     </row>
     <row r="338" spans="3:20" x14ac:dyDescent="0.25">
@@ -33980,7 +33980,7 @@
         <v>1197</v>
       </c>
       <c r="T338" t="s">
-        <v>4287</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="339" spans="3:20" x14ac:dyDescent="0.25">
@@ -34030,7 +34030,7 @@
         <v>1198</v>
       </c>
       <c r="T339" t="s">
-        <v>4288</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="340" spans="3:20" x14ac:dyDescent="0.25">
@@ -34080,7 +34080,7 @@
         <v>1199</v>
       </c>
       <c r="T340" t="s">
-        <v>4289</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="341" spans="3:20" x14ac:dyDescent="0.25">
@@ -34130,7 +34130,7 @@
         <v>1200</v>
       </c>
       <c r="T341" t="s">
-        <v>4290</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="342" spans="3:20" x14ac:dyDescent="0.25">
@@ -34180,7 +34180,7 @@
         <v>1201</v>
       </c>
       <c r="T342" t="s">
-        <v>4291</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="343" spans="3:20" x14ac:dyDescent="0.25">
@@ -34230,7 +34230,7 @@
         <v>1202</v>
       </c>
       <c r="T343" t="s">
-        <v>4292</v>
+        <v>4291</v>
       </c>
     </row>
     <row r="344" spans="3:20" x14ac:dyDescent="0.25">
@@ -34280,7 +34280,7 @@
         <v>1203</v>
       </c>
       <c r="T344" t="s">
-        <v>4293</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="345" spans="3:20" x14ac:dyDescent="0.25">
@@ -34330,7 +34330,7 @@
         <v>1204</v>
       </c>
       <c r="T345" t="s">
-        <v>4294</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="346" spans="3:20" x14ac:dyDescent="0.25">
@@ -34380,7 +34380,7 @@
         <v>1205</v>
       </c>
       <c r="T346" t="s">
-        <v>4295</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="347" spans="3:20" x14ac:dyDescent="0.25">
@@ -34430,7 +34430,7 @@
         <v>1206</v>
       </c>
       <c r="T347" t="s">
-        <v>4296</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="348" spans="3:20" x14ac:dyDescent="0.25">
@@ -34480,7 +34480,7 @@
         <v>1207</v>
       </c>
       <c r="T348" t="s">
-        <v>4297</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="349" spans="3:20" x14ac:dyDescent="0.25">
@@ -34530,7 +34530,7 @@
         <v>1208</v>
       </c>
       <c r="T349" t="s">
-        <v>4298</v>
+        <v>4297</v>
       </c>
     </row>
     <row r="350" spans="3:20" x14ac:dyDescent="0.25">
@@ -34580,7 +34580,7 @@
         <v>1209</v>
       </c>
       <c r="T350" t="s">
-        <v>4299</v>
+        <v>4298</v>
       </c>
     </row>
     <row r="351" spans="3:20" x14ac:dyDescent="0.25">
@@ -34630,7 +34630,7 @@
         <v>1210</v>
       </c>
       <c r="T351" t="s">
-        <v>4300</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="352" spans="3:20" x14ac:dyDescent="0.25">
@@ -34680,7 +34680,7 @@
         <v>1211</v>
       </c>
       <c r="T352" t="s">
-        <v>4301</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="353" spans="3:20" x14ac:dyDescent="0.25">
@@ -34730,7 +34730,7 @@
         <v>1212</v>
       </c>
       <c r="T353" t="s">
-        <v>4302</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="354" spans="3:20" x14ac:dyDescent="0.25">
@@ -34780,7 +34780,7 @@
         <v>1213</v>
       </c>
       <c r="T354" t="s">
-        <v>4303</v>
+        <v>4302</v>
       </c>
     </row>
     <row r="355" spans="3:20" x14ac:dyDescent="0.25">
@@ -34830,7 +34830,7 @@
         <v>1214</v>
       </c>
       <c r="T355" t="s">
-        <v>4304</v>
+        <v>4303</v>
       </c>
     </row>
     <row r="356" spans="3:20" x14ac:dyDescent="0.25">
@@ -34880,7 +34880,7 @@
         <v>1215</v>
       </c>
       <c r="T356" t="s">
-        <v>4305</v>
+        <v>4304</v>
       </c>
     </row>
     <row r="357" spans="3:20" x14ac:dyDescent="0.25">
@@ -34930,7 +34930,7 @@
         <v>1216</v>
       </c>
       <c r="T357" t="s">
-        <v>4306</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="358" spans="3:20" x14ac:dyDescent="0.25">
@@ -34980,7 +34980,7 @@
         <v>1217</v>
       </c>
       <c r="T358" t="s">
-        <v>4307</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="359" spans="3:20" x14ac:dyDescent="0.25">
@@ -35030,7 +35030,7 @@
         <v>1218</v>
       </c>
       <c r="T359" t="s">
-        <v>4308</v>
+        <v>4307</v>
       </c>
     </row>
     <row r="360" spans="3:20" x14ac:dyDescent="0.25">
@@ -35080,7 +35080,7 @@
         <v>1219</v>
       </c>
       <c r="T360" t="s">
-        <v>4309</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="361" spans="3:20" x14ac:dyDescent="0.25">
@@ -35130,7 +35130,7 @@
         <v>1220</v>
       </c>
       <c r="T361" t="s">
-        <v>4310</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="362" spans="3:20" x14ac:dyDescent="0.25">
@@ -35180,7 +35180,7 @@
         <v>1221</v>
       </c>
       <c r="T362" t="s">
-        <v>4311</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="363" spans="3:20" x14ac:dyDescent="0.25">
@@ -35230,7 +35230,7 @@
         <v>1222</v>
       </c>
       <c r="T363" t="s">
-        <v>4312</v>
+        <v>4311</v>
       </c>
     </row>
     <row r="364" spans="3:20" x14ac:dyDescent="0.25">
@@ -35280,7 +35280,7 @@
         <v>1223</v>
       </c>
       <c r="T364" t="s">
-        <v>4313</v>
+        <v>4312</v>
       </c>
     </row>
     <row r="365" spans="3:20" x14ac:dyDescent="0.25">
@@ -35330,7 +35330,7 @@
         <v>1224</v>
       </c>
       <c r="T365" t="s">
-        <v>4314</v>
+        <v>4313</v>
       </c>
     </row>
     <row r="366" spans="3:20" x14ac:dyDescent="0.25">
@@ -35380,7 +35380,7 @@
         <v>1225</v>
       </c>
       <c r="T366" t="s">
-        <v>4315</v>
+        <v>4314</v>
       </c>
     </row>
     <row r="367" spans="3:20" x14ac:dyDescent="0.25">
@@ -35430,7 +35430,7 @@
         <v>1226</v>
       </c>
       <c r="T367" t="s">
-        <v>4316</v>
+        <v>4315</v>
       </c>
     </row>
     <row r="368" spans="3:20" x14ac:dyDescent="0.25">
@@ -35480,7 +35480,7 @@
         <v>1227</v>
       </c>
       <c r="T368" t="s">
-        <v>4317</v>
+        <v>4316</v>
       </c>
     </row>
     <row r="369" spans="3:20" x14ac:dyDescent="0.25">
@@ -35530,7 +35530,7 @@
         <v>1228</v>
       </c>
       <c r="T369" t="s">
-        <v>4318</v>
+        <v>4317</v>
       </c>
     </row>
     <row r="370" spans="3:20" x14ac:dyDescent="0.25">
@@ -35580,7 +35580,7 @@
         <v>1229</v>
       </c>
       <c r="T370" t="s">
-        <v>4319</v>
+        <v>4318</v>
       </c>
     </row>
     <row r="371" spans="3:20" x14ac:dyDescent="0.25">
@@ -35630,7 +35630,7 @@
         <v>1230</v>
       </c>
       <c r="T371" t="s">
-        <v>4320</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="372" spans="3:20" x14ac:dyDescent="0.25">
@@ -35680,7 +35680,7 @@
         <v>1231</v>
       </c>
       <c r="T372" t="s">
-        <v>4321</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="373" spans="3:20" x14ac:dyDescent="0.25">
@@ -35730,7 +35730,7 @@
         <v>1232</v>
       </c>
       <c r="T373" t="s">
-        <v>4322</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="374" spans="3:20" x14ac:dyDescent="0.25">
@@ -35780,7 +35780,7 @@
         <v>1233</v>
       </c>
       <c r="T374" t="s">
-        <v>4323</v>
+        <v>4322</v>
       </c>
     </row>
     <row r="375" spans="3:20" x14ac:dyDescent="0.25">
@@ -35830,7 +35830,7 @@
         <v>1234</v>
       </c>
       <c r="T375" t="s">
-        <v>4324</v>
+        <v>4323</v>
       </c>
     </row>
     <row r="376" spans="3:20" x14ac:dyDescent="0.25">
@@ -35880,7 +35880,7 @@
         <v>1235</v>
       </c>
       <c r="T376" t="s">
-        <v>4325</v>
+        <v>4324</v>
       </c>
     </row>
     <row r="377" spans="3:20" x14ac:dyDescent="0.25">
@@ -35930,7 +35930,7 @@
         <v>1236</v>
       </c>
       <c r="T377" t="s">
-        <v>4326</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="378" spans="3:20" x14ac:dyDescent="0.25">
@@ -35980,7 +35980,7 @@
         <v>1237</v>
       </c>
       <c r="T378" t="s">
-        <v>4327</v>
+        <v>4326</v>
       </c>
     </row>
     <row r="379" spans="3:20" x14ac:dyDescent="0.25">
@@ -36030,7 +36030,7 @@
         <v>1238</v>
       </c>
       <c r="T379" t="s">
-        <v>4328</v>
+        <v>4327</v>
       </c>
     </row>
     <row r="380" spans="3:20" x14ac:dyDescent="0.25">
@@ -36080,7 +36080,7 @@
         <v>1239</v>
       </c>
       <c r="T380" t="s">
-        <v>4329</v>
+        <v>4328</v>
       </c>
     </row>
     <row r="381" spans="3:20" x14ac:dyDescent="0.25">
@@ -36130,7 +36130,7 @@
         <v>1240</v>
       </c>
       <c r="T381" t="s">
-        <v>4330</v>
+        <v>4329</v>
       </c>
     </row>
     <row r="382" spans="3:20" x14ac:dyDescent="0.25">
@@ -36180,7 +36180,7 @@
         <v>1241</v>
       </c>
       <c r="T382" t="s">
-        <v>4331</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="383" spans="3:20" x14ac:dyDescent="0.25">
@@ -36230,7 +36230,7 @@
         <v>1242</v>
       </c>
       <c r="T383" t="s">
-        <v>4332</v>
+        <v>4331</v>
       </c>
     </row>
     <row r="384" spans="3:20" x14ac:dyDescent="0.25">
@@ -36280,7 +36280,7 @@
         <v>1243</v>
       </c>
       <c r="T384" t="s">
-        <v>4333</v>
+        <v>4332</v>
       </c>
     </row>
     <row r="385" spans="3:20" x14ac:dyDescent="0.25">
@@ -36330,7 +36330,7 @@
         <v>1244</v>
       </c>
       <c r="T385" t="s">
-        <v>4334</v>
+        <v>4333</v>
       </c>
     </row>
     <row r="386" spans="3:20" x14ac:dyDescent="0.25">
@@ -36380,7 +36380,7 @@
         <v>1245</v>
       </c>
       <c r="T386" t="s">
-        <v>4335</v>
+        <v>4334</v>
       </c>
     </row>
     <row r="387" spans="3:20" x14ac:dyDescent="0.25">
@@ -36430,7 +36430,7 @@
         <v>1246</v>
       </c>
       <c r="T387" t="s">
-        <v>4336</v>
+        <v>4335</v>
       </c>
     </row>
     <row r="388" spans="3:20" x14ac:dyDescent="0.25">
@@ -36480,7 +36480,7 @@
         <v>1247</v>
       </c>
       <c r="T388" t="s">
-        <v>4337</v>
+        <v>4336</v>
       </c>
     </row>
     <row r="389" spans="3:20" x14ac:dyDescent="0.25">
@@ -36530,7 +36530,7 @@
         <v>1248</v>
       </c>
       <c r="T389" t="s">
-        <v>4338</v>
+        <v>4337</v>
       </c>
     </row>
     <row r="390" spans="3:20" x14ac:dyDescent="0.25">
@@ -36580,7 +36580,7 @@
         <v>1249</v>
       </c>
       <c r="T390" t="s">
-        <v>4339</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="391" spans="3:20" x14ac:dyDescent="0.25">
@@ -36630,7 +36630,7 @@
         <v>1250</v>
       </c>
       <c r="T391" t="s">
-        <v>4340</v>
+        <v>4339</v>
       </c>
     </row>
     <row r="392" spans="3:20" x14ac:dyDescent="0.25">
@@ -36680,7 +36680,7 @@
         <v>1251</v>
       </c>
       <c r="T392" t="s">
-        <v>4341</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="393" spans="3:20" x14ac:dyDescent="0.25">
@@ -36730,7 +36730,7 @@
         <v>1252</v>
       </c>
       <c r="T393" t="s">
-        <v>4342</v>
+        <v>4341</v>
       </c>
     </row>
     <row r="394" spans="3:20" x14ac:dyDescent="0.25">
@@ -36780,7 +36780,7 @@
         <v>1253</v>
       </c>
       <c r="T394" t="s">
-        <v>4343</v>
+        <v>4342</v>
       </c>
     </row>
     <row r="395" spans="3:20" x14ac:dyDescent="0.25">
@@ -36830,7 +36830,7 @@
         <v>1254</v>
       </c>
       <c r="T395" t="s">
-        <v>4344</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="396" spans="3:20" x14ac:dyDescent="0.25">
@@ -36880,7 +36880,7 @@
         <v>1255</v>
       </c>
       <c r="T396" t="s">
-        <v>4345</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="397" spans="3:20" x14ac:dyDescent="0.25">
@@ -36930,7 +36930,7 @@
         <v>1256</v>
       </c>
       <c r="T397" t="s">
-        <v>4346</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="398" spans="3:20" x14ac:dyDescent="0.25">
@@ -36980,7 +36980,7 @@
         <v>1257</v>
       </c>
       <c r="T398" t="s">
-        <v>4347</v>
+        <v>4346</v>
       </c>
     </row>
     <row r="399" spans="3:20" x14ac:dyDescent="0.25">
@@ -37030,7 +37030,7 @@
         <v>1258</v>
       </c>
       <c r="T399" t="s">
-        <v>4348</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="400" spans="3:20" x14ac:dyDescent="0.25">
@@ -37080,7 +37080,7 @@
         <v>1259</v>
       </c>
       <c r="T400" t="s">
-        <v>4349</v>
+        <v>4348</v>
       </c>
     </row>
     <row r="401" spans="3:20" x14ac:dyDescent="0.25">
@@ -37130,7 +37130,7 @@
         <v>1260</v>
       </c>
       <c r="T401" t="s">
-        <v>4350</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="402" spans="3:20" x14ac:dyDescent="0.25">
@@ -37180,7 +37180,7 @@
         <v>1261</v>
       </c>
       <c r="T402" t="s">
-        <v>4351</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="403" spans="3:20" x14ac:dyDescent="0.25">
@@ -37230,7 +37230,7 @@
         <v>1262</v>
       </c>
       <c r="T403" t="s">
-        <v>4352</v>
+        <v>4351</v>
       </c>
     </row>
     <row r="404" spans="3:20" x14ac:dyDescent="0.25">
@@ -37280,7 +37280,7 @@
         <v>1263</v>
       </c>
       <c r="T404" t="s">
-        <v>4353</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="405" spans="3:20" x14ac:dyDescent="0.25">
@@ -37330,7 +37330,7 @@
         <v>1264</v>
       </c>
       <c r="T405" t="s">
-        <v>4354</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="406" spans="3:20" x14ac:dyDescent="0.25">
@@ -37380,7 +37380,7 @@
         <v>1265</v>
       </c>
       <c r="T406" t="s">
-        <v>4355</v>
+        <v>4354</v>
       </c>
     </row>
     <row r="407" spans="3:20" x14ac:dyDescent="0.25">
@@ -37430,7 +37430,7 @@
         <v>1266</v>
       </c>
       <c r="T407" t="s">
-        <v>4356</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="408" spans="3:20" x14ac:dyDescent="0.25">
@@ -37477,7 +37477,7 @@
         <v>1267</v>
       </c>
       <c r="T408" t="s">
-        <v>4357</v>
+        <v>4356</v>
       </c>
     </row>
     <row r="409" spans="3:20" x14ac:dyDescent="0.25">
@@ -37524,7 +37524,7 @@
         <v>1268</v>
       </c>
       <c r="T409" t="s">
-        <v>4358</v>
+        <v>4357</v>
       </c>
     </row>
     <row r="410" spans="3:20" x14ac:dyDescent="0.25">
@@ -37571,7 +37571,7 @@
         <v>1269</v>
       </c>
       <c r="T410" t="s">
-        <v>4359</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="411" spans="3:20" x14ac:dyDescent="0.25">
@@ -37618,7 +37618,7 @@
         <v>1270</v>
       </c>
       <c r="T411" t="s">
-        <v>4360</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="412" spans="3:20" x14ac:dyDescent="0.25">
@@ -37665,7 +37665,7 @@
         <v>1271</v>
       </c>
       <c r="T412" t="s">
-        <v>4361</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="413" spans="3:20" x14ac:dyDescent="0.25">
@@ -37712,7 +37712,7 @@
         <v>1272</v>
       </c>
       <c r="T413" t="s">
-        <v>4362</v>
+        <v>4361</v>
       </c>
     </row>
     <row r="414" spans="3:20" x14ac:dyDescent="0.25">
@@ -37759,7 +37759,7 @@
         <v>1273</v>
       </c>
       <c r="T414" t="s">
-        <v>4363</v>
+        <v>4362</v>
       </c>
     </row>
     <row r="415" spans="3:20" x14ac:dyDescent="0.25">
@@ -37806,7 +37806,7 @@
         <v>1274</v>
       </c>
       <c r="T415" t="s">
-        <v>4364</v>
+        <v>4363</v>
       </c>
     </row>
     <row r="416" spans="3:20" x14ac:dyDescent="0.25">
@@ -37853,7 +37853,7 @@
         <v>1275</v>
       </c>
       <c r="T416" t="s">
-        <v>4365</v>
+        <v>4364</v>
       </c>
     </row>
     <row r="417" spans="3:20" x14ac:dyDescent="0.25">
@@ -37900,7 +37900,7 @@
         <v>1276</v>
       </c>
       <c r="T417" t="s">
-        <v>4366</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="418" spans="3:20" x14ac:dyDescent="0.25">
@@ -37947,7 +37947,7 @@
         <v>1277</v>
       </c>
       <c r="T418" t="s">
-        <v>4367</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="419" spans="3:20" x14ac:dyDescent="0.25">
@@ -37994,7 +37994,7 @@
         <v>1278</v>
       </c>
       <c r="T419" t="s">
-        <v>4368</v>
+        <v>4367</v>
       </c>
     </row>
     <row r="420" spans="3:20" x14ac:dyDescent="0.25">
@@ -38041,7 +38041,7 @@
         <v>1279</v>
       </c>
       <c r="T420" t="s">
-        <v>4369</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="421" spans="3:20" x14ac:dyDescent="0.25">
@@ -38088,7 +38088,7 @@
         <v>1280</v>
       </c>
       <c r="T421" t="s">
-        <v>4370</v>
+        <v>4369</v>
       </c>
     </row>
     <row r="422" spans="3:20" x14ac:dyDescent="0.25">
@@ -38135,7 +38135,7 @@
         <v>1281</v>
       </c>
       <c r="T422" t="s">
-        <v>4371</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="423" spans="3:20" x14ac:dyDescent="0.25">
@@ -38182,7 +38182,7 @@
         <v>1282</v>
       </c>
       <c r="T423" t="s">
-        <v>4372</v>
+        <v>4371</v>
       </c>
     </row>
     <row r="424" spans="3:20" x14ac:dyDescent="0.25">
@@ -38229,7 +38229,7 @@
         <v>1283</v>
       </c>
       <c r="T424" t="s">
-        <v>4373</v>
+        <v>4372</v>
       </c>
     </row>
     <row r="425" spans="3:20" x14ac:dyDescent="0.25">
@@ -38276,7 +38276,7 @@
         <v>1284</v>
       </c>
       <c r="T425" t="s">
-        <v>4374</v>
+        <v>4373</v>
       </c>
     </row>
     <row r="426" spans="3:20" x14ac:dyDescent="0.25">
@@ -38323,7 +38323,7 @@
         <v>1285</v>
       </c>
       <c r="T426" t="s">
-        <v>4375</v>
+        <v>4374</v>
       </c>
     </row>
     <row r="427" spans="3:20" x14ac:dyDescent="0.25">
@@ -38370,7 +38370,7 @@
         <v>1286</v>
       </c>
       <c r="T427" t="s">
-        <v>4376</v>
+        <v>4375</v>
       </c>
     </row>
     <row r="428" spans="3:20" x14ac:dyDescent="0.25">
@@ -38417,7 +38417,7 @@
         <v>1287</v>
       </c>
       <c r="T428" t="s">
-        <v>4377</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="429" spans="3:20" x14ac:dyDescent="0.25">
@@ -38464,7 +38464,7 @@
         <v>1288</v>
       </c>
       <c r="T429" t="s">
-        <v>4378</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="430" spans="3:20" x14ac:dyDescent="0.25">
@@ -38511,7 +38511,7 @@
         <v>1289</v>
       </c>
       <c r="T430" t="s">
-        <v>4379</v>
+        <v>4378</v>
       </c>
     </row>
     <row r="431" spans="3:20" x14ac:dyDescent="0.25">
@@ -38558,7 +38558,7 @@
         <v>1290</v>
       </c>
       <c r="T431" t="s">
-        <v>4380</v>
+        <v>4379</v>
       </c>
     </row>
     <row r="432" spans="3:20" x14ac:dyDescent="0.25">
@@ -38605,7 +38605,7 @@
         <v>1291</v>
       </c>
       <c r="T432" t="s">
-        <v>4381</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="433" spans="3:20" x14ac:dyDescent="0.25">
@@ -38652,7 +38652,7 @@
         <v>1292</v>
       </c>
       <c r="T433" t="s">
-        <v>4382</v>
+        <v>4381</v>
       </c>
     </row>
     <row r="434" spans="3:20" x14ac:dyDescent="0.25">
@@ -38699,7 +38699,7 @@
         <v>1293</v>
       </c>
       <c r="T434" t="s">
-        <v>4383</v>
+        <v>4382</v>
       </c>
     </row>
     <row r="435" spans="3:20" x14ac:dyDescent="0.25">
@@ -38746,7 +38746,7 @@
         <v>1294</v>
       </c>
       <c r="T435" t="s">
-        <v>4384</v>
+        <v>4383</v>
       </c>
     </row>
     <row r="436" spans="3:20" x14ac:dyDescent="0.25">
@@ -38793,7 +38793,7 @@
         <v>1295</v>
       </c>
       <c r="T436" t="s">
-        <v>4385</v>
+        <v>4384</v>
       </c>
     </row>
     <row r="437" spans="3:20" x14ac:dyDescent="0.25">
@@ -38840,7 +38840,7 @@
         <v>1296</v>
       </c>
       <c r="T437" t="s">
-        <v>4386</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="438" spans="3:20" x14ac:dyDescent="0.25">
@@ -38887,7 +38887,7 @@
         <v>1297</v>
       </c>
       <c r="T438" t="s">
-        <v>4387</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="439" spans="3:20" x14ac:dyDescent="0.25">
@@ -38934,7 +38934,7 @@
         <v>1298</v>
       </c>
       <c r="T439" t="s">
-        <v>4388</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="440" spans="3:20" x14ac:dyDescent="0.25">
@@ -38981,7 +38981,7 @@
         <v>1299</v>
       </c>
       <c r="T440" t="s">
-        <v>4389</v>
+        <v>4388</v>
       </c>
     </row>
     <row r="441" spans="3:20" x14ac:dyDescent="0.25">
@@ -39028,7 +39028,7 @@
         <v>1300</v>
       </c>
       <c r="T441" t="s">
-        <v>4390</v>
+        <v>4389</v>
       </c>
     </row>
     <row r="442" spans="3:20" x14ac:dyDescent="0.25">
@@ -39075,7 +39075,7 @@
         <v>1301</v>
       </c>
       <c r="T442" t="s">
-        <v>4391</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="443" spans="3:20" x14ac:dyDescent="0.25">
@@ -39122,7 +39122,7 @@
         <v>1302</v>
       </c>
       <c r="T443" t="s">
-        <v>4392</v>
+        <v>4391</v>
       </c>
     </row>
     <row r="444" spans="3:20" x14ac:dyDescent="0.25">
@@ -39169,7 +39169,7 @@
         <v>1303</v>
       </c>
       <c r="T444" t="s">
-        <v>4393</v>
+        <v>4392</v>
       </c>
     </row>
     <row r="445" spans="3:20" x14ac:dyDescent="0.25">
@@ -39216,7 +39216,7 @@
         <v>1304</v>
       </c>
       <c r="T445" t="s">
-        <v>4394</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="446" spans="3:20" x14ac:dyDescent="0.25">
@@ -39263,7 +39263,7 @@
         <v>1305</v>
       </c>
       <c r="T446" t="s">
-        <v>4395</v>
+        <v>4394</v>
       </c>
     </row>
     <row r="447" spans="3:20" x14ac:dyDescent="0.25">
@@ -39310,7 +39310,7 @@
         <v>1306</v>
       </c>
       <c r="T447" t="s">
-        <v>4396</v>
+        <v>4395</v>
       </c>
     </row>
     <row r="448" spans="3:20" x14ac:dyDescent="0.25">
@@ -39357,7 +39357,7 @@
         <v>1307</v>
       </c>
       <c r="T448" t="s">
-        <v>4397</v>
+        <v>4396</v>
       </c>
     </row>
     <row r="449" spans="3:20" x14ac:dyDescent="0.25">
@@ -39404,7 +39404,7 @@
         <v>1308</v>
       </c>
       <c r="T449" t="s">
-        <v>4398</v>
+        <v>4397</v>
       </c>
     </row>
     <row r="450" spans="3:20" x14ac:dyDescent="0.25">
@@ -39451,7 +39451,7 @@
         <v>1309</v>
       </c>
       <c r="T450" t="s">
-        <v>4399</v>
+        <v>4398</v>
       </c>
     </row>
     <row r="451" spans="3:20" x14ac:dyDescent="0.25">
@@ -39498,7 +39498,7 @@
         <v>1310</v>
       </c>
       <c r="T451" t="s">
-        <v>4400</v>
+        <v>4399</v>
       </c>
     </row>
     <row r="452" spans="3:20" x14ac:dyDescent="0.25">
@@ -39545,7 +39545,7 @@
         <v>1311</v>
       </c>
       <c r="T452" t="s">
-        <v>4401</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="453" spans="3:20" x14ac:dyDescent="0.25">
@@ -39592,7 +39592,7 @@
         <v>1312</v>
       </c>
       <c r="T453" t="s">
-        <v>4402</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="454" spans="3:20" x14ac:dyDescent="0.25">
@@ -39639,7 +39639,7 @@
         <v>1313</v>
       </c>
       <c r="T454" t="s">
-        <v>4403</v>
+        <v>4402</v>
       </c>
     </row>
     <row r="455" spans="3:20" x14ac:dyDescent="0.25">
@@ -39686,7 +39686,7 @@
         <v>1314</v>
       </c>
       <c r="T455" t="s">
-        <v>4404</v>
+        <v>4403</v>
       </c>
     </row>
     <row r="456" spans="3:20" x14ac:dyDescent="0.25">
@@ -39733,7 +39733,7 @@
         <v>1315</v>
       </c>
       <c r="T456" t="s">
-        <v>4405</v>
+        <v>4404</v>
       </c>
     </row>
     <row r="457" spans="3:20" x14ac:dyDescent="0.25">
@@ -39780,7 +39780,7 @@
         <v>1316</v>
       </c>
       <c r="T457" t="s">
-        <v>4406</v>
+        <v>4405</v>
       </c>
     </row>
     <row r="458" spans="3:20" x14ac:dyDescent="0.25">
@@ -39827,7 +39827,7 @@
         <v>1317</v>
       </c>
       <c r="T458" t="s">
-        <v>4407</v>
+        <v>4406</v>
       </c>
     </row>
     <row r="459" spans="3:20" x14ac:dyDescent="0.25">
@@ -39874,7 +39874,7 @@
         <v>1318</v>
       </c>
       <c r="T459" t="s">
-        <v>4408</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="460" spans="3:20" x14ac:dyDescent="0.25">
@@ -39921,7 +39921,7 @@
         <v>1319</v>
       </c>
       <c r="T460" t="s">
-        <v>4409</v>
+        <v>4408</v>
       </c>
     </row>
     <row r="461" spans="3:20" x14ac:dyDescent="0.25">
@@ -39968,7 +39968,7 @@
         <v>1320</v>
       </c>
       <c r="T461" t="s">
-        <v>4410</v>
+        <v>4409</v>
       </c>
     </row>
     <row r="462" spans="3:20" x14ac:dyDescent="0.25">
@@ -40015,7 +40015,7 @@
         <v>1321</v>
       </c>
       <c r="T462" t="s">
-        <v>4411</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="463" spans="3:20" x14ac:dyDescent="0.25">
@@ -40062,7 +40062,7 @@
         <v>1322</v>
       </c>
       <c r="T463" t="s">
-        <v>4412</v>
+        <v>4411</v>
       </c>
     </row>
     <row r="464" spans="3:20" x14ac:dyDescent="0.25">
@@ -40109,7 +40109,7 @@
         <v>1323</v>
       </c>
       <c r="T464" t="s">
-        <v>4413</v>
+        <v>4412</v>
       </c>
     </row>
     <row r="465" spans="3:20" x14ac:dyDescent="0.25">
@@ -40156,7 +40156,7 @@
         <v>1324</v>
       </c>
       <c r="T465" t="s">
-        <v>4414</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="466" spans="3:20" x14ac:dyDescent="0.25">
@@ -40203,7 +40203,7 @@
         <v>1325</v>
       </c>
       <c r="T466" t="s">
-        <v>4415</v>
+        <v>4414</v>
       </c>
     </row>
     <row r="467" spans="3:20" x14ac:dyDescent="0.25">
@@ -40250,7 +40250,7 @@
         <v>1326</v>
       </c>
       <c r="T467" t="s">
-        <v>4416</v>
+        <v>4415</v>
       </c>
     </row>
     <row r="468" spans="3:20" x14ac:dyDescent="0.25">
@@ -40297,7 +40297,7 @@
         <v>1327</v>
       </c>
       <c r="T468" t="s">
-        <v>4417</v>
+        <v>4416</v>
       </c>
     </row>
     <row r="469" spans="3:20" x14ac:dyDescent="0.25">
@@ -40344,7 +40344,7 @@
         <v>1328</v>
       </c>
       <c r="T469" t="s">
-        <v>4418</v>
+        <v>4417</v>
       </c>
     </row>
     <row r="470" spans="3:20" x14ac:dyDescent="0.25">
@@ -40391,7 +40391,7 @@
         <v>1329</v>
       </c>
       <c r="T470" t="s">
-        <v>4419</v>
+        <v>4418</v>
       </c>
     </row>
     <row r="471" spans="3:20" x14ac:dyDescent="0.25">
@@ -40438,7 +40438,7 @@
         <v>1330</v>
       </c>
       <c r="T471" t="s">
-        <v>4420</v>
+        <v>4419</v>
       </c>
     </row>
     <row r="472" spans="3:20" x14ac:dyDescent="0.25">
@@ -40485,7 +40485,7 @@
         <v>1331</v>
       </c>
       <c r="T472" t="s">
-        <v>4421</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="473" spans="3:20" x14ac:dyDescent="0.25">
@@ -40532,7 +40532,7 @@
         <v>1332</v>
       </c>
       <c r="T473" t="s">
-        <v>4422</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="474" spans="3:20" x14ac:dyDescent="0.25">
@@ -40579,7 +40579,7 @@
         <v>1333</v>
       </c>
       <c r="T474" t="s">
-        <v>4423</v>
+        <v>4422</v>
       </c>
     </row>
     <row r="475" spans="3:20" x14ac:dyDescent="0.25">
@@ -40626,7 +40626,7 @@
         <v>1334</v>
       </c>
       <c r="T475" t="s">
-        <v>4424</v>
+        <v>4423</v>
       </c>
     </row>
     <row r="476" spans="3:20" x14ac:dyDescent="0.25">
@@ -40673,7 +40673,7 @@
         <v>1335</v>
       </c>
       <c r="T476" t="s">
-        <v>4425</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="477" spans="3:20" x14ac:dyDescent="0.25">
@@ -40720,7 +40720,7 @@
         <v>1336</v>
       </c>
       <c r="T477" t="s">
-        <v>4426</v>
+        <v>4425</v>
       </c>
     </row>
     <row r="478" spans="3:20" x14ac:dyDescent="0.25">
@@ -40767,7 +40767,7 @@
         <v>1337</v>
       </c>
       <c r="T478" t="s">
-        <v>4427</v>
+        <v>4426</v>
       </c>
     </row>
     <row r="479" spans="3:20" x14ac:dyDescent="0.25">
@@ -40814,7 +40814,7 @@
         <v>1338</v>
       </c>
       <c r="T479" t="s">
-        <v>4428</v>
+        <v>4427</v>
       </c>
     </row>
     <row r="480" spans="3:20" x14ac:dyDescent="0.25">
@@ -40861,7 +40861,7 @@
         <v>1339</v>
       </c>
       <c r="T480" t="s">
-        <v>4429</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="481" spans="3:20" x14ac:dyDescent="0.25">
@@ -40908,7 +40908,7 @@
         <v>1340</v>
       </c>
       <c r="T481" t="s">
-        <v>4430</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="482" spans="3:20" x14ac:dyDescent="0.25">
@@ -40955,7 +40955,7 @@
         <v>1341</v>
       </c>
       <c r="T482" t="s">
-        <v>4431</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="483" spans="3:20" x14ac:dyDescent="0.25">
@@ -41002,7 +41002,7 @@
         <v>1342</v>
       </c>
       <c r="T483" t="s">
-        <v>4432</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="484" spans="3:20" x14ac:dyDescent="0.25">
@@ -41049,7 +41049,7 @@
         <v>1343</v>
       </c>
       <c r="T484" t="s">
-        <v>4433</v>
+        <v>4432</v>
       </c>
     </row>
     <row r="485" spans="3:20" x14ac:dyDescent="0.25">
@@ -41090,7 +41090,7 @@
         <v>1344</v>
       </c>
       <c r="T485" t="s">
-        <v>4434</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="486" spans="3:20" x14ac:dyDescent="0.25">
@@ -41131,7 +41131,7 @@
         <v>1345</v>
       </c>
       <c r="T486" t="s">
-        <v>4435</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="487" spans="3:20" x14ac:dyDescent="0.25">
@@ -41172,7 +41172,7 @@
         <v>1346</v>
       </c>
       <c r="T487" t="s">
-        <v>4436</v>
+        <v>4435</v>
       </c>
     </row>
     <row r="488" spans="3:20" x14ac:dyDescent="0.25">
@@ -41213,7 +41213,7 @@
         <v>1347</v>
       </c>
       <c r="T488" t="s">
-        <v>4437</v>
+        <v>4436</v>
       </c>
     </row>
     <row r="489" spans="3:20" x14ac:dyDescent="0.25">
@@ -41254,7 +41254,7 @@
         <v>1348</v>
       </c>
       <c r="T489" t="s">
-        <v>4438</v>
+        <v>4437</v>
       </c>
     </row>
     <row r="490" spans="3:20" x14ac:dyDescent="0.25">
@@ -41295,7 +41295,7 @@
         <v>1349</v>
       </c>
       <c r="T490" t="s">
-        <v>4439</v>
+        <v>4438</v>
       </c>
     </row>
     <row r="491" spans="3:20" x14ac:dyDescent="0.25">
@@ -41336,7 +41336,7 @@
         <v>1350</v>
       </c>
       <c r="T491" t="s">
-        <v>4440</v>
+        <v>4439</v>
       </c>
     </row>
     <row r="492" spans="3:20" x14ac:dyDescent="0.25">
@@ -41377,7 +41377,7 @@
         <v>1383</v>
       </c>
       <c r="T492" t="s">
-        <v>4441</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="493" spans="3:20" x14ac:dyDescent="0.25">
@@ -41418,7 +41418,7 @@
         <v>1384</v>
       </c>
       <c r="T493" t="s">
-        <v>4442</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="494" spans="3:20" x14ac:dyDescent="0.25">
@@ -41459,7 +41459,7 @@
         <v>1385</v>
       </c>
       <c r="T494" t="s">
-        <v>4443</v>
+        <v>4442</v>
       </c>
     </row>
     <row r="495" spans="3:20" x14ac:dyDescent="0.25">
@@ -41500,7 +41500,7 @@
         <v>1386</v>
       </c>
       <c r="T495" t="s">
-        <v>4444</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="496" spans="3:20" x14ac:dyDescent="0.25">
@@ -41541,7 +41541,7 @@
         <v>1387</v>
       </c>
       <c r="T496" t="s">
-        <v>4445</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="497" spans="3:20" x14ac:dyDescent="0.25">
@@ -41582,7 +41582,7 @@
         <v>1388</v>
       </c>
       <c r="T497" t="s">
-        <v>4446</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="498" spans="3:20" x14ac:dyDescent="0.25">
@@ -41623,7 +41623,7 @@
         <v>1389</v>
       </c>
       <c r="T498" t="s">
-        <v>4447</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="499" spans="3:20" x14ac:dyDescent="0.25">
@@ -41664,7 +41664,7 @@
         <v>1390</v>
       </c>
       <c r="T499" t="s">
-        <v>4448</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="500" spans="3:20" x14ac:dyDescent="0.25">
@@ -41705,7 +41705,7 @@
         <v>1391</v>
       </c>
       <c r="T500" t="s">
-        <v>4449</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="501" spans="3:20" x14ac:dyDescent="0.25">
@@ -41746,7 +41746,7 @@
         <v>1392</v>
       </c>
       <c r="T501" t="s">
-        <v>4450</v>
+        <v>4449</v>
       </c>
     </row>
     <row r="502" spans="3:20" x14ac:dyDescent="0.25">
@@ -41787,7 +41787,7 @@
         <v>1393</v>
       </c>
       <c r="T502" t="s">
-        <v>4451</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="503" spans="3:20" x14ac:dyDescent="0.25">
@@ -41828,7 +41828,7 @@
         <v>1394</v>
       </c>
       <c r="T503" t="s">
-        <v>4452</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="504" spans="3:20" x14ac:dyDescent="0.25">
@@ -41869,7 +41869,7 @@
         <v>1395</v>
       </c>
       <c r="T504" t="s">
-        <v>4453</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="505" spans="3:20" x14ac:dyDescent="0.25">
@@ -41910,7 +41910,7 @@
         <v>1396</v>
       </c>
       <c r="T505" t="s">
-        <v>4454</v>
+        <v>4453</v>
       </c>
     </row>
     <row r="506" spans="3:20" x14ac:dyDescent="0.25">
@@ -41951,7 +41951,7 @@
         <v>1397</v>
       </c>
       <c r="T506" t="s">
-        <v>4455</v>
+        <v>4454</v>
       </c>
     </row>
     <row r="507" spans="3:20" x14ac:dyDescent="0.25">
@@ -41992,7 +41992,7 @@
         <v>1398</v>
       </c>
       <c r="T507" t="s">
-        <v>4456</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="508" spans="3:20" x14ac:dyDescent="0.25">
@@ -42033,7 +42033,7 @@
         <v>1399</v>
       </c>
       <c r="T508" t="s">
-        <v>4457</v>
+        <v>4456</v>
       </c>
     </row>
     <row r="509" spans="3:20" x14ac:dyDescent="0.25">
@@ -42074,7 +42074,7 @@
         <v>1400</v>
       </c>
       <c r="T509" t="s">
-        <v>4458</v>
+        <v>4457</v>
       </c>
     </row>
     <row r="510" spans="3:20" x14ac:dyDescent="0.25">
@@ -42115,7 +42115,7 @@
         <v>1401</v>
       </c>
       <c r="T510" t="s">
-        <v>4459</v>
+        <v>4458</v>
       </c>
     </row>
     <row r="511" spans="3:20" x14ac:dyDescent="0.25">
@@ -42153,7 +42153,7 @@
         <v>1402</v>
       </c>
       <c r="T511" t="s">
-        <v>4460</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="512" spans="3:20" x14ac:dyDescent="0.25">
@@ -42191,7 +42191,7 @@
         <v>1403</v>
       </c>
       <c r="T512" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="513" spans="3:20" x14ac:dyDescent="0.25">
@@ -42229,7 +42229,7 @@
         <v>1404</v>
       </c>
       <c r="T513" t="s">
-        <v>4462</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="514" spans="3:20" x14ac:dyDescent="0.25">
@@ -42267,7 +42267,7 @@
         <v>1405</v>
       </c>
       <c r="T514" t="s">
-        <v>4463</v>
+        <v>4462</v>
       </c>
     </row>
     <row r="515" spans="3:20" x14ac:dyDescent="0.25">
@@ -42305,7 +42305,7 @@
         <v>1406</v>
       </c>
       <c r="T515" t="s">
-        <v>4464</v>
+        <v>4463</v>
       </c>
     </row>
     <row r="516" spans="3:20" x14ac:dyDescent="0.25">
@@ -42343,7 +42343,7 @@
         <v>1407</v>
       </c>
       <c r="T516" t="s">
-        <v>4465</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="517" spans="3:20" x14ac:dyDescent="0.25">
@@ -42381,7 +42381,7 @@
         <v>1408</v>
       </c>
       <c r="T517" t="s">
-        <v>4466</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="518" spans="3:20" x14ac:dyDescent="0.25">
@@ -42419,7 +42419,7 @@
         <v>1409</v>
       </c>
       <c r="T518" t="s">
-        <v>4467</v>
+        <v>4466</v>
       </c>
     </row>
     <row r="519" spans="3:20" x14ac:dyDescent="0.25">
@@ -42457,7 +42457,7 @@
         <v>1410</v>
       </c>
       <c r="T519" t="s">
-        <v>4468</v>
+        <v>4467</v>
       </c>
     </row>
     <row r="520" spans="3:20" x14ac:dyDescent="0.25">
@@ -42495,7 +42495,7 @@
         <v>1411</v>
       </c>
       <c r="T520" t="s">
-        <v>4469</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="521" spans="3:20" x14ac:dyDescent="0.25">
@@ -42533,7 +42533,7 @@
         <v>1412</v>
       </c>
       <c r="T521" t="s">
-        <v>4470</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="522" spans="3:20" x14ac:dyDescent="0.25">
@@ -42571,7 +42571,7 @@
         <v>1413</v>
       </c>
       <c r="T522" t="s">
-        <v>4471</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="523" spans="3:20" x14ac:dyDescent="0.25">
@@ -42609,7 +42609,7 @@
         <v>1414</v>
       </c>
       <c r="T523" t="s">
-        <v>4472</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="524" spans="3:20" x14ac:dyDescent="0.25">
@@ -42647,7 +42647,7 @@
         <v>1415</v>
       </c>
       <c r="T524" t="s">
-        <v>4473</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="525" spans="3:20" x14ac:dyDescent="0.25">
@@ -42685,7 +42685,7 @@
         <v>1416</v>
       </c>
       <c r="T525" t="s">
-        <v>4474</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="526" spans="3:20" x14ac:dyDescent="0.25">
@@ -42723,7 +42723,7 @@
         <v>1417</v>
       </c>
       <c r="T526" t="s">
-        <v>4475</v>
+        <v>4474</v>
       </c>
     </row>
     <row r="527" spans="3:20" x14ac:dyDescent="0.25">
@@ -42761,7 +42761,7 @@
         <v>1418</v>
       </c>
       <c r="T527" t="s">
-        <v>4476</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="528" spans="3:20" x14ac:dyDescent="0.25">
@@ -42799,7 +42799,7 @@
         <v>1419</v>
       </c>
       <c r="T528" t="s">
-        <v>4477</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="529" spans="3:20" x14ac:dyDescent="0.25">
@@ -42837,7 +42837,7 @@
         <v>1420</v>
       </c>
       <c r="T529" t="s">
-        <v>4478</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="530" spans="3:20" x14ac:dyDescent="0.25">
@@ -42875,7 +42875,7 @@
         <v>1421</v>
       </c>
       <c r="T530" t="s">
-        <v>4479</v>
+        <v>4478</v>
       </c>
     </row>
     <row r="531" spans="3:20" x14ac:dyDescent="0.25">
@@ -42913,7 +42913,7 @@
         <v>1422</v>
       </c>
       <c r="T531" t="s">
-        <v>4480</v>
+        <v>4479</v>
       </c>
     </row>
     <row r="532" spans="3:20" x14ac:dyDescent="0.25">
@@ -42951,7 +42951,7 @@
         <v>1423</v>
       </c>
       <c r="T532" t="s">
-        <v>4481</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="533" spans="3:20" x14ac:dyDescent="0.25">
@@ -42989,7 +42989,7 @@
         <v>1424</v>
       </c>
       <c r="T533" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="534" spans="3:20" x14ac:dyDescent="0.25">
@@ -43027,7 +43027,7 @@
         <v>1425</v>
       </c>
       <c r="T534" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="535" spans="3:20" x14ac:dyDescent="0.25">
@@ -43065,7 +43065,7 @@
         <v>1426</v>
       </c>
       <c r="T535" t="s">
-        <v>4484</v>
+        <v>4483</v>
       </c>
     </row>
     <row r="536" spans="3:20" x14ac:dyDescent="0.25">
@@ -43103,7 +43103,7 @@
         <v>1427</v>
       </c>
       <c r="T536" t="s">
-        <v>4485</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="537" spans="3:20" x14ac:dyDescent="0.25">
@@ -43141,7 +43141,7 @@
         <v>1428</v>
       </c>
       <c r="T537" t="s">
-        <v>4486</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="538" spans="3:20" x14ac:dyDescent="0.25">
@@ -43179,7 +43179,7 @@
         <v>1429</v>
       </c>
       <c r="T538" t="s">
-        <v>4487</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="539" spans="3:20" x14ac:dyDescent="0.25">
@@ -43217,7 +43217,7 @@
         <v>1430</v>
       </c>
       <c r="T539" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="540" spans="3:20" x14ac:dyDescent="0.25">
@@ -43255,7 +43255,7 @@
         <v>1431</v>
       </c>
       <c r="T540" t="s">
-        <v>4489</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="541" spans="3:20" x14ac:dyDescent="0.25">
@@ -43293,7 +43293,7 @@
         <v>1432</v>
       </c>
       <c r="T541" t="s">
-        <v>4490</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="542" spans="3:20" x14ac:dyDescent="0.25">
@@ -43331,7 +43331,7 @@
         <v>1433</v>
       </c>
       <c r="T542" t="s">
-        <v>4491</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="543" spans="3:20" x14ac:dyDescent="0.25">
@@ -43369,7 +43369,7 @@
         <v>1434</v>
       </c>
       <c r="T543" t="s">
-        <v>4492</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="544" spans="3:20" x14ac:dyDescent="0.25">
@@ -43407,7 +43407,7 @@
         <v>1435</v>
       </c>
       <c r="T544" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="545" spans="3:20" x14ac:dyDescent="0.25">
@@ -43445,7 +43445,7 @@
         <v>1436</v>
       </c>
       <c r="T545" t="s">
-        <v>4494</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="546" spans="3:20" x14ac:dyDescent="0.25">
@@ -43483,7 +43483,7 @@
         <v>1437</v>
       </c>
       <c r="T546" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="547" spans="3:20" x14ac:dyDescent="0.25">
@@ -43521,7 +43521,7 @@
         <v>1438</v>
       </c>
       <c r="T547" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="548" spans="3:20" x14ac:dyDescent="0.25">
@@ -43559,7 +43559,7 @@
         <v>1439</v>
       </c>
       <c r="T548" t="s">
-        <v>4497</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="549" spans="3:20" x14ac:dyDescent="0.25">
@@ -43597,7 +43597,7 @@
         <v>1440</v>
       </c>
       <c r="T549" t="s">
-        <v>4498</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="550" spans="3:20" x14ac:dyDescent="0.25">
@@ -43635,7 +43635,7 @@
         <v>1441</v>
       </c>
       <c r="T550" t="s">
-        <v>4499</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="551" spans="3:20" x14ac:dyDescent="0.25">
@@ -43673,7 +43673,7 @@
         <v>1442</v>
       </c>
       <c r="T551" t="s">
-        <v>4500</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="552" spans="3:20" x14ac:dyDescent="0.25">
@@ -43711,7 +43711,7 @@
         <v>1443</v>
       </c>
       <c r="T552" t="s">
-        <v>4501</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="553" spans="3:20" x14ac:dyDescent="0.25">
@@ -43749,7 +43749,7 @@
         <v>1444</v>
       </c>
       <c r="T553" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="554" spans="3:20" x14ac:dyDescent="0.25">
@@ -43787,7 +43787,7 @@
         <v>1445</v>
       </c>
       <c r="T554" t="s">
-        <v>4503</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="555" spans="3:20" x14ac:dyDescent="0.25">
@@ -43825,7 +43825,7 @@
         <v>1446</v>
       </c>
       <c r="T555" t="s">
-        <v>4504</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="556" spans="3:20" x14ac:dyDescent="0.25">
@@ -43863,7 +43863,7 @@
         <v>1451</v>
       </c>
       <c r="T556" t="s">
-        <v>4505</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="557" spans="3:20" x14ac:dyDescent="0.25">
@@ -43901,7 +43901,7 @@
         <v>1452</v>
       </c>
       <c r="T557" t="s">
-        <v>4506</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="558" spans="3:20" x14ac:dyDescent="0.25">
@@ -43939,7 +43939,7 @@
         <v>1453</v>
       </c>
       <c r="T558" t="s">
-        <v>4507</v>
+        <v>4506</v>
       </c>
     </row>
     <row r="559" spans="3:20" x14ac:dyDescent="0.25">
@@ -43977,7 +43977,7 @@
         <v>1454</v>
       </c>
       <c r="T559" t="s">
-        <v>4508</v>
+        <v>4507</v>
       </c>
     </row>
     <row r="560" spans="3:20" x14ac:dyDescent="0.25">
@@ -44015,7 +44015,7 @@
         <v>1455</v>
       </c>
       <c r="T560" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="561" spans="3:20" x14ac:dyDescent="0.25">
@@ -44053,7 +44053,7 @@
         <v>1456</v>
       </c>
       <c r="T561" t="s">
-        <v>4510</v>
+        <v>4509</v>
       </c>
     </row>
     <row r="562" spans="3:20" x14ac:dyDescent="0.25">
@@ -44091,7 +44091,7 @@
         <v>1457</v>
       </c>
       <c r="T562" t="s">
-        <v>4511</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="563" spans="3:20" x14ac:dyDescent="0.25">
@@ -44129,7 +44129,7 @@
         <v>1458</v>
       </c>
       <c r="T563" t="s">
-        <v>4512</v>
+        <v>4511</v>
       </c>
     </row>
     <row r="564" spans="3:20" x14ac:dyDescent="0.25">
@@ -44167,7 +44167,7 @@
         <v>1459</v>
       </c>
       <c r="T564" t="s">
-        <v>4513</v>
+        <v>4512</v>
       </c>
     </row>
     <row r="565" spans="3:20" x14ac:dyDescent="0.25">
@@ -44205,7 +44205,7 @@
         <v>4169</v>
       </c>
       <c r="T565" t="s">
-        <v>4514</v>
+        <v>4513</v>
       </c>
     </row>
     <row r="566" spans="3:20" x14ac:dyDescent="0.25">
@@ -44243,7 +44243,7 @@
         <v>4170</v>
       </c>
       <c r="T566" t="s">
-        <v>4515</v>
+        <v>4514</v>
       </c>
     </row>
     <row r="567" spans="3:20" x14ac:dyDescent="0.25">
@@ -44281,7 +44281,7 @@
         <v>4171</v>
       </c>
       <c r="T567" t="s">
-        <v>4516</v>
+        <v>4515</v>
       </c>
     </row>
     <row r="568" spans="3:20" x14ac:dyDescent="0.25">
@@ -44319,7 +44319,7 @@
         <v>4172</v>
       </c>
       <c r="T568" t="s">
-        <v>4517</v>
+        <v>4516</v>
       </c>
     </row>
     <row r="569" spans="3:20" x14ac:dyDescent="0.25">
@@ -44357,7 +44357,7 @@
         <v>4173</v>
       </c>
       <c r="T569" t="s">
-        <v>4518</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="570" spans="3:20" x14ac:dyDescent="0.25">
@@ -44392,7 +44392,7 @@
         <v>3890</v>
       </c>
       <c r="T570" t="s">
-        <v>4519</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="571" spans="3:20" x14ac:dyDescent="0.25">
@@ -44427,7 +44427,7 @@
         <v>3891</v>
       </c>
       <c r="T571" t="s">
-        <v>4520</v>
+        <v>4519</v>
       </c>
     </row>
     <row r="572" spans="3:20" x14ac:dyDescent="0.25">
@@ -44462,7 +44462,7 @@
         <v>3892</v>
       </c>
       <c r="T572" t="s">
-        <v>4521</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="573" spans="3:20" x14ac:dyDescent="0.25">
@@ -44497,7 +44497,7 @@
         <v>3893</v>
       </c>
       <c r="T573" t="s">
-        <v>4522</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="574" spans="3:20" x14ac:dyDescent="0.25">
@@ -44532,7 +44532,7 @@
         <v>3894</v>
       </c>
       <c r="T574" t="s">
-        <v>4523</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="575" spans="3:20" x14ac:dyDescent="0.25">
@@ -44567,7 +44567,7 @@
         <v>3895</v>
       </c>
       <c r="T575" t="s">
-        <v>4524</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="576" spans="3:20" x14ac:dyDescent="0.25">
@@ -44602,7 +44602,7 @@
         <v>3896</v>
       </c>
       <c r="T576" t="s">
-        <v>4525</v>
+        <v>4524</v>
       </c>
     </row>
     <row r="577" spans="3:20" x14ac:dyDescent="0.25">
@@ -44637,7 +44637,7 @@
         <v>3897</v>
       </c>
       <c r="T577" t="s">
-        <v>4526</v>
+        <v>4525</v>
       </c>
     </row>
     <row r="578" spans="3:20" x14ac:dyDescent="0.25">
@@ -44672,7 +44672,7 @@
         <v>3898</v>
       </c>
       <c r="T578" t="s">
-        <v>4527</v>
+        <v>4526</v>
       </c>
     </row>
     <row r="579" spans="3:20" x14ac:dyDescent="0.25">
@@ -44707,7 +44707,7 @@
         <v>1249</v>
       </c>
       <c r="T579" t="s">
-        <v>4528</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="580" spans="3:20" x14ac:dyDescent="0.25">
@@ -44742,7 +44742,7 @@
         <v>1250</v>
       </c>
       <c r="T580" t="s">
-        <v>4529</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="581" spans="3:20" x14ac:dyDescent="0.25">
@@ -44777,7 +44777,7 @@
         <v>1260</v>
       </c>
       <c r="T581" t="s">
-        <v>4530</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="582" spans="3:20" x14ac:dyDescent="0.25">
@@ -44812,7 +44812,7 @@
         <v>1251</v>
       </c>
       <c r="T582" t="s">
-        <v>4531</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="583" spans="3:20" x14ac:dyDescent="0.25">
@@ -44847,7 +44847,7 @@
         <v>1252</v>
       </c>
       <c r="T583" t="s">
-        <v>4532</v>
+        <v>4531</v>
       </c>
     </row>
     <row r="584" spans="3:20" x14ac:dyDescent="0.25">
@@ -44882,7 +44882,7 @@
         <v>1253</v>
       </c>
       <c r="T584" t="s">
-        <v>4533</v>
+        <v>4532</v>
       </c>
     </row>
     <row r="585" spans="3:20" x14ac:dyDescent="0.25">
@@ -44917,7 +44917,7 @@
         <v>1254</v>
       </c>
       <c r="T585" t="s">
-        <v>4534</v>
+        <v>4533</v>
       </c>
     </row>
     <row r="586" spans="3:20" x14ac:dyDescent="0.25">
@@ -44952,7 +44952,7 @@
         <v>1255</v>
       </c>
       <c r="T586" t="s">
-        <v>4535</v>
+        <v>4534</v>
       </c>
     </row>
     <row r="587" spans="3:20" x14ac:dyDescent="0.25">
@@ -44987,7 +44987,7 @@
         <v>1256</v>
       </c>
       <c r="T587" t="s">
-        <v>4536</v>
+        <v>4535</v>
       </c>
     </row>
     <row r="588" spans="3:20" x14ac:dyDescent="0.25">
@@ -45022,7 +45022,7 @@
         <v>1257</v>
       </c>
       <c r="T588" t="s">
-        <v>4537</v>
+        <v>4536</v>
       </c>
     </row>
     <row r="589" spans="3:20" x14ac:dyDescent="0.25">
@@ -45057,7 +45057,7 @@
         <v>1258</v>
       </c>
       <c r="T589" t="s">
-        <v>4538</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="590" spans="3:20" x14ac:dyDescent="0.25">
@@ -45092,7 +45092,7 @@
         <v>1259</v>
       </c>
       <c r="T590" t="s">
-        <v>4539</v>
+        <v>4538</v>
       </c>
     </row>
     <row r="591" spans="3:20" x14ac:dyDescent="0.25">
@@ -45127,7 +45127,7 @@
         <v>3899</v>
       </c>
       <c r="T591" t="s">
-        <v>4540</v>
+        <v>4539</v>
       </c>
     </row>
     <row r="592" spans="3:20" x14ac:dyDescent="0.25">
@@ -45162,7 +45162,7 @@
         <v>3900</v>
       </c>
       <c r="T592" t="s">
-        <v>4541</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="593" spans="3:20" x14ac:dyDescent="0.25">
@@ -45197,7 +45197,7 @@
         <v>3901</v>
       </c>
       <c r="T593" t="s">
-        <v>4542</v>
+        <v>4541</v>
       </c>
     </row>
     <row r="594" spans="3:20" x14ac:dyDescent="0.25">
@@ -45232,7 +45232,7 @@
         <v>1263</v>
       </c>
       <c r="T594" t="s">
-        <v>4543</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="595" spans="3:20" x14ac:dyDescent="0.25">
@@ -45267,7 +45267,7 @@
         <v>1248</v>
       </c>
       <c r="T595" t="s">
-        <v>4544</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="596" spans="3:20" x14ac:dyDescent="0.25">
@@ -45302,7 +45302,7 @@
         <v>1264</v>
       </c>
       <c r="T596" t="s">
-        <v>4545</v>
+        <v>4544</v>
       </c>
     </row>
     <row r="597" spans="3:20" x14ac:dyDescent="0.25">
@@ -45337,7 +45337,7 @@
         <v>3902</v>
       </c>
       <c r="T597" t="s">
-        <v>4546</v>
+        <v>4545</v>
       </c>
     </row>
     <row r="598" spans="3:20" x14ac:dyDescent="0.25">
@@ -45372,7 +45372,7 @@
         <v>3903</v>
       </c>
       <c r="T598" t="s">
-        <v>4547</v>
+        <v>4546</v>
       </c>
     </row>
     <row r="599" spans="3:20" x14ac:dyDescent="0.25">
@@ -45407,7 +45407,7 @@
         <v>3904</v>
       </c>
       <c r="T599" t="s">
-        <v>4548</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="600" spans="3:20" x14ac:dyDescent="0.25">
@@ -45442,7 +45442,7 @@
         <v>3905</v>
       </c>
       <c r="T600" t="s">
-        <v>4549</v>
+        <v>4548</v>
       </c>
     </row>
     <row r="601" spans="3:20" x14ac:dyDescent="0.25">
@@ -45477,7 +45477,7 @@
         <v>3906</v>
       </c>
       <c r="T601" t="s">
-        <v>4550</v>
+        <v>4549</v>
       </c>
     </row>
     <row r="602" spans="3:20" x14ac:dyDescent="0.25">
@@ -45512,7 +45512,7 @@
         <v>3907</v>
       </c>
       <c r="T602" t="s">
-        <v>4551</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="603" spans="3:20" x14ac:dyDescent="0.25">
@@ -45547,7 +45547,7 @@
         <v>3908</v>
       </c>
       <c r="T603" t="s">
-        <v>4552</v>
+        <v>4551</v>
       </c>
     </row>
     <row r="604" spans="3:20" x14ac:dyDescent="0.25">
@@ -45582,7 +45582,7 @@
         <v>3909</v>
       </c>
       <c r="T604" t="s">
-        <v>4553</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="605" spans="3:20" x14ac:dyDescent="0.25">
@@ -45617,7 +45617,7 @@
         <v>3910</v>
       </c>
       <c r="T605" t="s">
-        <v>4554</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="606" spans="3:20" x14ac:dyDescent="0.25">
@@ -45652,7 +45652,7 @@
         <v>3911</v>
       </c>
       <c r="T606" t="s">
-        <v>4555</v>
+        <v>4554</v>
       </c>
     </row>
     <row r="607" spans="3:20" x14ac:dyDescent="0.25">
@@ -45687,7 +45687,7 @@
         <v>3912</v>
       </c>
       <c r="T607" t="s">
-        <v>4556</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="608" spans="3:20" x14ac:dyDescent="0.25">
@@ -45722,7 +45722,7 @@
         <v>3913</v>
       </c>
       <c r="T608" t="s">
-        <v>4557</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="609" spans="3:20" x14ac:dyDescent="0.25">
@@ -45757,7 +45757,7 @@
         <v>3914</v>
       </c>
       <c r="T609" t="s">
-        <v>4558</v>
+        <v>4557</v>
       </c>
     </row>
     <row r="610" spans="3:20" x14ac:dyDescent="0.25">
@@ -45792,7 +45792,7 @@
         <v>3915</v>
       </c>
       <c r="T610" t="s">
-        <v>4559</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="611" spans="3:20" x14ac:dyDescent="0.25">
@@ -45827,7 +45827,7 @@
         <v>3916</v>
       </c>
       <c r="T611" t="s">
-        <v>4560</v>
+        <v>4559</v>
       </c>
     </row>
     <row r="612" spans="3:20" x14ac:dyDescent="0.25">
@@ -45862,7 +45862,7 @@
         <v>3917</v>
       </c>
       <c r="T612" t="s">
-        <v>4561</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="613" spans="3:20" x14ac:dyDescent="0.25">
@@ -45897,7 +45897,7 @@
         <v>3918</v>
       </c>
       <c r="T613" t="s">
-        <v>4562</v>
+        <v>4561</v>
       </c>
     </row>
     <row r="614" spans="3:20" x14ac:dyDescent="0.25">
@@ -45932,7 +45932,7 @@
         <v>3919</v>
       </c>
       <c r="T614" t="s">
-        <v>4563</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="615" spans="3:20" x14ac:dyDescent="0.25">
@@ -45967,7 +45967,7 @@
         <v>3920</v>
       </c>
       <c r="T615" t="s">
-        <v>4564</v>
+        <v>4563</v>
       </c>
     </row>
     <row r="616" spans="3:20" x14ac:dyDescent="0.25">
@@ -46002,7 +46002,7 @@
         <v>3921</v>
       </c>
       <c r="T616" t="s">
-        <v>4565</v>
+        <v>4564</v>
       </c>
     </row>
     <row r="617" spans="3:20" x14ac:dyDescent="0.25">
@@ -46037,7 +46037,7 @@
         <v>3922</v>
       </c>
       <c r="T617" t="s">
-        <v>4566</v>
+        <v>4565</v>
       </c>
     </row>
     <row r="618" spans="3:20" x14ac:dyDescent="0.25">
@@ -46107,7 +46107,7 @@
         <v>3924</v>
       </c>
       <c r="T619" t="s">
-        <v>4567</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="620" spans="3:20" x14ac:dyDescent="0.25">
@@ -46177,7 +46177,7 @@
         <v>3926</v>
       </c>
       <c r="T621" t="s">
-        <v>4568</v>
+        <v>4567</v>
       </c>
     </row>
     <row r="622" spans="3:20" x14ac:dyDescent="0.25">
@@ -46282,7 +46282,7 @@
         <v>3929</v>
       </c>
       <c r="T624" t="s">
-        <v>4569</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="625" spans="3:20" x14ac:dyDescent="0.25">
@@ -46387,7 +46387,7 @@
         <v>3932</v>
       </c>
       <c r="T627" t="s">
-        <v>4570</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="628" spans="3:20" x14ac:dyDescent="0.25">
@@ -46422,7 +46422,7 @@
         <v>3933</v>
       </c>
       <c r="T628" t="s">
-        <v>4571</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="629" spans="3:20" x14ac:dyDescent="0.25">
@@ -46457,7 +46457,7 @@
         <v>3934</v>
       </c>
       <c r="T629" t="s">
-        <v>4572</v>
+        <v>4571</v>
       </c>
     </row>
     <row r="630" spans="3:20" x14ac:dyDescent="0.25">
@@ -46492,7 +46492,7 @@
         <v>3935</v>
       </c>
       <c r="T630" t="s">
-        <v>4573</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="631" spans="3:20" x14ac:dyDescent="0.25">
@@ -46527,7 +46527,7 @@
         <v>3936</v>
       </c>
       <c r="T631" t="s">
-        <v>4574</v>
+        <v>4573</v>
       </c>
     </row>
     <row r="632" spans="3:20" x14ac:dyDescent="0.25">
@@ -46562,7 +46562,7 @@
         <v>3937</v>
       </c>
       <c r="T632" t="s">
-        <v>4575</v>
+        <v>4574</v>
       </c>
     </row>
     <row r="633" spans="3:20" x14ac:dyDescent="0.25">
@@ -46597,7 +46597,7 @@
         <v>3938</v>
       </c>
       <c r="T633" t="s">
-        <v>4576</v>
+        <v>4575</v>
       </c>
     </row>
     <row r="634" spans="3:20" x14ac:dyDescent="0.25">
@@ -46632,7 +46632,7 @@
         <v>3939</v>
       </c>
       <c r="T634" t="s">
-        <v>4577</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="635" spans="3:20" x14ac:dyDescent="0.25">
@@ -46667,7 +46667,7 @@
         <v>3940</v>
       </c>
       <c r="T635" t="s">
-        <v>4578</v>
+        <v>4577</v>
       </c>
     </row>
     <row r="636" spans="3:20" x14ac:dyDescent="0.25">
@@ -46702,7 +46702,7 @@
         <v>3941</v>
       </c>
       <c r="T636" t="s">
-        <v>4579</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="637" spans="3:20" x14ac:dyDescent="0.25">
@@ -46737,7 +46737,7 @@
         <v>3942</v>
       </c>
       <c r="T637" t="s">
-        <v>4580</v>
+        <v>4579</v>
       </c>
     </row>
     <row r="638" spans="3:20" x14ac:dyDescent="0.25">
@@ -46772,7 +46772,7 @@
         <v>3943</v>
       </c>
       <c r="T638" t="s">
-        <v>4581</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="639" spans="3:20" x14ac:dyDescent="0.25">
@@ -46807,7 +46807,7 @@
         <v>3944</v>
       </c>
       <c r="T639" t="s">
-        <v>4582</v>
+        <v>4581</v>
       </c>
     </row>
     <row r="640" spans="3:20" x14ac:dyDescent="0.25">
@@ -46842,7 +46842,7 @@
         <v>3945</v>
       </c>
       <c r="T640" t="s">
-        <v>4583</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="641" spans="3:20" x14ac:dyDescent="0.25">
@@ -46877,7 +46877,7 @@
         <v>3946</v>
       </c>
       <c r="T641" t="s">
-        <v>4584</v>
+        <v>4583</v>
       </c>
     </row>
     <row r="642" spans="3:20" x14ac:dyDescent="0.25">
@@ -46912,7 +46912,7 @@
         <v>3947</v>
       </c>
       <c r="T642" t="s">
-        <v>4585</v>
+        <v>4584</v>
       </c>
     </row>
     <row r="643" spans="3:20" x14ac:dyDescent="0.25">
@@ -46947,7 +46947,7 @@
         <v>3948</v>
       </c>
       <c r="T643" t="s">
-        <v>4586</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="644" spans="3:20" x14ac:dyDescent="0.25">
@@ -46982,7 +46982,7 @@
         <v>3949</v>
       </c>
       <c r="T644" t="s">
-        <v>4587</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="645" spans="3:20" x14ac:dyDescent="0.25">
@@ -47017,7 +47017,7 @@
         <v>3950</v>
       </c>
       <c r="T645" t="s">
-        <v>4588</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="646" spans="3:20" x14ac:dyDescent="0.25">
@@ -47052,7 +47052,7 @@
         <v>3951</v>
       </c>
       <c r="T646" t="s">
-        <v>4589</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="647" spans="3:20" x14ac:dyDescent="0.25">
@@ -47087,7 +47087,7 @@
         <v>3952</v>
       </c>
       <c r="T647" t="s">
-        <v>4590</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="648" spans="3:20" x14ac:dyDescent="0.25">
@@ -47122,7 +47122,7 @@
         <v>3953</v>
       </c>
       <c r="T648" t="s">
-        <v>4591</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="649" spans="3:20" x14ac:dyDescent="0.25">
@@ -47157,7 +47157,7 @@
         <v>3954</v>
       </c>
       <c r="T649" t="s">
-        <v>4592</v>
+        <v>4591</v>
       </c>
     </row>
     <row r="650" spans="3:20" x14ac:dyDescent="0.25">
@@ -47192,7 +47192,7 @@
         <v>3955</v>
       </c>
       <c r="T650" t="s">
-        <v>4593</v>
+        <v>4592</v>
       </c>
     </row>
     <row r="651" spans="3:20" x14ac:dyDescent="0.25">
@@ -47227,7 +47227,7 @@
         <v>3956</v>
       </c>
       <c r="T651" t="s">
-        <v>4594</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="652" spans="3:20" x14ac:dyDescent="0.25">
@@ -47262,7 +47262,7 @@
         <v>3957</v>
       </c>
       <c r="T652" t="s">
-        <v>4595</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="653" spans="3:20" x14ac:dyDescent="0.25">
@@ -47297,7 +47297,7 @@
         <v>3958</v>
       </c>
       <c r="T653" t="s">
-        <v>4596</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="654" spans="3:20" x14ac:dyDescent="0.25">
@@ -47332,7 +47332,7 @@
         <v>3959</v>
       </c>
       <c r="T654" t="s">
-        <v>4597</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="655" spans="3:20" x14ac:dyDescent="0.25">
@@ -47367,7 +47367,7 @@
         <v>3960</v>
       </c>
       <c r="T655" t="s">
-        <v>4598</v>
+        <v>4597</v>
       </c>
     </row>
     <row r="656" spans="3:20" x14ac:dyDescent="0.25">
@@ -47402,7 +47402,7 @@
         <v>3961</v>
       </c>
       <c r="T656" t="s">
-        <v>4599</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="657" spans="3:20" x14ac:dyDescent="0.25">
@@ -47437,7 +47437,7 @@
         <v>3962</v>
       </c>
       <c r="T657" t="s">
-        <v>4600</v>
+        <v>4599</v>
       </c>
     </row>
     <row r="658" spans="3:20" x14ac:dyDescent="0.25">
@@ -47472,7 +47472,7 @@
         <v>3963</v>
       </c>
       <c r="T658" t="s">
-        <v>4601</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="659" spans="3:20" x14ac:dyDescent="0.25">
@@ -47507,7 +47507,7 @@
         <v>3964</v>
       </c>
       <c r="T659" t="s">
-        <v>4602</v>
+        <v>4601</v>
       </c>
     </row>
     <row r="660" spans="3:20" x14ac:dyDescent="0.25">
@@ -47682,7 +47682,7 @@
         <v>3969</v>
       </c>
       <c r="T664" t="s">
-        <v>4603</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="665" spans="3:20" x14ac:dyDescent="0.25">
@@ -47717,7 +47717,7 @@
         <v>3970</v>
       </c>
       <c r="T665" t="s">
-        <v>4604</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="666" spans="3:20" x14ac:dyDescent="0.25">
@@ -47752,7 +47752,7 @@
         <v>3971</v>
       </c>
       <c r="T666" t="s">
-        <v>4605</v>
+        <v>4604</v>
       </c>
     </row>
     <row r="667" spans="3:20" x14ac:dyDescent="0.25">
@@ -47787,7 +47787,7 @@
         <v>3972</v>
       </c>
       <c r="T667" t="s">
-        <v>4606</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="668" spans="3:20" x14ac:dyDescent="0.25">
@@ -47822,7 +47822,7 @@
         <v>3973</v>
       </c>
       <c r="T668" t="s">
-        <v>4607</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="669" spans="3:20" x14ac:dyDescent="0.25">

--- a/Excel/Allplanttaglist.xlsx
+++ b/Excel/Allplanttaglist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel-Files\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D08D582-07FF-409E-9471-588AFD781940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC843BF-32B0-4593-9536-CF59969B8591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{0DFC0680-056B-49A9-993E-B17935078FFA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12843" uniqueCount="4608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13315" uniqueCount="4609">
   <si>
     <t>omkamal</t>
   </si>
@@ -13858,6 +13858,9 @@
   </si>
   <si>
     <t>acvpl</t>
+  </si>
+  <si>
+    <t>PDIPL</t>
   </si>
 </sst>
 </file>
@@ -14209,7 +14212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7382AB7-75C8-44B4-BF78-34EC17E0275A}">
-  <dimension ref="A1:T1271"/>
+  <dimension ref="A1:U1271"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -14231,9 +14234,10 @@
     <col min="18" max="18" width="26.5703125" customWidth="1"/>
     <col min="19" max="19" width="23" customWidth="1"/>
     <col min="20" max="20" width="15" customWidth="1"/>
+    <col min="21" max="21" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14294,8 +14298,11 @@
       <c r="T1" t="s">
         <v>4607</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U1" t="s">
+        <v>4608</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -14356,8 +14363,11 @@
       <c r="T2" t="s">
         <v>1437</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U2" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -14418,8 +14428,11 @@
       <c r="T3" t="s">
         <v>1436</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U3" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -14480,8 +14493,11 @@
       <c r="T4" t="s">
         <v>1435</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U4" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -14542,8 +14558,11 @@
       <c r="T5" t="s">
         <v>1433</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U5" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -14604,8 +14623,11 @@
       <c r="T6" t="s">
         <v>1429</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U6" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -14666,8 +14688,11 @@
       <c r="T7" t="s">
         <v>1425</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U7" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -14728,8 +14753,11 @@
       <c r="T8" t="s">
         <v>1421</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U8" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -14790,8 +14818,11 @@
       <c r="T9" t="s">
         <v>1420</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U9" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -14852,8 +14883,11 @@
       <c r="T10" t="s">
         <v>1419</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U10" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -14914,8 +14948,11 @@
       <c r="T11" t="s">
         <v>1418</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U11" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -14976,8 +15013,11 @@
       <c r="T12" t="s">
         <v>1417</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U12" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -15038,8 +15078,11 @@
       <c r="T13" t="s">
         <v>4138</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U13" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -15100,8 +15143,11 @@
       <c r="T14" t="s">
         <v>4137</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U14" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -15162,8 +15208,11 @@
       <c r="T15" t="s">
         <v>4136</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U15" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -15224,8 +15273,11 @@
       <c r="T16" t="s">
         <v>4134</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U16" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -15286,8 +15338,11 @@
       <c r="T17" t="s">
         <v>4130</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U17" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -15348,8 +15403,11 @@
       <c r="T18" t="s">
         <v>4126</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U18" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -15410,8 +15468,11 @@
       <c r="T19" t="s">
         <v>4122</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U19" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -15472,8 +15533,11 @@
       <c r="T20" t="s">
         <v>4121</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U20" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -15534,8 +15598,11 @@
       <c r="T21" t="s">
         <v>4120</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U21" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -15596,8 +15663,11 @@
       <c r="T22" t="s">
         <v>4119</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U22" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -15658,8 +15728,11 @@
       <c r="T23" t="s">
         <v>4118</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U23" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -15720,8 +15793,11 @@
       <c r="T24" t="s">
         <v>4106</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U24" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -15782,8 +15858,11 @@
       <c r="T25" t="s">
         <v>4105</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U25" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -15844,8 +15923,11 @@
       <c r="T26" t="s">
         <v>4104</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U26" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -15906,8 +15988,11 @@
       <c r="T27" t="s">
         <v>4102</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U27" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -15968,8 +16053,11 @@
       <c r="T28" t="s">
         <v>4098</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U28" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -16030,8 +16118,11 @@
       <c r="T29" t="s">
         <v>4094</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U29" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -16092,8 +16183,11 @@
       <c r="T30" t="s">
         <v>4090</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U30" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -16154,8 +16248,11 @@
       <c r="T31" t="s">
         <v>4089</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U31" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -16216,8 +16313,11 @@
       <c r="T32" t="s">
         <v>4088</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U32" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -16278,8 +16378,11 @@
       <c r="T33" t="s">
         <v>4087</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U33" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>51</v>
       </c>
@@ -16340,8 +16443,11 @@
       <c r="T34" t="s">
         <v>4086</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U34" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -16402,8 +16508,11 @@
       <c r="T35" t="s">
         <v>1405</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U35" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -16464,8 +16573,11 @@
       <c r="T36" t="s">
         <v>1404</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U36" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -16526,8 +16638,11 @@
       <c r="T37" t="s">
         <v>3349</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U37" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -16588,8 +16703,11 @@
       <c r="T38" t="s">
         <v>1401</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U38" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -16650,8 +16768,11 @@
       <c r="T39" t="s">
         <v>1397</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U39" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -16712,8 +16833,11 @@
       <c r="T40" t="s">
         <v>1393</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U40" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -16774,8 +16898,11 @@
       <c r="T41" t="s">
         <v>1389</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U41" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -16836,8 +16963,11 @@
       <c r="T42" t="s">
         <v>1388</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U42" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -16898,8 +17028,11 @@
       <c r="T43" t="s">
         <v>1387</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U43" t="s">
+        <v>3347</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -16960,8 +17093,11 @@
       <c r="T44" t="s">
         <v>1386</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U44" t="s">
+        <v>3346</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>62</v>
       </c>
@@ -17022,8 +17158,11 @@
       <c r="T45" t="s">
         <v>1385</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U45" t="s">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>63</v>
       </c>
@@ -17084,8 +17223,11 @@
       <c r="T46" t="s">
         <v>1373</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U46" t="s">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>64</v>
       </c>
@@ -17146,8 +17288,11 @@
       <c r="T47" t="s">
         <v>1372</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U47" t="s">
+        <v>3343</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -17208,8 +17353,11 @@
       <c r="T48" t="s">
         <v>4174</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U48" t="s">
+        <v>3342</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -17270,8 +17418,11 @@
       <c r="T49" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U49" t="s">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>67</v>
       </c>
@@ -17332,8 +17483,11 @@
       <c r="T50" t="s">
         <v>1365</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U50" t="s">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>68</v>
       </c>
@@ -17394,8 +17548,11 @@
       <c r="T51" t="s">
         <v>1361</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U51" t="s">
+        <v>3339</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -17456,8 +17613,11 @@
       <c r="T52" t="s">
         <v>1357</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U52" t="s">
+        <v>3338</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>70</v>
       </c>
@@ -17518,8 +17678,11 @@
       <c r="T53" t="s">
         <v>1356</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U53" t="s">
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>71</v>
       </c>
@@ -17580,8 +17743,11 @@
       <c r="T54" t="s">
         <v>1355</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U54" t="s">
+        <v>3336</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -17642,8 +17808,11 @@
       <c r="T55" t="s">
         <v>1354</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U55" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>73</v>
       </c>
@@ -17704,8 +17873,11 @@
       <c r="T56" t="s">
         <v>1353</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U56" t="s">
+        <v>3334</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -17766,8 +17938,11 @@
       <c r="T57" t="s">
         <v>1349</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U57" t="s">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -17828,8 +18003,11 @@
       <c r="T58" t="s">
         <v>2250</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U58" t="s">
+        <v>3332</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>76</v>
       </c>
@@ -17890,8 +18068,11 @@
       <c r="T59" t="s">
         <v>1348</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U59" t="s">
+        <v>3331</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>77</v>
       </c>
@@ -17952,8 +18133,11 @@
       <c r="T60" t="s">
         <v>1332</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U60" t="s">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>78</v>
       </c>
@@ -18014,8 +18198,11 @@
       <c r="T61" t="s">
         <v>1346</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U61" t="s">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>79</v>
       </c>
@@ -18076,8 +18263,11 @@
       <c r="T62" t="s">
         <v>1344</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U62" t="s">
+        <v>3328</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -18138,8 +18328,11 @@
       <c r="T63" t="s">
         <v>1337</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U63" t="s">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>81</v>
       </c>
@@ -18200,8 +18393,11 @@
       <c r="T64" t="s">
         <v>1336</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U64" t="s">
+        <v>3326</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>82</v>
       </c>
@@ -18262,8 +18458,11 @@
       <c r="T65" t="s">
         <v>1345</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U65" t="s">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -18324,8 +18523,11 @@
       <c r="T66" t="s">
         <v>1343</v>
       </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U66" t="s">
+        <v>3324</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>84</v>
       </c>
@@ -18386,8 +18588,11 @@
       <c r="T67" t="s">
         <v>1342</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U67" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>85</v>
       </c>
@@ -18448,8 +18653,11 @@
       <c r="T68" t="s">
         <v>1341</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U68" t="s">
+        <v>3322</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -18510,8 +18718,11 @@
       <c r="T69" t="s">
         <v>1340</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U69" t="s">
+        <v>3321</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>87</v>
       </c>
@@ -18572,8 +18783,11 @@
       <c r="T70" t="s">
         <v>1339</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U70" t="s">
+        <v>3320</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>88</v>
       </c>
@@ -18634,8 +18848,11 @@
       <c r="T71" t="s">
         <v>1338</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U71" t="s">
+        <v>3319</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>89</v>
       </c>
@@ -18696,8 +18913,11 @@
       <c r="T72" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U72" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -18758,8 +18978,11 @@
       <c r="T73" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U73" t="s">
+        <v>3317</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -18820,8 +19043,11 @@
       <c r="T74" t="s">
         <v>1264</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U74" t="s">
+        <v>3316</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -18882,8 +19108,11 @@
       <c r="T75" t="s">
         <v>1248</v>
       </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U75" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>93</v>
       </c>
@@ -18944,8 +19173,11 @@
       <c r="T76" t="s">
         <v>1263</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U76" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -19006,8 +19238,11 @@
       <c r="T77" t="s">
         <v>1247</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U77" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>95</v>
       </c>
@@ -19068,8 +19303,11 @@
       <c r="T78" t="s">
         <v>1261</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U78" t="s">
+        <v>4083</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>96</v>
       </c>
@@ -19130,8 +19368,11 @@
       <c r="T79" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U79" t="s">
+        <v>4082</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>97</v>
       </c>
@@ -19192,8 +19433,11 @@
       <c r="T80" t="s">
         <v>1252</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U80" t="s">
+        <v>4081</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>98</v>
       </c>
@@ -19254,8 +19498,11 @@
       <c r="T81" t="s">
         <v>1251</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U81" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>99</v>
       </c>
@@ -19316,8 +19563,11 @@
       <c r="T82" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U82" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>100</v>
       </c>
@@ -19378,8 +19628,11 @@
       <c r="T83" t="s">
         <v>1258</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U83" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>101</v>
       </c>
@@ -19440,8 +19693,11 @@
       <c r="T84" t="s">
         <v>1257</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U84" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>102</v>
       </c>
@@ -19502,8 +19758,11 @@
       <c r="T85" t="s">
         <v>1256</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U85" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>103</v>
       </c>
@@ -19564,8 +19823,11 @@
       <c r="T86" t="s">
         <v>1255</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U86" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>104</v>
       </c>
@@ -19626,8 +19888,11 @@
       <c r="T87" t="s">
         <v>1254</v>
       </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U87" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>105</v>
       </c>
@@ -19688,8 +19953,11 @@
       <c r="T88" t="s">
         <v>1253</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U88" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>106</v>
       </c>
@@ -19750,8 +20018,11 @@
       <c r="T89" t="s">
         <v>1250</v>
       </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U89" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>107</v>
       </c>
@@ -19812,8 +20083,11 @@
       <c r="T90" t="s">
         <v>1249</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U90" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>108</v>
       </c>
@@ -19874,8 +20148,11 @@
       <c r="T91" t="s">
         <v>1180</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U91" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>109</v>
       </c>
@@ -19936,8 +20213,11 @@
       <c r="T92" t="s">
         <v>1164</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U92" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>110</v>
       </c>
@@ -19998,8 +20278,11 @@
       <c r="T93" t="s">
         <v>1179</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U93" t="s">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>111</v>
       </c>
@@ -20060,8 +20343,11 @@
       <c r="T94" t="s">
         <v>1163</v>
       </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U94" t="s">
+        <v>4079</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>112</v>
       </c>
@@ -20122,8 +20408,11 @@
       <c r="T95" t="s">
         <v>1177</v>
       </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U95" t="s">
+        <v>4078</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>113</v>
       </c>
@@ -20184,8 +20473,11 @@
       <c r="T96" t="s">
         <v>1175</v>
       </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U96" t="s">
+        <v>4077</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>114</v>
       </c>
@@ -20246,8 +20538,11 @@
       <c r="T97" t="s">
         <v>1168</v>
       </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U97" t="s">
+        <v>4076</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>115</v>
       </c>
@@ -20308,8 +20603,11 @@
       <c r="T98" t="s">
         <v>1167</v>
       </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U98" t="s">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>116</v>
       </c>
@@ -20370,8 +20668,11 @@
       <c r="T99" t="s">
         <v>1176</v>
       </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U99" t="s">
+        <v>4074</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>117</v>
       </c>
@@ -20432,8 +20733,11 @@
       <c r="T100" t="s">
         <v>1174</v>
       </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U100" t="s">
+        <v>4073</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>118</v>
       </c>
@@ -20494,8 +20798,11 @@
       <c r="T101" t="s">
         <v>1173</v>
       </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U101" t="s">
+        <v>4072</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>119</v>
       </c>
@@ -20556,8 +20863,11 @@
       <c r="T102" t="s">
         <v>1172</v>
       </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U102" t="s">
+        <v>4071</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>120</v>
       </c>
@@ -20618,8 +20928,11 @@
       <c r="T103" t="s">
         <v>1171</v>
       </c>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U103" t="s">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>121</v>
       </c>
@@ -20680,8 +20993,11 @@
       <c r="T104" t="s">
         <v>1170</v>
       </c>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U104" t="s">
+        <v>4069</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>122</v>
       </c>
@@ -20742,8 +21058,11 @@
       <c r="T105" t="s">
         <v>1169</v>
       </c>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U105" t="s">
+        <v>4068</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>123</v>
       </c>
@@ -20804,8 +21123,11 @@
       <c r="T106" t="s">
         <v>1166</v>
       </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U106" t="s">
+        <v>4067</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>124</v>
       </c>
@@ -20866,8 +21188,11 @@
       <c r="T107" t="s">
         <v>1165</v>
       </c>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U107" t="s">
+        <v>4066</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>125</v>
       </c>
@@ -20928,8 +21253,11 @@
       <c r="T108" t="s">
         <v>1094</v>
       </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U108" t="s">
+        <v>4065</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>126</v>
       </c>
@@ -20990,8 +21318,11 @@
       <c r="T109" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U109" t="s">
+        <v>4064</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>127</v>
       </c>
@@ -21052,8 +21383,11 @@
       <c r="T110" t="s">
         <v>1093</v>
       </c>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U110" t="s">
+        <v>4063</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>128</v>
       </c>
@@ -21114,8 +21448,11 @@
       <c r="T111" t="s">
         <v>1077</v>
       </c>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U111" t="s">
+        <v>4062</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>129</v>
       </c>
@@ -21176,8 +21513,11 @@
       <c r="T112" t="s">
         <v>1091</v>
       </c>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U112" t="s">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>130</v>
       </c>
@@ -21238,8 +21578,11 @@
       <c r="T113" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U113" t="s">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>131</v>
       </c>
@@ -21300,8 +21643,11 @@
       <c r="T114" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U114" t="s">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>132</v>
       </c>
@@ -21362,8 +21708,11 @@
       <c r="T115" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U115" t="s">
+        <v>4058</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>133</v>
       </c>
@@ -21424,8 +21773,11 @@
       <c r="T116" t="s">
         <v>1090</v>
       </c>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U116" t="s">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>134</v>
       </c>
@@ -21486,8 +21838,11 @@
       <c r="T117" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U117" t="s">
+        <v>4056</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>135</v>
       </c>
@@ -21548,8 +21903,11 @@
       <c r="T118" t="s">
         <v>1087</v>
       </c>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U118" t="s">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>136</v>
       </c>
@@ -21610,8 +21968,11 @@
       <c r="T119" t="s">
         <v>1086</v>
       </c>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U119" t="s">
+        <v>4054</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>137</v>
       </c>
@@ -21672,8 +22033,11 @@
       <c r="T120" t="s">
         <v>1085</v>
       </c>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U120" t="s">
+        <v>4053</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>138</v>
       </c>
@@ -21734,8 +22098,11 @@
       <c r="T121" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U121" t="s">
+        <v>4052</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>139</v>
       </c>
@@ -21796,8 +22163,11 @@
       <c r="T122" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U122" t="s">
+        <v>4051</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>140</v>
       </c>
@@ -21858,8 +22228,11 @@
       <c r="T123" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U123" t="s">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>141</v>
       </c>
@@ -21920,8 +22293,11 @@
       <c r="T124" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U124" t="s">
+        <v>4049</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>142</v>
       </c>
@@ -21982,8 +22358,11 @@
       <c r="T125" t="s">
         <v>1009</v>
       </c>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U125" t="s">
+        <v>4048</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>143</v>
       </c>
@@ -22044,8 +22423,11 @@
       <c r="T126" t="s">
         <v>993</v>
       </c>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U126" t="s">
+        <v>4047</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>144</v>
       </c>
@@ -22106,8 +22488,11 @@
       <c r="T127" t="s">
         <v>1008</v>
       </c>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U127" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>145</v>
       </c>
@@ -22168,8 +22553,11 @@
       <c r="T128" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U128" t="s">
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>146</v>
       </c>
@@ -22230,8 +22618,11 @@
       <c r="T129" t="s">
         <v>1006</v>
       </c>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U129" t="s">
+        <v>4044</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>147</v>
       </c>
@@ -22292,8 +22683,11 @@
       <c r="T130" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U130" t="s">
+        <v>4043</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>148</v>
       </c>
@@ -22354,8 +22748,11 @@
       <c r="T131" t="s">
         <v>997</v>
       </c>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U131" t="s">
+        <v>4042</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>149</v>
       </c>
@@ -22416,8 +22813,11 @@
       <c r="T132" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U132" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>150</v>
       </c>
@@ -22478,8 +22878,11 @@
       <c r="T133" t="s">
         <v>1005</v>
       </c>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U133" t="s">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>151</v>
       </c>
@@ -22540,8 +22943,11 @@
       <c r="T134" t="s">
         <v>1003</v>
       </c>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U134" t="s">
+        <v>4039</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>152</v>
       </c>
@@ -22602,8 +23008,11 @@
       <c r="T135" t="s">
         <v>1002</v>
       </c>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U135" t="s">
+        <v>4038</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>153</v>
       </c>
@@ -22661,8 +23070,11 @@
       <c r="T136" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U136" t="s">
+        <v>4037</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>154</v>
       </c>
@@ -22720,8 +23132,11 @@
       <c r="T137" t="s">
         <v>1000</v>
       </c>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U137" t="s">
+        <v>4036</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>155</v>
       </c>
@@ -22779,8 +23194,11 @@
       <c r="T138" t="s">
         <v>999</v>
       </c>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U138" t="s">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>156</v>
       </c>
@@ -22838,8 +23256,11 @@
       <c r="T139" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U139" t="s">
+        <v>4034</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>157</v>
       </c>
@@ -22897,8 +23318,11 @@
       <c r="T140" t="s">
         <v>995</v>
       </c>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U140" t="s">
+        <v>4033</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>158</v>
       </c>
@@ -22956,8 +23380,11 @@
       <c r="T141" t="s">
         <v>994</v>
       </c>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U141" t="s">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -23015,8 +23442,11 @@
       <c r="T142" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U142" t="s">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>160</v>
       </c>
@@ -23074,8 +23504,11 @@
       <c r="T143" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U143" t="s">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>161</v>
       </c>
@@ -23133,8 +23566,11 @@
       <c r="T144" t="s">
         <v>923</v>
       </c>
-    </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U144" t="s">
+        <v>4029</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>162</v>
       </c>
@@ -23192,8 +23628,11 @@
       <c r="T145" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U145" t="s">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -23251,8 +23690,11 @@
       <c r="T146" t="s">
         <v>921</v>
       </c>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U146" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>164</v>
       </c>
@@ -23310,8 +23752,11 @@
       <c r="T147" t="s">
         <v>919</v>
       </c>
-    </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U147" t="s">
+        <v>4026</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>165</v>
       </c>
@@ -23369,8 +23814,11 @@
       <c r="T148" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U148" t="s">
+        <v>4025</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>166</v>
       </c>
@@ -23428,8 +23876,11 @@
       <c r="T149" t="s">
         <v>911</v>
       </c>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U149" t="s">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>167</v>
       </c>
@@ -23487,8 +23938,11 @@
       <c r="T150" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U150" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>168</v>
       </c>
@@ -23546,8 +24000,11 @@
       <c r="T151" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U151" t="s">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>169</v>
       </c>
@@ -23605,8 +24062,11 @@
       <c r="T152" t="s">
         <v>917</v>
       </c>
-    </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U152" t="s">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>170</v>
       </c>
@@ -23664,8 +24124,11 @@
       <c r="T153" t="s">
         <v>916</v>
       </c>
-    </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U153" t="s">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>171</v>
       </c>
@@ -23723,8 +24186,11 @@
       <c r="T154" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U154" t="s">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>172</v>
       </c>
@@ -23782,8 +24248,11 @@
       <c r="T155" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U155" t="s">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>173</v>
       </c>
@@ -23841,8 +24310,11 @@
       <c r="T156" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U156" t="s">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>174</v>
       </c>
@@ -23900,8 +24372,11 @@
       <c r="T157" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U157" t="s">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>175</v>
       </c>
@@ -23959,8 +24434,11 @@
       <c r="T158" t="s">
         <v>909</v>
       </c>
-    </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U158" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>176</v>
       </c>
@@ -24018,8 +24496,11 @@
       <c r="T159" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U159" t="s">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>177</v>
       </c>
@@ -24077,8 +24558,11 @@
       <c r="T160" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U160" t="s">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>178</v>
       </c>
@@ -24136,8 +24620,11 @@
       <c r="T161" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U161" t="s">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>179</v>
       </c>
@@ -24195,8 +24682,11 @@
       <c r="T162" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U162" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>180</v>
       </c>
@@ -24254,8 +24744,11 @@
       <c r="T163" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U163" t="s">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>181</v>
       </c>
@@ -24313,8 +24806,11 @@
       <c r="T164" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U164" t="s">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>182</v>
       </c>
@@ -24372,8 +24868,11 @@
       <c r="T165" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U165" t="s">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>183</v>
       </c>
@@ -24431,8 +24930,11 @@
       <c r="T166" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U166" t="s">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>184</v>
       </c>
@@ -24490,8 +24992,11 @@
       <c r="T167" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U167" t="s">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>185</v>
       </c>
@@ -24549,8 +25054,11 @@
       <c r="T168" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U168" t="s">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>186</v>
       </c>
@@ -24608,8 +25116,11 @@
       <c r="T169" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U169" t="s">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>187</v>
       </c>
@@ -24667,8 +25178,11 @@
       <c r="T170" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U170" t="s">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>188</v>
       </c>
@@ -24726,8 +25240,11 @@
       <c r="T171" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U171" t="s">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>189</v>
       </c>
@@ -24785,8 +25302,11 @@
       <c r="T172" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U172" t="s">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>190</v>
       </c>
@@ -24844,8 +25364,11 @@
       <c r="T173" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U173" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>191</v>
       </c>
@@ -24903,8 +25426,11 @@
       <c r="T174" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U174" t="s">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>192</v>
       </c>
@@ -24962,8 +25488,11 @@
       <c r="T175" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U175" t="s">
+        <v>3998</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>193</v>
       </c>
@@ -25021,8 +25550,11 @@
       <c r="T176" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U176" t="s">
+        <v>3997</v>
+      </c>
+    </row>
+    <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>194</v>
       </c>
@@ -25080,8 +25612,11 @@
       <c r="T177" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U177" t="s">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>195</v>
       </c>
@@ -25139,8 +25674,11 @@
       <c r="T178" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U178" t="s">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>196</v>
       </c>
@@ -25198,8 +25736,11 @@
       <c r="T179" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U179" t="s">
+        <v>3994</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>197</v>
       </c>
@@ -25257,8 +25798,11 @@
       <c r="T180" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U180" t="s">
+        <v>3993</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>198</v>
       </c>
@@ -25316,8 +25860,11 @@
       <c r="T181" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U181" t="s">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>199</v>
       </c>
@@ -25375,8 +25922,11 @@
       <c r="T182" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U182" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>200</v>
       </c>
@@ -25434,8 +25984,11 @@
       <c r="T183" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U183" t="s">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>201</v>
       </c>
@@ -25493,8 +26046,11 @@
       <c r="T184" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U184" t="s">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>202</v>
       </c>
@@ -25552,8 +26108,11 @@
       <c r="T185" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U185" t="s">
+        <v>3988</v>
+      </c>
+    </row>
+    <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>203</v>
       </c>
@@ -25611,8 +26170,11 @@
       <c r="T186" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U186" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>204</v>
       </c>
@@ -25670,8 +26232,11 @@
       <c r="T187" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U187" t="s">
+        <v>3986</v>
+      </c>
+    </row>
+    <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>205</v>
       </c>
@@ -25729,8 +26294,11 @@
       <c r="T188" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U188" t="s">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>206</v>
       </c>
@@ -25788,8 +26356,11 @@
       <c r="T189" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U189" t="s">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>207</v>
       </c>
@@ -25847,8 +26418,11 @@
       <c r="T190" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U190" t="s">
+        <v>3983</v>
+      </c>
+    </row>
+    <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>208</v>
       </c>
@@ -25906,8 +26480,11 @@
       <c r="T191" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U191" t="s">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>209</v>
       </c>
@@ -25965,8 +26542,11 @@
       <c r="T192" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U192" t="s">
+        <v>3981</v>
+      </c>
+    </row>
+    <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>210</v>
       </c>
@@ -26024,8 +26604,11 @@
       <c r="T193" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U193" t="s">
+        <v>3980</v>
+      </c>
+    </row>
+    <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>211</v>
       </c>
@@ -26083,8 +26666,11 @@
       <c r="T194" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U194" t="s">
+        <v>3979</v>
+      </c>
+    </row>
+    <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>212</v>
       </c>
@@ -26142,8 +26728,11 @@
       <c r="T195" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U195" t="s">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>213</v>
       </c>
@@ -26201,8 +26790,11 @@
       <c r="T196" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U196" t="s">
+        <v>3977</v>
+      </c>
+    </row>
+    <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>214</v>
       </c>
@@ -26260,8 +26852,11 @@
       <c r="T197" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U197" t="s">
+        <v>3976</v>
+      </c>
+    </row>
+    <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>215</v>
       </c>
@@ -26319,8 +26914,11 @@
       <c r="T198" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U198" t="s">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>216</v>
       </c>
@@ -26378,8 +26976,11 @@
       <c r="T199" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U199" t="s">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>217</v>
       </c>
@@ -26437,8 +27038,11 @@
       <c r="T200" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U200" t="s">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>218</v>
       </c>
@@ -26493,8 +27097,11 @@
       <c r="T201" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U201" t="s">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>219</v>
       </c>
@@ -26549,8 +27156,11 @@
       <c r="T202" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U202" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>220</v>
       </c>
@@ -26605,8 +27215,11 @@
       <c r="T203" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U203" t="s">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>221</v>
       </c>
@@ -26661,8 +27274,11 @@
       <c r="T204" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U204" t="s">
+        <v>3969</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>222</v>
       </c>
@@ -26717,8 +27333,11 @@
       <c r="T205" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U205" t="s">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>223</v>
       </c>
@@ -26773,8 +27392,11 @@
       <c r="T206" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U206" t="s">
+        <v>3967</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>224</v>
       </c>
@@ -26829,8 +27451,11 @@
       <c r="T207" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U207" t="s">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>225</v>
       </c>
@@ -26885,8 +27510,11 @@
       <c r="T208" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U208" t="s">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>226</v>
       </c>
@@ -26941,8 +27569,11 @@
       <c r="T209" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U209" t="s">
+        <v>3964</v>
+      </c>
+    </row>
+    <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>227</v>
       </c>
@@ -26997,8 +27628,11 @@
       <c r="T210" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U210" t="s">
+        <v>3963</v>
+      </c>
+    </row>
+    <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>228</v>
       </c>
@@ -27053,8 +27687,11 @@
       <c r="T211" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U211" t="s">
+        <v>3962</v>
+      </c>
+    </row>
+    <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>229</v>
       </c>
@@ -27109,8 +27746,11 @@
       <c r="T212" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U212" t="s">
+        <v>3961</v>
+      </c>
+    </row>
+    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>230</v>
       </c>
@@ -27165,8 +27805,11 @@
       <c r="T213" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U213" t="s">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>231</v>
       </c>
@@ -27221,8 +27864,11 @@
       <c r="T214" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U214" t="s">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>232</v>
       </c>
@@ -27277,8 +27923,11 @@
       <c r="T215" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U215" t="s">
+        <v>3958</v>
+      </c>
+    </row>
+    <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>233</v>
       </c>
@@ -27333,8 +27982,11 @@
       <c r="T216" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U216" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>234</v>
       </c>
@@ -27389,8 +28041,11 @@
       <c r="T217" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U217" t="s">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>235</v>
       </c>
@@ -27445,8 +28100,11 @@
       <c r="T218" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U218" t="s">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>236</v>
       </c>
@@ -27501,8 +28159,11 @@
       <c r="T219" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U219" t="s">
+        <v>3954</v>
+      </c>
+    </row>
+    <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>237</v>
       </c>
@@ -27557,8 +28218,11 @@
       <c r="T220" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U220" t="s">
+        <v>3953</v>
+      </c>
+    </row>
+    <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>238</v>
       </c>
@@ -27613,8 +28277,11 @@
       <c r="T221" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U221" t="s">
+        <v>3952</v>
+      </c>
+    </row>
+    <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>239</v>
       </c>
@@ -27669,8 +28336,11 @@
       <c r="T222" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U222" t="s">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>240</v>
       </c>
@@ -27725,8 +28395,11 @@
       <c r="T223" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U223" t="s">
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>241</v>
       </c>
@@ -27781,8 +28454,11 @@
       <c r="T224" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U224" t="s">
+        <v>3949</v>
+      </c>
+    </row>
+    <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>242</v>
       </c>
@@ -27837,8 +28513,11 @@
       <c r="T225" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U225" t="s">
+        <v>3948</v>
+      </c>
+    </row>
+    <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>243</v>
       </c>
@@ -27893,8 +28572,11 @@
       <c r="T226" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U226" t="s">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>244</v>
       </c>
@@ -27949,8 +28631,11 @@
       <c r="T227" t="s">
         <v>4175</v>
       </c>
-    </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U227" t="s">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>245</v>
       </c>
@@ -28005,8 +28690,11 @@
       <c r="T228" t="s">
         <v>4176</v>
       </c>
-    </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U228" t="s">
+        <v>3945</v>
+      </c>
+    </row>
+    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>246</v>
       </c>
@@ -28061,8 +28749,11 @@
       <c r="T229" t="s">
         <v>4177</v>
       </c>
-    </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U229" t="s">
+        <v>3944</v>
+      </c>
+    </row>
+    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>247</v>
       </c>
@@ -28117,8 +28808,11 @@
       <c r="T230" t="s">
         <v>4178</v>
       </c>
-    </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U230" t="s">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>248</v>
       </c>
@@ -28173,8 +28867,11 @@
       <c r="T231" t="s">
         <v>4179</v>
       </c>
-    </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U231" t="s">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>249</v>
       </c>
@@ -28229,8 +28926,11 @@
       <c r="T232" t="s">
         <v>4180</v>
       </c>
-    </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U232" t="s">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>250</v>
       </c>
@@ -28285,8 +28985,11 @@
       <c r="T233" t="s">
         <v>4181</v>
       </c>
-    </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U233" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>251</v>
       </c>
@@ -28341,8 +29044,11 @@
       <c r="T234" t="s">
         <v>4182</v>
       </c>
-    </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U234" t="s">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>252</v>
       </c>
@@ -28397,8 +29103,11 @@
       <c r="T235" t="s">
         <v>4183</v>
       </c>
-    </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U235" t="s">
+        <v>3938</v>
+      </c>
+    </row>
+    <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>253</v>
       </c>
@@ -28453,8 +29162,11 @@
       <c r="T236" t="s">
         <v>4184</v>
       </c>
-    </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U236" t="s">
+        <v>3937</v>
+      </c>
+    </row>
+    <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>254</v>
       </c>
@@ -28509,8 +29221,11 @@
       <c r="T237" t="s">
         <v>4185</v>
       </c>
-    </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U237" t="s">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>255</v>
       </c>
@@ -28565,8 +29280,11 @@
       <c r="T238" t="s">
         <v>4186</v>
       </c>
-    </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U238" t="s">
+        <v>3935</v>
+      </c>
+    </row>
+    <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>256</v>
       </c>
@@ -28621,8 +29339,11 @@
       <c r="T239" t="s">
         <v>4187</v>
       </c>
-    </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U239" t="s">
+        <v>3934</v>
+      </c>
+    </row>
+    <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>257</v>
       </c>
@@ -28677,8 +29398,11 @@
       <c r="T240" t="s">
         <v>4188</v>
       </c>
-    </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U240" t="s">
+        <v>3933</v>
+      </c>
+    </row>
+    <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>258</v>
       </c>
@@ -28733,8 +29457,11 @@
       <c r="T241" t="s">
         <v>4189</v>
       </c>
-    </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U241" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>259</v>
       </c>
@@ -28789,8 +29516,11 @@
       <c r="T242" t="s">
         <v>4190</v>
       </c>
-    </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U242" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>260</v>
       </c>
@@ -28845,8 +29575,11 @@
       <c r="T243" t="s">
         <v>4191</v>
       </c>
-    </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U243" t="s">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>261</v>
       </c>
@@ -28901,8 +29634,11 @@
       <c r="T244" t="s">
         <v>4192</v>
       </c>
-    </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U244" t="s">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>262</v>
       </c>
@@ -28957,8 +29693,11 @@
       <c r="T245" t="s">
         <v>4193</v>
       </c>
-    </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U245" t="s">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>263</v>
       </c>
@@ -29013,8 +29752,11 @@
       <c r="T246" t="s">
         <v>4194</v>
       </c>
-    </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U246" t="s">
+        <v>3927</v>
+      </c>
+    </row>
+    <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>264</v>
       </c>
@@ -29069,8 +29811,11 @@
       <c r="T247" t="s">
         <v>4195</v>
       </c>
-    </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U247" t="s">
+        <v>3926</v>
+      </c>
+    </row>
+    <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>265</v>
       </c>
@@ -29125,8 +29870,11 @@
       <c r="T248" t="s">
         <v>4196</v>
       </c>
-    </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U248" t="s">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>266</v>
       </c>
@@ -29181,8 +29929,11 @@
       <c r="T249" t="s">
         <v>4197</v>
       </c>
-    </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U249" t="s">
+        <v>3924</v>
+      </c>
+    </row>
+    <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>267</v>
       </c>
@@ -29237,8 +29988,11 @@
       <c r="T250" t="s">
         <v>4198</v>
       </c>
-    </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U250" t="s">
+        <v>3923</v>
+      </c>
+    </row>
+    <row r="251" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>268</v>
       </c>
@@ -29293,8 +30047,11 @@
       <c r="T251" t="s">
         <v>4199</v>
       </c>
-    </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U251" t="s">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>269</v>
       </c>
@@ -29349,8 +30106,11 @@
       <c r="T252" t="s">
         <v>4200</v>
       </c>
-    </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U252" t="s">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="253" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>270</v>
       </c>
@@ -29405,8 +30165,11 @@
       <c r="T253" t="s">
         <v>4201</v>
       </c>
-    </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U253" t="s">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>271</v>
       </c>
@@ -29461,8 +30224,11 @@
       <c r="T254" t="s">
         <v>4202</v>
       </c>
-    </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U254" t="s">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>271</v>
       </c>
@@ -29517,8 +30283,11 @@
       <c r="T255" t="s">
         <v>4203</v>
       </c>
-    </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U255" t="s">
+        <v>3918</v>
+      </c>
+    </row>
+    <row r="256" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>272</v>
       </c>
@@ -29573,8 +30342,11 @@
       <c r="T256" t="s">
         <v>4204</v>
       </c>
-    </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U256" t="s">
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>272</v>
       </c>
@@ -29629,8 +30401,11 @@
       <c r="T257" t="s">
         <v>4205</v>
       </c>
-    </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U257" t="s">
+        <v>3916</v>
+      </c>
+    </row>
+    <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>273</v>
       </c>
@@ -29685,8 +30460,11 @@
       <c r="T258" t="s">
         <v>4206</v>
       </c>
-    </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U258" t="s">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>274</v>
       </c>
@@ -29741,8 +30519,11 @@
       <c r="T259" t="s">
         <v>4207</v>
       </c>
-    </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U259" t="s">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>275</v>
       </c>
@@ -29797,8 +30578,11 @@
       <c r="T260" t="s">
         <v>4208</v>
       </c>
-    </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U260" t="s">
+        <v>3913</v>
+      </c>
+    </row>
+    <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>276</v>
       </c>
@@ -29853,8 +30637,11 @@
       <c r="T261" t="s">
         <v>4209</v>
       </c>
-    </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U261" t="s">
+        <v>3912</v>
+      </c>
+    </row>
+    <row r="262" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>277</v>
       </c>
@@ -29909,8 +30696,11 @@
       <c r="T262" t="s">
         <v>4210</v>
       </c>
-    </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U262" t="s">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>278</v>
       </c>
@@ -29965,8 +30755,11 @@
       <c r="T263" t="s">
         <v>4211</v>
       </c>
-    </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U263" t="s">
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>279</v>
       </c>
@@ -30021,8 +30814,11 @@
       <c r="T264" t="s">
         <v>4212</v>
       </c>
-    </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U264" t="s">
+        <v>3909</v>
+      </c>
+    </row>
+    <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>280</v>
       </c>
@@ -30077,8 +30873,11 @@
       <c r="T265" t="s">
         <v>4213</v>
       </c>
-    </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U265" t="s">
+        <v>3908</v>
+      </c>
+    </row>
+    <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>281</v>
       </c>
@@ -30133,8 +30932,11 @@
       <c r="T266" t="s">
         <v>4214</v>
       </c>
-    </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U266" t="s">
+        <v>3907</v>
+      </c>
+    </row>
+    <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>282</v>
       </c>
@@ -30189,8 +30991,11 @@
       <c r="T267" t="s">
         <v>4215</v>
       </c>
-    </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U267" t="s">
+        <v>3906</v>
+      </c>
+    </row>
+    <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>283</v>
       </c>
@@ -30245,8 +31050,11 @@
       <c r="T268" t="s">
         <v>4216</v>
       </c>
-    </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U268" t="s">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>284</v>
       </c>
@@ -30301,8 +31109,11 @@
       <c r="T269" t="s">
         <v>4217</v>
       </c>
-    </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U269" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>285</v>
       </c>
@@ -30357,8 +31168,11 @@
       <c r="T270" t="s">
         <v>4218</v>
       </c>
-    </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U270" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>286</v>
       </c>
@@ -30413,8 +31227,11 @@
       <c r="T271" t="s">
         <v>4219</v>
       </c>
-    </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U271" t="s">
+        <v>3902</v>
+      </c>
+    </row>
+    <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>287</v>
       </c>
@@ -30469,8 +31286,11 @@
       <c r="T272" t="s">
         <v>4220</v>
       </c>
-    </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U272" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>288</v>
       </c>
@@ -30525,8 +31345,11 @@
       <c r="T273" t="s">
         <v>4221</v>
       </c>
-    </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U273" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>289</v>
       </c>
@@ -30581,8 +31404,11 @@
       <c r="T274" t="s">
         <v>4222</v>
       </c>
-    </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U274" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>290</v>
       </c>
@@ -30637,8 +31463,11 @@
       <c r="T275" t="s">
         <v>4223</v>
       </c>
-    </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U275" t="s">
+        <v>3901</v>
+      </c>
+    </row>
+    <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>291</v>
       </c>
@@ -30693,8 +31522,11 @@
       <c r="T276" t="s">
         <v>4224</v>
       </c>
-    </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U276" t="s">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>292</v>
       </c>
@@ -30749,8 +31581,11 @@
       <c r="T277" t="s">
         <v>4225</v>
       </c>
-    </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U277" t="s">
+        <v>3899</v>
+      </c>
+    </row>
+    <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>293</v>
       </c>
@@ -30805,8 +31640,11 @@
       <c r="T278" t="s">
         <v>4226</v>
       </c>
-    </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U278" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>294</v>
       </c>
@@ -30861,8 +31699,11 @@
       <c r="T279" t="s">
         <v>4227</v>
       </c>
-    </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U279" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>295</v>
       </c>
@@ -30917,8 +31758,11 @@
       <c r="T280" t="s">
         <v>4228</v>
       </c>
-    </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U280" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>296</v>
       </c>
@@ -30973,8 +31817,11 @@
       <c r="T281" t="s">
         <v>4229</v>
       </c>
-    </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U281" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>297</v>
       </c>
@@ -31029,8 +31876,11 @@
       <c r="T282" t="s">
         <v>4230</v>
       </c>
-    </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U282" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>298</v>
       </c>
@@ -31085,8 +31935,11 @@
       <c r="T283" t="s">
         <v>4231</v>
       </c>
-    </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U283" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>299</v>
       </c>
@@ -31138,8 +31991,11 @@
       <c r="T284" t="s">
         <v>4232</v>
       </c>
-    </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U284" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="285" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>300</v>
       </c>
@@ -31191,8 +32047,11 @@
       <c r="T285" t="s">
         <v>4233</v>
       </c>
-    </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U285" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="286" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>301</v>
       </c>
@@ -31244,8 +32103,11 @@
       <c r="T286" t="s">
         <v>4234</v>
       </c>
-    </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U286" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="287" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>302</v>
       </c>
@@ -31297,8 +32159,11 @@
       <c r="T287" t="s">
         <v>4235</v>
       </c>
-    </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U287" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="288" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>302</v>
       </c>
@@ -31350,8 +32215,11 @@
       <c r="T288" t="s">
         <v>4236</v>
       </c>
-    </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U288" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="289" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>303</v>
       </c>
@@ -31403,8 +32271,11 @@
       <c r="T289" t="s">
         <v>4237</v>
       </c>
-    </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U289" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="290" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>303</v>
       </c>
@@ -31456,8 +32327,11 @@
       <c r="T290" t="s">
         <v>4238</v>
       </c>
-    </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U290" t="s">
+        <v>3898</v>
+      </c>
+    </row>
+    <row r="291" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>304</v>
       </c>
@@ -31509,8 +32383,11 @@
       <c r="T291" t="s">
         <v>4239</v>
       </c>
-    </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U291" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="292" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>305</v>
       </c>
@@ -31562,8 +32439,11 @@
       <c r="T292" t="s">
         <v>4240</v>
       </c>
-    </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U292" t="s">
+        <v>3896</v>
+      </c>
+    </row>
+    <row r="293" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>306</v>
       </c>
@@ -31615,8 +32495,11 @@
       <c r="T293" t="s">
         <v>4241</v>
       </c>
-    </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U293" t="s">
+        <v>3895</v>
+      </c>
+    </row>
+    <row r="294" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>307</v>
       </c>
@@ -31668,8 +32551,11 @@
       <c r="T294" t="s">
         <v>4242</v>
       </c>
-    </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U294" t="s">
+        <v>3894</v>
+      </c>
+    </row>
+    <row r="295" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>308</v>
       </c>
@@ -31721,8 +32607,11 @@
       <c r="T295" t="s">
         <v>4243</v>
       </c>
-    </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U295" t="s">
+        <v>3893</v>
+      </c>
+    </row>
+    <row r="296" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>309</v>
       </c>
@@ -31774,8 +32663,11 @@
       <c r="T296" t="s">
         <v>4244</v>
       </c>
-    </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U296" t="s">
+        <v>3892</v>
+      </c>
+    </row>
+    <row r="297" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>310</v>
       </c>
@@ -31827,8 +32719,11 @@
       <c r="T297" t="s">
         <v>4245</v>
       </c>
-    </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U297" t="s">
+        <v>3891</v>
+      </c>
+    </row>
+    <row r="298" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>311</v>
       </c>
@@ -31880,8 +32775,11 @@
       <c r="T298" t="s">
         <v>4246</v>
       </c>
-    </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U298" t="s">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="299" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>312</v>
       </c>
@@ -31933,8 +32831,11 @@
       <c r="T299" t="s">
         <v>4247</v>
       </c>
-    </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U299" t="s">
+        <v>3889</v>
+      </c>
+    </row>
+    <row r="300" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>313</v>
       </c>
@@ -31986,8 +32887,11 @@
       <c r="T300" t="s">
         <v>4248</v>
       </c>
-    </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U300" t="s">
+        <v>3888</v>
+      </c>
+    </row>
+    <row r="301" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>314</v>
       </c>
@@ -32039,8 +32943,11 @@
       <c r="T301" t="s">
         <v>4249</v>
       </c>
-    </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U301" t="s">
+        <v>3887</v>
+      </c>
+    </row>
+    <row r="302" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>315</v>
       </c>
@@ -32092,8 +32999,11 @@
       <c r="T302" t="s">
         <v>4250</v>
       </c>
-    </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U302" t="s">
+        <v>3886</v>
+      </c>
+    </row>
+    <row r="303" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>316</v>
       </c>
@@ -32145,8 +33055,11 @@
       <c r="T303" t="s">
         <v>4251</v>
       </c>
-    </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U303" t="s">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="304" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>317</v>
       </c>
@@ -32198,8 +33111,11 @@
       <c r="T304" t="s">
         <v>4252</v>
       </c>
-    </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U304" t="s">
+        <v>3884</v>
+      </c>
+    </row>
+    <row r="305" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>318</v>
       </c>
@@ -32251,8 +33167,11 @@
       <c r="T305" t="s">
         <v>4253</v>
       </c>
-    </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U305" t="s">
+        <v>3883</v>
+      </c>
+    </row>
+    <row r="306" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>319</v>
       </c>
@@ -32304,8 +33223,11 @@
       <c r="T306" t="s">
         <v>4254</v>
       </c>
-    </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U306" t="s">
+        <v>3882</v>
+      </c>
+    </row>
+    <row r="307" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>320</v>
       </c>
@@ -32357,8 +33279,11 @@
       <c r="T307" t="s">
         <v>4255</v>
       </c>
-    </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U307" t="s">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="308" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>321</v>
       </c>
@@ -32410,8 +33335,11 @@
       <c r="T308" t="s">
         <v>4256</v>
       </c>
-    </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U308" t="s">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="309" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>322</v>
       </c>
@@ -32463,8 +33391,11 @@
       <c r="T309" t="s">
         <v>4257</v>
       </c>
-    </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U309" t="s">
+        <v>3879</v>
+      </c>
+    </row>
+    <row r="310" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>323</v>
       </c>
@@ -32516,8 +33447,11 @@
       <c r="T310" t="s">
         <v>4258</v>
       </c>
-    </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U310" t="s">
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="311" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>324</v>
       </c>
@@ -32569,8 +33503,11 @@
       <c r="T311" t="s">
         <v>4259</v>
       </c>
-    </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U311" t="s">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="312" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>325</v>
       </c>
@@ -32622,8 +33559,11 @@
       <c r="T312" t="s">
         <v>4260</v>
       </c>
-    </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U312" t="s">
+        <v>3876</v>
+      </c>
+    </row>
+    <row r="313" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>326</v>
       </c>
@@ -32675,8 +33615,11 @@
       <c r="T313" t="s">
         <v>4261</v>
       </c>
-    </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U313" t="s">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="314" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>327</v>
       </c>
@@ -32728,8 +33671,11 @@
       <c r="T314" t="s">
         <v>4262</v>
       </c>
-    </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U314" t="s">
+        <v>3874</v>
+      </c>
+    </row>
+    <row r="315" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>328</v>
       </c>
@@ -32781,8 +33727,11 @@
       <c r="T315" t="s">
         <v>4263</v>
       </c>
-    </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U315" t="s">
+        <v>3873</v>
+      </c>
+    </row>
+    <row r="316" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>329</v>
       </c>
@@ -32834,8 +33783,11 @@
       <c r="T316" t="s">
         <v>4264</v>
       </c>
-    </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U316" t="s">
+        <v>3872</v>
+      </c>
+    </row>
+    <row r="317" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>330</v>
       </c>
@@ -32887,8 +33839,11 @@
       <c r="T317" t="s">
         <v>4265</v>
       </c>
-    </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U317" t="s">
+        <v>3871</v>
+      </c>
+    </row>
+    <row r="318" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>331</v>
       </c>
@@ -32940,8 +33895,11 @@
       <c r="T318" t="s">
         <v>4266</v>
       </c>
-    </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U318" t="s">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="319" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>332</v>
       </c>
@@ -32993,8 +33951,11 @@
       <c r="T319" t="s">
         <v>4267</v>
       </c>
-    </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U319" t="s">
+        <v>3869</v>
+      </c>
+    </row>
+    <row r="320" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>333</v>
       </c>
@@ -33046,8 +34007,11 @@
       <c r="T320" t="s">
         <v>4268</v>
       </c>
-    </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U320" t="s">
+        <v>3868</v>
+      </c>
+    </row>
+    <row r="321" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>334</v>
       </c>
@@ -33099,8 +34063,11 @@
       <c r="T321" t="s">
         <v>4269</v>
       </c>
-    </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U321" t="s">
+        <v>3867</v>
+      </c>
+    </row>
+    <row r="322" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>335</v>
       </c>
@@ -33152,8 +34119,11 @@
       <c r="T322" t="s">
         <v>4270</v>
       </c>
-    </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U322" t="s">
+        <v>3866</v>
+      </c>
+    </row>
+    <row r="323" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>336</v>
       </c>
@@ -33205,8 +34175,11 @@
       <c r="T323" t="s">
         <v>4271</v>
       </c>
-    </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U323" t="s">
+        <v>3865</v>
+      </c>
+    </row>
+    <row r="324" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>337</v>
       </c>
@@ -33258,8 +34231,11 @@
       <c r="T324" t="s">
         <v>4272</v>
       </c>
-    </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U324" t="s">
+        <v>3864</v>
+      </c>
+    </row>
+    <row r="325" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>338</v>
       </c>
@@ -33311,8 +34287,11 @@
       <c r="T325" t="s">
         <v>4273</v>
       </c>
-    </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U325" t="s">
+        <v>3863</v>
+      </c>
+    </row>
+    <row r="326" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>339</v>
       </c>
@@ -33364,8 +34343,11 @@
       <c r="T326" t="s">
         <v>4274</v>
       </c>
-    </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U326" t="s">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="327" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>340</v>
       </c>
@@ -33417,8 +34399,11 @@
       <c r="T327" t="s">
         <v>4275</v>
       </c>
-    </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U327" t="s">
+        <v>3861</v>
+      </c>
+    </row>
+    <row r="328" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>341</v>
       </c>
@@ -33470,8 +34455,11 @@
       <c r="T328" t="s">
         <v>4276</v>
       </c>
-    </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U328" t="s">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="329" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>342</v>
       </c>
@@ -33523,8 +34511,11 @@
       <c r="T329" t="s">
         <v>4277</v>
       </c>
-    </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U329" t="s">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="330" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>343</v>
       </c>
@@ -33576,8 +34567,11 @@
       <c r="T330" t="s">
         <v>4278</v>
       </c>
-    </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U330" t="s">
+        <v>3858</v>
+      </c>
+    </row>
+    <row r="331" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>344</v>
       </c>
@@ -33629,8 +34623,11 @@
       <c r="T331" t="s">
         <v>4279</v>
       </c>
-    </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U331" t="s">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="332" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>345</v>
       </c>
@@ -33682,8 +34679,11 @@
       <c r="T332" t="s">
         <v>4280</v>
       </c>
-    </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U332" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="333" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C333" t="s">
         <v>831</v>
       </c>
@@ -33732,8 +34732,11 @@
       <c r="T333" t="s">
         <v>4281</v>
       </c>
-    </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U333" t="s">
+        <v>3855</v>
+      </c>
+    </row>
+    <row r="334" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C334" t="s">
         <v>832</v>
       </c>
@@ -33782,8 +34785,11 @@
       <c r="T334" t="s">
         <v>4282</v>
       </c>
-    </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U334" t="s">
+        <v>3854</v>
+      </c>
+    </row>
+    <row r="335" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C335" t="s">
         <v>833</v>
       </c>
@@ -33832,8 +34838,11 @@
       <c r="T335" t="s">
         <v>4283</v>
       </c>
-    </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U335" t="s">
+        <v>3853</v>
+      </c>
+    </row>
+    <row r="336" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C336" t="s">
         <v>834</v>
       </c>
@@ -33882,8 +34891,11 @@
       <c r="T336" t="s">
         <v>4284</v>
       </c>
-    </row>
-    <row r="337" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U336" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="337" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C337" t="s">
         <v>835</v>
       </c>
@@ -33932,8 +34944,11 @@
       <c r="T337" t="s">
         <v>4285</v>
       </c>
-    </row>
-    <row r="338" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U337" t="s">
+        <v>3851</v>
+      </c>
+    </row>
+    <row r="338" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C338" t="s">
         <v>836</v>
       </c>
@@ -33982,8 +34997,11 @@
       <c r="T338" t="s">
         <v>4286</v>
       </c>
-    </row>
-    <row r="339" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U338" t="s">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="339" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C339" t="s">
         <v>837</v>
       </c>
@@ -34032,8 +35050,11 @@
       <c r="T339" t="s">
         <v>4287</v>
       </c>
-    </row>
-    <row r="340" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U339" t="s">
+        <v>3849</v>
+      </c>
+    </row>
+    <row r="340" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C340" t="s">
         <v>838</v>
       </c>
@@ -34082,8 +35103,11 @@
       <c r="T340" t="s">
         <v>4288</v>
       </c>
-    </row>
-    <row r="341" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U340" t="s">
+        <v>3848</v>
+      </c>
+    </row>
+    <row r="341" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C341" t="s">
         <v>839</v>
       </c>
@@ -34132,8 +35156,11 @@
       <c r="T341" t="s">
         <v>4289</v>
       </c>
-    </row>
-    <row r="342" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U341" t="s">
+        <v>3847</v>
+      </c>
+    </row>
+    <row r="342" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C342" t="s">
         <v>840</v>
       </c>
@@ -34182,8 +35209,11 @@
       <c r="T342" t="s">
         <v>4290</v>
       </c>
-    </row>
-    <row r="343" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U342" t="s">
+        <v>3846</v>
+      </c>
+    </row>
+    <row r="343" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C343" t="s">
         <v>841</v>
       </c>
@@ -34232,8 +35262,11 @@
       <c r="T343" t="s">
         <v>4291</v>
       </c>
-    </row>
-    <row r="344" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U343" t="s">
+        <v>3845</v>
+      </c>
+    </row>
+    <row r="344" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C344" t="s">
         <v>842</v>
       </c>
@@ -34282,8 +35315,11 @@
       <c r="T344" t="s">
         <v>4292</v>
       </c>
-    </row>
-    <row r="345" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U344" t="s">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="345" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C345" t="s">
         <v>843</v>
       </c>
@@ -34332,8 +35368,11 @@
       <c r="T345" t="s">
         <v>4293</v>
       </c>
-    </row>
-    <row r="346" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U345" t="s">
+        <v>3843</v>
+      </c>
+    </row>
+    <row r="346" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C346" t="s">
         <v>844</v>
       </c>
@@ -34382,8 +35421,11 @@
       <c r="T346" t="s">
         <v>4294</v>
       </c>
-    </row>
-    <row r="347" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U346" t="s">
+        <v>3842</v>
+      </c>
+    </row>
+    <row r="347" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C347" t="s">
         <v>845</v>
       </c>
@@ -34432,8 +35474,11 @@
       <c r="T347" t="s">
         <v>4295</v>
       </c>
-    </row>
-    <row r="348" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U347" t="s">
+        <v>3841</v>
+      </c>
+    </row>
+    <row r="348" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C348" t="s">
         <v>846</v>
       </c>
@@ -34482,8 +35527,11 @@
       <c r="T348" t="s">
         <v>4296</v>
       </c>
-    </row>
-    <row r="349" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U348" t="s">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="349" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C349" t="s">
         <v>847</v>
       </c>
@@ -34532,8 +35580,11 @@
       <c r="T349" t="s">
         <v>4297</v>
       </c>
-    </row>
-    <row r="350" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U349" t="s">
+        <v>3839</v>
+      </c>
+    </row>
+    <row r="350" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C350" t="s">
         <v>848</v>
       </c>
@@ -34582,8 +35633,11 @@
       <c r="T350" t="s">
         <v>4298</v>
       </c>
-    </row>
-    <row r="351" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U350" t="s">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="351" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C351" t="s">
         <v>849</v>
       </c>
@@ -34632,8 +35686,11 @@
       <c r="T351" t="s">
         <v>4299</v>
       </c>
-    </row>
-    <row r="352" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U351" t="s">
+        <v>3837</v>
+      </c>
+    </row>
+    <row r="352" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C352" t="s">
         <v>850</v>
       </c>
@@ -34682,8 +35739,11 @@
       <c r="T352" t="s">
         <v>4300</v>
       </c>
-    </row>
-    <row r="353" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U352" t="s">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="353" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C353" t="s">
         <v>851</v>
       </c>
@@ -34732,8 +35792,11 @@
       <c r="T353" t="s">
         <v>4301</v>
       </c>
-    </row>
-    <row r="354" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U353" t="s">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="354" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C354" t="s">
         <v>852</v>
       </c>
@@ -34782,8 +35845,11 @@
       <c r="T354" t="s">
         <v>4302</v>
       </c>
-    </row>
-    <row r="355" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U354" t="s">
+        <v>3834</v>
+      </c>
+    </row>
+    <row r="355" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C355" t="s">
         <v>853</v>
       </c>
@@ -34832,8 +35898,11 @@
       <c r="T355" t="s">
         <v>4303</v>
       </c>
-    </row>
-    <row r="356" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U355" t="s">
+        <v>3833</v>
+      </c>
+    </row>
+    <row r="356" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C356" t="s">
         <v>854</v>
       </c>
@@ -34882,8 +35951,11 @@
       <c r="T356" t="s">
         <v>4304</v>
       </c>
-    </row>
-    <row r="357" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U356" t="s">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="357" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C357" t="s">
         <v>855</v>
       </c>
@@ -34932,8 +36004,11 @@
       <c r="T357" t="s">
         <v>4305</v>
       </c>
-    </row>
-    <row r="358" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U357" t="s">
+        <v>3831</v>
+      </c>
+    </row>
+    <row r="358" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C358" t="s">
         <v>856</v>
       </c>
@@ -34982,8 +36057,11 @@
       <c r="T358" t="s">
         <v>4306</v>
       </c>
-    </row>
-    <row r="359" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U358" t="s">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="359" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C359" t="s">
         <v>857</v>
       </c>
@@ -35032,8 +36110,11 @@
       <c r="T359" t="s">
         <v>4307</v>
       </c>
-    </row>
-    <row r="360" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U359" t="s">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="360" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C360" t="s">
         <v>858</v>
       </c>
@@ -35082,8 +36163,11 @@
       <c r="T360" t="s">
         <v>4308</v>
       </c>
-    </row>
-    <row r="361" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U360" t="s">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="361" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C361" t="s">
         <v>859</v>
       </c>
@@ -35132,8 +36216,11 @@
       <c r="T361" t="s">
         <v>4309</v>
       </c>
-    </row>
-    <row r="362" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U361" t="s">
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="362" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C362" t="s">
         <v>860</v>
       </c>
@@ -35182,8 +36269,11 @@
       <c r="T362" t="s">
         <v>4310</v>
       </c>
-    </row>
-    <row r="363" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U362" t="s">
+        <v>3826</v>
+      </c>
+    </row>
+    <row r="363" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C363" t="s">
         <v>861</v>
       </c>
@@ -35232,8 +36322,11 @@
       <c r="T363" t="s">
         <v>4311</v>
       </c>
-    </row>
-    <row r="364" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U363" t="s">
+        <v>3825</v>
+      </c>
+    </row>
+    <row r="364" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C364" t="s">
         <v>862</v>
       </c>
@@ -35282,8 +36375,11 @@
       <c r="T364" t="s">
         <v>4312</v>
       </c>
-    </row>
-    <row r="365" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U364" t="s">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="365" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C365" t="s">
         <v>863</v>
       </c>
@@ -35332,8 +36428,11 @@
       <c r="T365" t="s">
         <v>4313</v>
       </c>
-    </row>
-    <row r="366" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U365" t="s">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="366" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C366" t="s">
         <v>864</v>
       </c>
@@ -35382,8 +36481,11 @@
       <c r="T366" t="s">
         <v>4314</v>
       </c>
-    </row>
-    <row r="367" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U366" t="s">
+        <v>3822</v>
+      </c>
+    </row>
+    <row r="367" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C367" t="s">
         <v>865</v>
       </c>
@@ -35432,8 +36534,11 @@
       <c r="T367" t="s">
         <v>4315</v>
       </c>
-    </row>
-    <row r="368" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U367" t="s">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="368" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C368" t="s">
         <v>866</v>
       </c>
@@ -35482,8 +36587,11 @@
       <c r="T368" t="s">
         <v>4316</v>
       </c>
-    </row>
-    <row r="369" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U368" t="s">
+        <v>3820</v>
+      </c>
+    </row>
+    <row r="369" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C369" t="s">
         <v>867</v>
       </c>
@@ -35532,8 +36640,11 @@
       <c r="T369" t="s">
         <v>4317</v>
       </c>
-    </row>
-    <row r="370" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U369" t="s">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="370" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C370" t="s">
         <v>868</v>
       </c>
@@ -35582,8 +36693,11 @@
       <c r="T370" t="s">
         <v>4318</v>
       </c>
-    </row>
-    <row r="371" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U370" t="s">
+        <v>3818</v>
+      </c>
+    </row>
+    <row r="371" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C371" t="s">
         <v>869</v>
       </c>
@@ -35632,8 +36746,11 @@
       <c r="T371" t="s">
         <v>4319</v>
       </c>
-    </row>
-    <row r="372" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U371" t="s">
+        <v>3817</v>
+      </c>
+    </row>
+    <row r="372" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C372" t="s">
         <v>870</v>
       </c>
@@ -35682,8 +36799,11 @@
       <c r="T372" t="s">
         <v>4320</v>
       </c>
-    </row>
-    <row r="373" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U372" t="s">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="373" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C373" t="s">
         <v>871</v>
       </c>
@@ -35732,8 +36852,11 @@
       <c r="T373" t="s">
         <v>4321</v>
       </c>
-    </row>
-    <row r="374" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U373" t="s">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="374" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C374" t="s">
         <v>872</v>
       </c>
@@ -35782,8 +36905,11 @@
       <c r="T374" t="s">
         <v>4322</v>
       </c>
-    </row>
-    <row r="375" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U374" t="s">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="375" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C375" t="s">
         <v>873</v>
       </c>
@@ -35832,8 +36958,11 @@
       <c r="T375" t="s">
         <v>4323</v>
       </c>
-    </row>
-    <row r="376" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U375" t="s">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="376" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C376" t="s">
         <v>874</v>
       </c>
@@ -35882,8 +37011,11 @@
       <c r="T376" t="s">
         <v>4324</v>
       </c>
-    </row>
-    <row r="377" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U376" t="s">
+        <v>3812</v>
+      </c>
+    </row>
+    <row r="377" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C377" t="s">
         <v>875</v>
       </c>
@@ -35932,8 +37064,11 @@
       <c r="T377" t="s">
         <v>4325</v>
       </c>
-    </row>
-    <row r="378" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U377" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="378" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C378" t="s">
         <v>876</v>
       </c>
@@ -35982,8 +37117,11 @@
       <c r="T378" t="s">
         <v>4326</v>
       </c>
-    </row>
-    <row r="379" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U378" t="s">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="379" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C379" t="s">
         <v>877</v>
       </c>
@@ -36032,8 +37170,11 @@
       <c r="T379" t="s">
         <v>4327</v>
       </c>
-    </row>
-    <row r="380" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U379" t="s">
+        <v>3809</v>
+      </c>
+    </row>
+    <row r="380" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C380" t="s">
         <v>878</v>
       </c>
@@ -36082,8 +37223,11 @@
       <c r="T380" t="s">
         <v>4328</v>
       </c>
-    </row>
-    <row r="381" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U380" t="s">
+        <v>3808</v>
+      </c>
+    </row>
+    <row r="381" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C381" t="s">
         <v>879</v>
       </c>
@@ -36132,8 +37276,11 @@
       <c r="T381" t="s">
         <v>4329</v>
       </c>
-    </row>
-    <row r="382" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U381" t="s">
+        <v>3807</v>
+      </c>
+    </row>
+    <row r="382" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C382" t="s">
         <v>880</v>
       </c>
@@ -36182,8 +37329,11 @@
       <c r="T382" t="s">
         <v>4330</v>
       </c>
-    </row>
-    <row r="383" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U382" t="s">
+        <v>3806</v>
+      </c>
+    </row>
+    <row r="383" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C383" t="s">
         <v>881</v>
       </c>
@@ -36232,8 +37382,11 @@
       <c r="T383" t="s">
         <v>4331</v>
       </c>
-    </row>
-    <row r="384" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U383" t="s">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="384" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C384" t="s">
         <v>882</v>
       </c>
@@ -36282,8 +37435,11 @@
       <c r="T384" t="s">
         <v>4332</v>
       </c>
-    </row>
-    <row r="385" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U384" t="s">
+        <v>3804</v>
+      </c>
+    </row>
+    <row r="385" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C385" t="s">
         <v>883</v>
       </c>
@@ -36332,8 +37488,11 @@
       <c r="T385" t="s">
         <v>4333</v>
       </c>
-    </row>
-    <row r="386" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U385" t="s">
+        <v>3803</v>
+      </c>
+    </row>
+    <row r="386" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C386" t="s">
         <v>884</v>
       </c>
@@ -36382,8 +37541,11 @@
       <c r="T386" t="s">
         <v>4334</v>
       </c>
-    </row>
-    <row r="387" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U386" t="s">
+        <v>3802</v>
+      </c>
+    </row>
+    <row r="387" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C387" t="s">
         <v>885</v>
       </c>
@@ -36432,8 +37594,11 @@
       <c r="T387" t="s">
         <v>4335</v>
       </c>
-    </row>
-    <row r="388" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U387" t="s">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="388" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C388" t="s">
         <v>886</v>
       </c>
@@ -36482,8 +37647,11 @@
       <c r="T388" t="s">
         <v>4336</v>
       </c>
-    </row>
-    <row r="389" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U388" t="s">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="389" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C389" t="s">
         <v>887</v>
       </c>
@@ -36532,8 +37700,11 @@
       <c r="T389" t="s">
         <v>4337</v>
       </c>
-    </row>
-    <row r="390" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U389" t="s">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="390" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C390" t="s">
         <v>888</v>
       </c>
@@ -36582,8 +37753,11 @@
       <c r="T390" t="s">
         <v>4338</v>
       </c>
-    </row>
-    <row r="391" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U390" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="391" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C391" t="s">
         <v>889</v>
       </c>
@@ -36632,8 +37806,11 @@
       <c r="T391" t="s">
         <v>4339</v>
       </c>
-    </row>
-    <row r="392" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U391" t="s">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="392" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C392" t="s">
         <v>890</v>
       </c>
@@ -36682,8 +37859,11 @@
       <c r="T392" t="s">
         <v>4340</v>
       </c>
-    </row>
-    <row r="393" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U392" t="s">
+        <v>3796</v>
+      </c>
+    </row>
+    <row r="393" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C393" t="s">
         <v>891</v>
       </c>
@@ -36732,8 +37912,11 @@
       <c r="T393" t="s">
         <v>4341</v>
       </c>
-    </row>
-    <row r="394" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U393" t="s">
+        <v>3795</v>
+      </c>
+    </row>
+    <row r="394" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C394" t="s">
         <v>892</v>
       </c>
@@ -36782,8 +37965,11 @@
       <c r="T394" t="s">
         <v>4342</v>
       </c>
-    </row>
-    <row r="395" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U394" t="s">
+        <v>3794</v>
+      </c>
+    </row>
+    <row r="395" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C395" t="s">
         <v>893</v>
       </c>
@@ -36832,8 +38018,11 @@
       <c r="T395" t="s">
         <v>4343</v>
       </c>
-    </row>
-    <row r="396" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U395" t="s">
+        <v>3793</v>
+      </c>
+    </row>
+    <row r="396" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C396" t="s">
         <v>894</v>
       </c>
@@ -36882,8 +38071,11 @@
       <c r="T396" t="s">
         <v>4344</v>
       </c>
-    </row>
-    <row r="397" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U396" t="s">
+        <v>3792</v>
+      </c>
+    </row>
+    <row r="397" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C397" t="s">
         <v>895</v>
       </c>
@@ -36932,8 +38124,11 @@
       <c r="T397" t="s">
         <v>4345</v>
       </c>
-    </row>
-    <row r="398" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U397" t="s">
+        <v>3791</v>
+      </c>
+    </row>
+    <row r="398" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C398" t="s">
         <v>896</v>
       </c>
@@ -36982,8 +38177,11 @@
       <c r="T398" t="s">
         <v>4346</v>
       </c>
-    </row>
-    <row r="399" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U398" t="s">
+        <v>3790</v>
+      </c>
+    </row>
+    <row r="399" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C399" t="s">
         <v>897</v>
       </c>
@@ -37032,8 +38230,11 @@
       <c r="T399" t="s">
         <v>4347</v>
       </c>
-    </row>
-    <row r="400" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U399" t="s">
+        <v>3789</v>
+      </c>
+    </row>
+    <row r="400" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C400" t="s">
         <v>898</v>
       </c>
@@ -37082,8 +38283,11 @@
       <c r="T400" t="s">
         <v>4348</v>
       </c>
-    </row>
-    <row r="401" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U400" t="s">
+        <v>3788</v>
+      </c>
+    </row>
+    <row r="401" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C401" t="s">
         <v>899</v>
       </c>
@@ -37132,8 +38336,11 @@
       <c r="T401" t="s">
         <v>4349</v>
       </c>
-    </row>
-    <row r="402" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U401" t="s">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="402" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C402" t="s">
         <v>900</v>
       </c>
@@ -37182,8 +38389,11 @@
       <c r="T402" t="s">
         <v>4350</v>
       </c>
-    </row>
-    <row r="403" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U402" t="s">
+        <v>3786</v>
+      </c>
+    </row>
+    <row r="403" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C403" t="s">
         <v>901</v>
       </c>
@@ -37232,8 +38442,11 @@
       <c r="T403" t="s">
         <v>4351</v>
       </c>
-    </row>
-    <row r="404" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U403" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="404" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C404" t="s">
         <v>902</v>
       </c>
@@ -37282,8 +38495,11 @@
       <c r="T404" t="s">
         <v>4352</v>
       </c>
-    </row>
-    <row r="405" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U404" t="s">
+        <v>3784</v>
+      </c>
+    </row>
+    <row r="405" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C405" t="s">
         <v>903</v>
       </c>
@@ -37332,8 +38548,11 @@
       <c r="T405" t="s">
         <v>4353</v>
       </c>
-    </row>
-    <row r="406" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U405" t="s">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="406" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C406" t="s">
         <v>904</v>
       </c>
@@ -37382,8 +38601,11 @@
       <c r="T406" t="s">
         <v>4354</v>
       </c>
-    </row>
-    <row r="407" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U406" t="s">
+        <v>3782</v>
+      </c>
+    </row>
+    <row r="407" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C407" t="s">
         <v>905</v>
       </c>
@@ -37432,8 +38654,11 @@
       <c r="T407" t="s">
         <v>4355</v>
       </c>
-    </row>
-    <row r="408" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U407" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="408" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C408" t="s">
         <v>906</v>
       </c>
@@ -37479,8 +38704,11 @@
       <c r="T408" t="s">
         <v>4356</v>
       </c>
-    </row>
-    <row r="409" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U408" t="s">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="409" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C409" t="s">
         <v>907</v>
       </c>
@@ -37526,8 +38754,11 @@
       <c r="T409" t="s">
         <v>4357</v>
       </c>
-    </row>
-    <row r="410" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U409" t="s">
+        <v>3779</v>
+      </c>
+    </row>
+    <row r="410" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C410" t="s">
         <v>908</v>
       </c>
@@ -37573,8 +38804,11 @@
       <c r="T410" t="s">
         <v>4358</v>
       </c>
-    </row>
-    <row r="411" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U410" t="s">
+        <v>3778</v>
+      </c>
+    </row>
+    <row r="411" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C411" t="s">
         <v>909</v>
       </c>
@@ -37620,8 +38854,11 @@
       <c r="T411" t="s">
         <v>4359</v>
       </c>
-    </row>
-    <row r="412" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U411" t="s">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="412" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C412" t="s">
         <v>910</v>
       </c>
@@ -37667,8 +38904,11 @@
       <c r="T412" t="s">
         <v>4360</v>
       </c>
-    </row>
-    <row r="413" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U412" t="s">
+        <v>3776</v>
+      </c>
+    </row>
+    <row r="413" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C413" t="s">
         <v>911</v>
       </c>
@@ -37714,8 +38954,11 @@
       <c r="T413" t="s">
         <v>4361</v>
       </c>
-    </row>
-    <row r="414" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U413" t="s">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="414" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C414" t="s">
         <v>912</v>
       </c>
@@ -37761,8 +39004,11 @@
       <c r="T414" t="s">
         <v>4362</v>
       </c>
-    </row>
-    <row r="415" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U414" t="s">
+        <v>3774</v>
+      </c>
+    </row>
+    <row r="415" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C415" t="s">
         <v>913</v>
       </c>
@@ -37808,8 +39054,11 @@
       <c r="T415" t="s">
         <v>4363</v>
       </c>
-    </row>
-    <row r="416" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U415" t="s">
+        <v>3773</v>
+      </c>
+    </row>
+    <row r="416" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C416" t="s">
         <v>914</v>
       </c>
@@ -37855,8 +39104,11 @@
       <c r="T416" t="s">
         <v>4364</v>
       </c>
-    </row>
-    <row r="417" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U416" t="s">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="417" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C417" t="s">
         <v>915</v>
       </c>
@@ -37902,8 +39154,11 @@
       <c r="T417" t="s">
         <v>4365</v>
       </c>
-    </row>
-    <row r="418" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U417" t="s">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="418" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C418" t="s">
         <v>916</v>
       </c>
@@ -37949,8 +39204,11 @@
       <c r="T418" t="s">
         <v>4366</v>
       </c>
-    </row>
-    <row r="419" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U418" t="s">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="419" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C419" t="s">
         <v>917</v>
       </c>
@@ -37996,8 +39254,11 @@
       <c r="T419" t="s">
         <v>4367</v>
       </c>
-    </row>
-    <row r="420" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U419" t="s">
+        <v>3769</v>
+      </c>
+    </row>
+    <row r="420" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C420" t="s">
         <v>918</v>
       </c>
@@ -38043,8 +39304,11 @@
       <c r="T420" t="s">
         <v>4368</v>
       </c>
-    </row>
-    <row r="421" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U420" t="s">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="421" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C421" t="s">
         <v>919</v>
       </c>
@@ -38090,8 +39354,11 @@
       <c r="T421" t="s">
         <v>4369</v>
       </c>
-    </row>
-    <row r="422" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U421" t="s">
+        <v>3767</v>
+      </c>
+    </row>
+    <row r="422" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C422" t="s">
         <v>920</v>
       </c>
@@ -38137,8 +39404,11 @@
       <c r="T422" t="s">
         <v>4370</v>
       </c>
-    </row>
-    <row r="423" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U422" t="s">
+        <v>3766</v>
+      </c>
+    </row>
+    <row r="423" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C423" t="s">
         <v>921</v>
       </c>
@@ -38184,8 +39454,11 @@
       <c r="T423" t="s">
         <v>4371</v>
       </c>
-    </row>
-    <row r="424" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U423" t="s">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="424" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C424" t="s">
         <v>922</v>
       </c>
@@ -38231,8 +39504,11 @@
       <c r="T424" t="s">
         <v>4372</v>
       </c>
-    </row>
-    <row r="425" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U424" t="s">
+        <v>3764</v>
+      </c>
+    </row>
+    <row r="425" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C425" t="s">
         <v>923</v>
       </c>
@@ -38278,8 +39554,11 @@
       <c r="T425" t="s">
         <v>4373</v>
       </c>
-    </row>
-    <row r="426" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U425" t="s">
+        <v>3763</v>
+      </c>
+    </row>
+    <row r="426" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C426" t="s">
         <v>924</v>
       </c>
@@ -38325,8 +39604,11 @@
       <c r="T426" t="s">
         <v>4374</v>
       </c>
-    </row>
-    <row r="427" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U426" t="s">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="427" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C427" t="s">
         <v>925</v>
       </c>
@@ -38372,8 +39654,11 @@
       <c r="T427" t="s">
         <v>4375</v>
       </c>
-    </row>
-    <row r="428" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U427" t="s">
+        <v>3761</v>
+      </c>
+    </row>
+    <row r="428" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C428" t="s">
         <v>926</v>
       </c>
@@ -38419,8 +39704,11 @@
       <c r="T428" t="s">
         <v>4376</v>
       </c>
-    </row>
-    <row r="429" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U428" t="s">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="429" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C429" t="s">
         <v>927</v>
       </c>
@@ -38466,8 +39754,11 @@
       <c r="T429" t="s">
         <v>4377</v>
       </c>
-    </row>
-    <row r="430" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U429" t="s">
+        <v>3759</v>
+      </c>
+    </row>
+    <row r="430" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C430" t="s">
         <v>928</v>
       </c>
@@ -38513,8 +39804,11 @@
       <c r="T430" t="s">
         <v>4378</v>
       </c>
-    </row>
-    <row r="431" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U430" t="s">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="431" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C431" t="s">
         <v>929</v>
       </c>
@@ -38560,8 +39854,11 @@
       <c r="T431" t="s">
         <v>4379</v>
       </c>
-    </row>
-    <row r="432" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U431" t="s">
+        <v>3757</v>
+      </c>
+    </row>
+    <row r="432" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C432" t="s">
         <v>930</v>
       </c>
@@ -38607,8 +39904,11 @@
       <c r="T432" t="s">
         <v>4380</v>
       </c>
-    </row>
-    <row r="433" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U432" t="s">
+        <v>3756</v>
+      </c>
+    </row>
+    <row r="433" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C433" t="s">
         <v>931</v>
       </c>
@@ -38654,8 +39954,11 @@
       <c r="T433" t="s">
         <v>4381</v>
       </c>
-    </row>
-    <row r="434" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U433" t="s">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="434" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C434" t="s">
         <v>932</v>
       </c>
@@ -38701,8 +40004,11 @@
       <c r="T434" t="s">
         <v>4382</v>
       </c>
-    </row>
-    <row r="435" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U434" t="s">
+        <v>3754</v>
+      </c>
+    </row>
+    <row r="435" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C435" t="s">
         <v>933</v>
       </c>
@@ -38748,8 +40054,11 @@
       <c r="T435" t="s">
         <v>4383</v>
       </c>
-    </row>
-    <row r="436" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U435" t="s">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="436" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C436" t="s">
         <v>934</v>
       </c>
@@ -38795,8 +40104,11 @@
       <c r="T436" t="s">
         <v>4384</v>
       </c>
-    </row>
-    <row r="437" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U436" t="s">
+        <v>3752</v>
+      </c>
+    </row>
+    <row r="437" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C437" t="s">
         <v>935</v>
       </c>
@@ -38842,8 +40154,11 @@
       <c r="T437" t="s">
         <v>4385</v>
       </c>
-    </row>
-    <row r="438" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U437" t="s">
+        <v>3751</v>
+      </c>
+    </row>
+    <row r="438" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C438" t="s">
         <v>936</v>
       </c>
@@ -38889,8 +40204,11 @@
       <c r="T438" t="s">
         <v>4386</v>
       </c>
-    </row>
-    <row r="439" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U438" t="s">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="439" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C439" t="s">
         <v>937</v>
       </c>
@@ -38936,8 +40254,11 @@
       <c r="T439" t="s">
         <v>4387</v>
       </c>
-    </row>
-    <row r="440" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U439" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="440" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C440" t="s">
         <v>938</v>
       </c>
@@ -38983,8 +40304,11 @@
       <c r="T440" t="s">
         <v>4388</v>
       </c>
-    </row>
-    <row r="441" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U440" t="s">
+        <v>3748</v>
+      </c>
+    </row>
+    <row r="441" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C441" t="s">
         <v>939</v>
       </c>
@@ -39030,8 +40354,11 @@
       <c r="T441" t="s">
         <v>4389</v>
       </c>
-    </row>
-    <row r="442" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U441" t="s">
+        <v>3747</v>
+      </c>
+    </row>
+    <row r="442" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C442" t="s">
         <v>940</v>
       </c>
@@ -39077,8 +40404,11 @@
       <c r="T442" t="s">
         <v>4390</v>
       </c>
-    </row>
-    <row r="443" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U442" t="s">
+        <v>3746</v>
+      </c>
+    </row>
+    <row r="443" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C443" t="s">
         <v>941</v>
       </c>
@@ -39124,8 +40454,11 @@
       <c r="T443" t="s">
         <v>4391</v>
       </c>
-    </row>
-    <row r="444" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U443" t="s">
+        <v>3745</v>
+      </c>
+    </row>
+    <row r="444" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C444" t="s">
         <v>942</v>
       </c>
@@ -39171,8 +40504,11 @@
       <c r="T444" t="s">
         <v>4392</v>
       </c>
-    </row>
-    <row r="445" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U444" t="s">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="445" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C445" t="s">
         <v>943</v>
       </c>
@@ -39218,8 +40554,11 @@
       <c r="T445" t="s">
         <v>4393</v>
       </c>
-    </row>
-    <row r="446" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U445" t="s">
+        <v>3743</v>
+      </c>
+    </row>
+    <row r="446" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C446" t="s">
         <v>944</v>
       </c>
@@ -39265,8 +40604,11 @@
       <c r="T446" t="s">
         <v>4394</v>
       </c>
-    </row>
-    <row r="447" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U446" t="s">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="447" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C447" t="s">
         <v>945</v>
       </c>
@@ -39312,8 +40654,11 @@
       <c r="T447" t="s">
         <v>4395</v>
       </c>
-    </row>
-    <row r="448" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U447" t="s">
+        <v>3741</v>
+      </c>
+    </row>
+    <row r="448" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C448" t="s">
         <v>946</v>
       </c>
@@ -39359,8 +40704,11 @@
       <c r="T448" t="s">
         <v>4396</v>
       </c>
-    </row>
-    <row r="449" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U448" t="s">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="449" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C449" t="s">
         <v>947</v>
       </c>
@@ -39406,8 +40754,11 @@
       <c r="T449" t="s">
         <v>4397</v>
       </c>
-    </row>
-    <row r="450" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U449" t="s">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="450" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C450" t="s">
         <v>948</v>
       </c>
@@ -39453,8 +40804,11 @@
       <c r="T450" t="s">
         <v>4398</v>
       </c>
-    </row>
-    <row r="451" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U450" t="s">
+        <v>3738</v>
+      </c>
+    </row>
+    <row r="451" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C451" t="s">
         <v>949</v>
       </c>
@@ -39500,8 +40854,11 @@
       <c r="T451" t="s">
         <v>4399</v>
       </c>
-    </row>
-    <row r="452" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U451" t="s">
+        <v>3737</v>
+      </c>
+    </row>
+    <row r="452" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C452" t="s">
         <v>950</v>
       </c>
@@ -39547,8 +40904,11 @@
       <c r="T452" t="s">
         <v>4400</v>
       </c>
-    </row>
-    <row r="453" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U452" t="s">
+        <v>3736</v>
+      </c>
+    </row>
+    <row r="453" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C453" t="s">
         <v>951</v>
       </c>
@@ -39594,8 +40954,11 @@
       <c r="T453" t="s">
         <v>4401</v>
       </c>
-    </row>
-    <row r="454" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U453" t="s">
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="454" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C454" t="s">
         <v>952</v>
       </c>
@@ -39641,8 +41004,11 @@
       <c r="T454" t="s">
         <v>4402</v>
       </c>
-    </row>
-    <row r="455" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U454" t="s">
+        <v>3734</v>
+      </c>
+    </row>
+    <row r="455" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C455" t="s">
         <v>953</v>
       </c>
@@ -39688,8 +41054,11 @@
       <c r="T455" t="s">
         <v>4403</v>
       </c>
-    </row>
-    <row r="456" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U455" t="s">
+        <v>3733</v>
+      </c>
+    </row>
+    <row r="456" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C456" t="s">
         <v>954</v>
       </c>
@@ -39735,8 +41104,11 @@
       <c r="T456" t="s">
         <v>4404</v>
       </c>
-    </row>
-    <row r="457" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U456" t="s">
+        <v>3732</v>
+      </c>
+    </row>
+    <row r="457" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C457" t="s">
         <v>955</v>
       </c>
@@ -39782,8 +41154,11 @@
       <c r="T457" t="s">
         <v>4405</v>
       </c>
-    </row>
-    <row r="458" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U457" t="s">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="458" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C458" t="s">
         <v>956</v>
       </c>
@@ -39829,8 +41204,11 @@
       <c r="T458" t="s">
         <v>4406</v>
       </c>
-    </row>
-    <row r="459" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U458" t="s">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="459" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C459" t="s">
         <v>957</v>
       </c>
@@ -39876,8 +41254,11 @@
       <c r="T459" t="s">
         <v>4407</v>
       </c>
-    </row>
-    <row r="460" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U459" t="s">
+        <v>3729</v>
+      </c>
+    </row>
+    <row r="460" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C460" t="s">
         <v>958</v>
       </c>
@@ -39923,8 +41304,11 @@
       <c r="T460" t="s">
         <v>4408</v>
       </c>
-    </row>
-    <row r="461" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U460" t="s">
+        <v>3728</v>
+      </c>
+    </row>
+    <row r="461" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C461" t="s">
         <v>959</v>
       </c>
@@ -39970,8 +41354,11 @@
       <c r="T461" t="s">
         <v>4409</v>
       </c>
-    </row>
-    <row r="462" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U461" t="s">
+        <v>3727</v>
+      </c>
+    </row>
+    <row r="462" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C462" t="s">
         <v>960</v>
       </c>
@@ -40017,8 +41404,11 @@
       <c r="T462" t="s">
         <v>4410</v>
       </c>
-    </row>
-    <row r="463" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U462" t="s">
+        <v>3726</v>
+      </c>
+    </row>
+    <row r="463" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C463" t="s">
         <v>961</v>
       </c>
@@ -40064,8 +41454,11 @@
       <c r="T463" t="s">
         <v>4411</v>
       </c>
-    </row>
-    <row r="464" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U463" t="s">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="464" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C464" t="s">
         <v>962</v>
       </c>
@@ -40111,8 +41504,11 @@
       <c r="T464" t="s">
         <v>4412</v>
       </c>
-    </row>
-    <row r="465" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U464" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="465" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C465" t="s">
         <v>963</v>
       </c>
@@ -40158,8 +41554,11 @@
       <c r="T465" t="s">
         <v>4413</v>
       </c>
-    </row>
-    <row r="466" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U465" t="s">
+        <v>3723</v>
+      </c>
+    </row>
+    <row r="466" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C466" t="s">
         <v>964</v>
       </c>
@@ -40205,8 +41604,11 @@
       <c r="T466" t="s">
         <v>4414</v>
       </c>
-    </row>
-    <row r="467" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U466" t="s">
+        <v>3722</v>
+      </c>
+    </row>
+    <row r="467" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C467" t="s">
         <v>965</v>
       </c>
@@ -40252,8 +41654,11 @@
       <c r="T467" t="s">
         <v>4415</v>
       </c>
-    </row>
-    <row r="468" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U467" t="s">
+        <v>3721</v>
+      </c>
+    </row>
+    <row r="468" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C468" t="s">
         <v>966</v>
       </c>
@@ -40299,8 +41704,11 @@
       <c r="T468" t="s">
         <v>4416</v>
       </c>
-    </row>
-    <row r="469" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U468" t="s">
+        <v>3720</v>
+      </c>
+    </row>
+    <row r="469" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C469" t="s">
         <v>967</v>
       </c>
@@ -40346,8 +41754,11 @@
       <c r="T469" t="s">
         <v>4417</v>
       </c>
-    </row>
-    <row r="470" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U469" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="470" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C470" t="s">
         <v>968</v>
       </c>
@@ -40393,8 +41804,11 @@
       <c r="T470" t="s">
         <v>4418</v>
       </c>
-    </row>
-    <row r="471" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U470" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="471" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C471" t="s">
         <v>969</v>
       </c>
@@ -40440,8 +41854,11 @@
       <c r="T471" t="s">
         <v>4419</v>
       </c>
-    </row>
-    <row r="472" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U471" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="472" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C472" t="s">
         <v>970</v>
       </c>
@@ -40487,8 +41904,11 @@
       <c r="T472" t="s">
         <v>4420</v>
       </c>
-    </row>
-    <row r="473" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="U472" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="473" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C473" t="s">
         <v>971</v>
       </c>
@@ -40535,7 +41955,7 @@
         <v>4421</v>
       </c>
     </row>
-    <row r="474" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="474" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C474" t="s">
         <v>972</v>
       </c>
@@ -40582,7 +42002,7 @@
         <v>4422</v>
       </c>
     </row>
-    <row r="475" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="475" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C475" t="s">
         <v>973</v>
       </c>
@@ -40629,7 +42049,7 @@
         <v>4423</v>
       </c>
     </row>
-    <row r="476" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="476" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C476" t="s">
         <v>974</v>
       </c>
@@ -40676,7 +42096,7 @@
         <v>4424</v>
       </c>
     </row>
-    <row r="477" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="477" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C477" t="s">
         <v>975</v>
       </c>
@@ -40723,7 +42143,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="478" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="478" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C478" t="s">
         <v>976</v>
       </c>
@@ -40770,7 +42190,7 @@
         <v>4426</v>
       </c>
     </row>
-    <row r="479" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="479" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C479" t="s">
         <v>977</v>
       </c>
@@ -40817,7 +42237,7 @@
         <v>4427</v>
       </c>
     </row>
-    <row r="480" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="480" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C480" t="s">
         <v>978</v>
       </c>

--- a/Excel/Allplanttaglist.xlsx
+++ b/Excel/Allplanttaglist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel-Files\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223EA3F3-38A0-4652-9A0A-493B95287D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F773185-AE79-474B-93AA-72584906CC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{0DFC0680-056B-49A9-993E-B17935078FFA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13884" uniqueCount="5579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14246" uniqueCount="5662">
   <si>
     <t>CSPPL</t>
   </si>
@@ -16771,6 +16771,255 @@
   </si>
   <si>
     <t>INV13_PCC_KVA</t>
+  </si>
+  <si>
+    <t>WCPS</t>
+  </si>
+  <si>
+    <t>SSPL</t>
+  </si>
+  <si>
+    <t>132KV_MW</t>
+  </si>
+  <si>
+    <t>132KV_MVAR</t>
+  </si>
+  <si>
+    <t>132KV_KV</t>
+  </si>
+  <si>
+    <t>132KV_HZ</t>
+  </si>
+  <si>
+    <t>132KV_TOT_AMP</t>
+  </si>
+  <si>
+    <t>132KV_PF</t>
+  </si>
+  <si>
+    <t>132KV_TOT_KVA</t>
+  </si>
+  <si>
+    <t>132KV_KWHE</t>
+  </si>
+  <si>
+    <t>11KV_MW</t>
+  </si>
+  <si>
+    <t>11KV_MVAR</t>
+  </si>
+  <si>
+    <t>11KV_KV</t>
+  </si>
+  <si>
+    <t>11KV_HZ</t>
+  </si>
+  <si>
+    <t>11KV_TOT_AMP</t>
+  </si>
+  <si>
+    <t>11KV_PF</t>
+  </si>
+  <si>
+    <t>11KV_TOT_KVA</t>
+  </si>
+  <si>
+    <t>11KV_KWHI</t>
+  </si>
+  <si>
+    <t>11KV_KWHE</t>
+  </si>
+  <si>
+    <t>TG_MW</t>
+  </si>
+  <si>
+    <t>TG_MVAR</t>
+  </si>
+  <si>
+    <t>TG_KV</t>
+  </si>
+  <si>
+    <t>TG_HZ</t>
+  </si>
+  <si>
+    <t>TG_TOT_AMP</t>
+  </si>
+  <si>
+    <t>TG_PF</t>
+  </si>
+  <si>
+    <t>TG_TOT_KVA</t>
+  </si>
+  <si>
+    <t>TG_KWHI</t>
+  </si>
+  <si>
+    <t>TG_KWHE</t>
+  </si>
+  <si>
+    <t>AUX_MW</t>
+  </si>
+  <si>
+    <t>AUX_MVAR</t>
+  </si>
+  <si>
+    <t>AUX_KV</t>
+  </si>
+  <si>
+    <t>DRI1_MW</t>
+  </si>
+  <si>
+    <t>DRI1_MVAR</t>
+  </si>
+  <si>
+    <t>DRI1_KV</t>
+  </si>
+  <si>
+    <t>DRI1_HZ</t>
+  </si>
+  <si>
+    <t>DRI1_TOT_AMP</t>
+  </si>
+  <si>
+    <t>DRI1_PF</t>
+  </si>
+  <si>
+    <t>DRI1_TOT_KVA</t>
+  </si>
+  <si>
+    <t>DRI1_KWHI</t>
+  </si>
+  <si>
+    <t>DRI2_MW</t>
+  </si>
+  <si>
+    <t>DRI2_MVAR</t>
+  </si>
+  <si>
+    <t>DRI2_KV</t>
+  </si>
+  <si>
+    <t>DRI2_HZ</t>
+  </si>
+  <si>
+    <t>DRI2_TOT_AMP</t>
+  </si>
+  <si>
+    <t>DRI2_PF</t>
+  </si>
+  <si>
+    <t>DRI2_TOT_KVA</t>
+  </si>
+  <si>
+    <t>DRI2_KWHI</t>
+  </si>
+  <si>
+    <t>FERRO1_MW</t>
+  </si>
+  <si>
+    <t>FERRO1_MVAR</t>
+  </si>
+  <si>
+    <t>FERRO1_KV</t>
+  </si>
+  <si>
+    <t>FERRO1_HZ</t>
+  </si>
+  <si>
+    <t>FERRO1_TOT_AMP</t>
+  </si>
+  <si>
+    <t>FERRO1_PF</t>
+  </si>
+  <si>
+    <t>FERRO1_TOT_KVA</t>
+  </si>
+  <si>
+    <t>FERRO1_KWHI</t>
+  </si>
+  <si>
+    <t>FERRO2_MW</t>
+  </si>
+  <si>
+    <t>FERRO2_MVAR</t>
+  </si>
+  <si>
+    <t>FERRO2_KV</t>
+  </si>
+  <si>
+    <t>FERRO2_HZ</t>
+  </si>
+  <si>
+    <t>FERRO2_TOT_AMP</t>
+  </si>
+  <si>
+    <t>FERRO2_PF</t>
+  </si>
+  <si>
+    <t>FERRO2_TOT_KVA</t>
+  </si>
+  <si>
+    <t>FERRO2_KWHI</t>
+  </si>
+  <si>
+    <t>LOAD_MW</t>
+  </si>
+  <si>
+    <t>LOAD_MVAR</t>
+  </si>
+  <si>
+    <t>132KV_CB_ON</t>
+  </si>
+  <si>
+    <t>11KV_CB_ON</t>
+  </si>
+  <si>
+    <t>TG_CB_ON</t>
+  </si>
+  <si>
+    <t>DRI1_CB_ON</t>
+  </si>
+  <si>
+    <t>DRI2_CB_ON</t>
+  </si>
+  <si>
+    <t>AUX_CB_ON</t>
+  </si>
+  <si>
+    <t>FERRO1_CB_ON</t>
+  </si>
+  <si>
+    <t>FERRO2_CB_ON</t>
+  </si>
+  <si>
+    <t>MFM_132KV_ON</t>
+  </si>
+  <si>
+    <t>MFM_11KV_ON</t>
+  </si>
+  <si>
+    <t>MFM_TG_ON</t>
+  </si>
+  <si>
+    <t>MFM_DRI1_ON</t>
+  </si>
+  <si>
+    <t>MFM_DRI2_ON</t>
+  </si>
+  <si>
+    <t>MFM_AUX_ON</t>
+  </si>
+  <si>
+    <t>MFM_FERRO1_ON</t>
+  </si>
+  <si>
+    <t>MFM_FERRO2_ON</t>
+  </si>
+  <si>
+    <t>SLDC_SERVER1_ON</t>
+  </si>
+  <si>
+    <t>SLDC_SERVER2_ON</t>
   </si>
 </sst>
 </file>
@@ -17261,9 +17510,11 @@
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -17619,7 +17870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7382AB7-75C8-44B4-BF78-34EC17E0275A}">
-  <dimension ref="A1:V964"/>
+  <dimension ref="A1:X964"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -17642,10 +17893,12 @@
     <col min="19" max="19" width="23" customWidth="1"/>
     <col min="20" max="20" width="15" customWidth="1"/>
     <col min="21" max="21" width="21" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" customWidth="1"/>
+    <col min="23" max="23" width="20.5703125" customWidth="1"/>
+    <col min="24" max="24" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4176</v>
       </c>
@@ -17712,8 +17965,14 @@
       <c r="V1" s="1" t="s">
         <v>4189</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W1" s="1" t="s">
+        <v>5579</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>5580</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -17780,8 +18039,14 @@
       <c r="V2" t="s">
         <v>1444</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W2" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>5581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -17848,8 +18113,14 @@
       <c r="V3" t="s">
         <v>4131</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W3" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>5582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -17916,8 +18187,14 @@
       <c r="V4" t="s">
         <v>1442</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W4" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>5583</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -17984,8 +18261,14 @@
       <c r="V5" t="s">
         <v>4132</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W5" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -18052,8 +18335,14 @@
       <c r="V6" t="s">
         <v>1440</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W6" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>5585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -18120,8 +18409,14 @@
       <c r="V7" t="s">
         <v>1439</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W7" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>5586</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -18188,8 +18483,14 @@
       <c r="V8" t="s">
         <v>1438</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W8" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>5587</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -18256,8 +18557,14 @@
       <c r="V9" t="s">
         <v>1437</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W9" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>5588</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -18324,8 +18631,14 @@
       <c r="V10" t="s">
         <v>1436</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W10" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>5589</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -18392,8 +18705,14 @@
       <c r="V11" t="s">
         <v>1431</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W11" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>5590</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -18460,8 +18779,14 @@
       <c r="V12" t="s">
         <v>1430</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W12" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>5591</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -18528,8 +18853,14 @@
       <c r="V13" t="s">
         <v>1429</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W13" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>5592</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -18596,8 +18927,14 @@
       <c r="V14" t="s">
         <v>1428</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W14" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>5593</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -18664,8 +19001,14 @@
       <c r="V15" t="s">
         <v>1427</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W15" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>5594</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -18732,8 +19075,14 @@
       <c r="V16" t="s">
         <v>1426</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W16" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>5595</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -18800,8 +19149,14 @@
       <c r="V17" t="s">
         <v>1425</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W17" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>5596</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -18868,8 +19223,14 @@
       <c r="V18" t="s">
         <v>1424</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W18" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>5597</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -18936,8 +19297,14 @@
       <c r="V19" t="s">
         <v>1423</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W19" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>5598</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -19004,8 +19371,14 @@
       <c r="V20" t="s">
         <v>1422</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W20" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>5599</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -19072,8 +19445,14 @@
       <c r="V21" t="s">
         <v>1421</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W21" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -19140,8 +19519,14 @@
       <c r="V22" t="s">
         <v>1420</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W22" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>5601</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -19208,8 +19593,14 @@
       <c r="V23" t="s">
         <v>1419</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W23" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>5602</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -19276,8 +19667,14 @@
       <c r="V24" t="s">
         <v>1418</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W24" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>5603</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -19344,8 +19741,14 @@
       <c r="V25" t="s">
         <v>1417</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W25" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>5604</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -19412,8 +19815,14 @@
       <c r="V26" t="s">
         <v>1416</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W26" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>5605</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -19480,8 +19889,14 @@
       <c r="V27" t="s">
         <v>1415</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W27" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>5606</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -19548,8 +19963,14 @@
       <c r="V28" t="s">
         <v>1414</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W28" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>5607</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -19616,8 +20037,14 @@
       <c r="V29" t="s">
         <v>1413</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W29" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>5608</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -19684,8 +20111,14 @@
       <c r="V30" t="s">
         <v>1412</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W30" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="X30" s="3" t="s">
+        <v>5609</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -19752,8 +20185,14 @@
       <c r="V31" t="s">
         <v>1411</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W31" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="X31" s="3" t="s">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -19820,8 +20259,14 @@
       <c r="V32" t="s">
         <v>1410</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W32" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -19888,8 +20333,14 @@
       <c r="V33" t="s">
         <v>1409</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W33" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -19956,8 +20407,14 @@
       <c r="V34" t="s">
         <v>1408</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W34" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -20024,8 +20481,14 @@
       <c r="V35" t="s">
         <v>1407</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W35" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -20092,8 +20555,14 @@
       <c r="V36" t="s">
         <v>1406</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W36" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="X36" s="3" t="s">
+        <v>5610</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -20160,8 +20629,14 @@
       <c r="V37" t="s">
         <v>1405</v>
       </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W37" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="X37" s="3" t="s">
+        <v>5611</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -20228,8 +20703,14 @@
       <c r="V38" t="s">
         <v>1404</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W38" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="X38" s="3" t="s">
+        <v>5612</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -20296,8 +20777,14 @@
       <c r="V39" t="s">
         <v>1403</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W39" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="X39" s="3" t="s">
+        <v>5613</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -20364,8 +20851,14 @@
       <c r="V40" t="s">
         <v>1402</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W40" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="X40" s="3" t="s">
+        <v>5614</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -20432,8 +20925,14 @@
       <c r="V41" t="s">
         <v>1401</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W41" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>5615</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -20500,8 +20999,14 @@
       <c r="V42" t="s">
         <v>1400</v>
       </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W42" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>5616</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -20568,8 +21073,14 @@
       <c r="V43" t="s">
         <v>2920</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W43" s="2" t="s">
+        <v>2912</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>5617</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -20636,8 +21147,14 @@
       <c r="V44" t="s">
         <v>2919</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W44" s="2" t="s">
+        <v>2911</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>5618</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -20704,8 +21221,14 @@
       <c r="V45" t="s">
         <v>2918</v>
       </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W45" s="2" t="s">
+        <v>2910</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>5619</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -20772,8 +21295,14 @@
       <c r="V46" t="s">
         <v>2917</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W46" s="2" t="s">
+        <v>2909</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>5620</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -20840,8 +21369,14 @@
       <c r="V47" t="s">
         <v>2916</v>
       </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W47" s="2" t="s">
+        <v>2908</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>5621</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -20908,8 +21443,14 @@
       <c r="V48" t="s">
         <v>2915</v>
       </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W48" s="2" t="s">
+        <v>2907</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>5622</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -20976,8 +21517,14 @@
       <c r="V49" t="s">
         <v>1393</v>
       </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W49" s="2" t="s">
+        <v>2906</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>5623</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -21044,8 +21591,14 @@
       <c r="V50" t="s">
         <v>1392</v>
       </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W50" s="2" t="s">
+        <v>2905</v>
+      </c>
+      <c r="X50" s="3" t="s">
+        <v>5624</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -21112,8 +21665,14 @@
       <c r="V51" t="s">
         <v>1391</v>
       </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W51" s="2" t="s">
+        <v>2904</v>
+      </c>
+      <c r="X51" s="3" t="s">
+        <v>5625</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -21180,8 +21739,14 @@
       <c r="V52" t="s">
         <v>1390</v>
       </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W52" s="2" t="s">
+        <v>2903</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>5626</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -21248,8 +21813,14 @@
       <c r="V53" t="s">
         <v>1389</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W53" s="2" t="s">
+        <v>2902</v>
+      </c>
+      <c r="X53" s="3" t="s">
+        <v>5627</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -21316,8 +21887,14 @@
       <c r="V54" t="s">
         <v>2914</v>
       </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W54" s="2" t="s">
+        <v>2901</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>5628</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -21384,8 +21961,14 @@
       <c r="V55" t="s">
         <v>2913</v>
       </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W55" s="2" t="s">
+        <v>2900</v>
+      </c>
+      <c r="X55" s="3" t="s">
+        <v>5629</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -21452,8 +22035,14 @@
       <c r="V56" t="s">
         <v>1386</v>
       </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W56" s="2" t="s">
+        <v>2899</v>
+      </c>
+      <c r="X56" s="3" t="s">
+        <v>5630</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -21520,8 +22109,14 @@
       <c r="V57" t="s">
         <v>1385</v>
       </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W57" s="2" t="s">
+        <v>2898</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>5631</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -21588,8 +22183,14 @@
       <c r="V58" t="s">
         <v>1384</v>
       </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W58" s="2" t="s">
+        <v>2897</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>5632</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -21656,8 +22257,14 @@
       <c r="V59" t="s">
         <v>1383</v>
       </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W59" s="2" t="s">
+        <v>2896</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>5633</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -21724,8 +22331,14 @@
       <c r="V60" t="s">
         <v>1382</v>
       </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W60" s="2" t="s">
+        <v>2895</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>5634</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -21792,8 +22405,14 @@
       <c r="V61" t="s">
         <v>1381</v>
       </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W61" s="2" t="s">
+        <v>2894</v>
+      </c>
+      <c r="X61" s="3" t="s">
+        <v>5635</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -21860,8 +22479,14 @@
       <c r="V62" t="s">
         <v>1380</v>
       </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W62" s="2" t="s">
+        <v>2893</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>5636</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -21928,8 +22553,14 @@
       <c r="V63" t="s">
         <v>1379</v>
       </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W63" s="2" t="s">
+        <v>2892</v>
+      </c>
+      <c r="X63" s="3" t="s">
+        <v>5637</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -21996,8 +22627,14 @@
       <c r="V64" t="s">
         <v>1378</v>
       </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W64" s="2" t="s">
+        <v>2891</v>
+      </c>
+      <c r="X64" s="3" t="s">
+        <v>5638</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -22064,8 +22701,14 @@
       <c r="V65" t="s">
         <v>1377</v>
       </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W65" s="2" t="s">
+        <v>2890</v>
+      </c>
+      <c r="X65" s="3" t="s">
+        <v>5639</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -22132,8 +22775,14 @@
       <c r="V66" t="s">
         <v>1376</v>
       </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W66" s="2" t="s">
+        <v>2889</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>5640</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -22200,8 +22849,14 @@
       <c r="V67" t="s">
         <v>1375</v>
       </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W67" s="2" t="s">
+        <v>2888</v>
+      </c>
+      <c r="X67" s="3" t="s">
+        <v>5641</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -22268,8 +22923,14 @@
       <c r="V68" t="s">
         <v>1374</v>
       </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W68" s="2" t="s">
+        <v>2887</v>
+      </c>
+      <c r="X68" s="3" t="s">
+        <v>5642</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -22336,8 +22997,14 @@
       <c r="V69" t="s">
         <v>1373</v>
       </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W69" s="2" t="s">
+        <v>2886</v>
+      </c>
+      <c r="X69" s="3" t="s">
+        <v>5643</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -22404,8 +23071,14 @@
       <c r="V70" t="s">
         <v>1372</v>
       </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W70" s="2" t="s">
+        <v>2885</v>
+      </c>
+      <c r="X70" s="3" t="s">
+        <v>5644</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -22472,8 +23145,14 @@
       <c r="V71" t="s">
         <v>1371</v>
       </c>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W71" s="2" t="s">
+        <v>2884</v>
+      </c>
+      <c r="X71" s="3" t="s">
+        <v>5645</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -22540,8 +23219,14 @@
       <c r="V72" t="s">
         <v>1370</v>
       </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W72" s="2" t="s">
+        <v>2883</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>5646</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -22608,8 +23293,14 @@
       <c r="V73" t="s">
         <v>1369</v>
       </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W73" s="2" t="s">
+        <v>2882</v>
+      </c>
+      <c r="X73" s="3" t="s">
+        <v>5647</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -22676,8 +23367,14 @@
       <c r="V74" t="s">
         <v>1368</v>
       </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W74" s="2" t="s">
+        <v>2881</v>
+      </c>
+      <c r="X74" s="3" t="s">
+        <v>5648</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -22744,8 +23441,14 @@
       <c r="V75" t="s">
         <v>2912</v>
       </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W75" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="X75" s="3" t="s">
+        <v>5649</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -22812,8 +23515,14 @@
       <c r="V76" t="s">
         <v>2911</v>
       </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W76" s="2" t="s">
+        <v>2235</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>5650</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -22880,8 +23589,14 @@
       <c r="V77" t="s">
         <v>2910</v>
       </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W77" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="X77" s="3" t="s">
+        <v>5651</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -22948,8 +23663,14 @@
       <c r="V78" t="s">
         <v>2909</v>
       </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W78" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="X78" s="3" t="s">
+        <v>5652</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -23016,8 +23737,14 @@
       <c r="V79" t="s">
         <v>2908</v>
       </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W79" s="2" t="s">
+        <v>3647</v>
+      </c>
+      <c r="X79" s="3" t="s">
+        <v>5653</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -23084,8 +23811,14 @@
       <c r="V80" t="s">
         <v>2907</v>
       </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W80" s="2" t="s">
+        <v>3646</v>
+      </c>
+      <c r="X80" s="3" t="s">
+        <v>5654</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -23152,8 +23885,14 @@
       <c r="V81" t="s">
         <v>2906</v>
       </c>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W81" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>5655</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -23220,8 +23959,14 @@
       <c r="V82" t="s">
         <v>2905</v>
       </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W82" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="X82" s="3" t="s">
+        <v>5656</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -23288,8 +24033,14 @@
       <c r="V83" t="s">
         <v>2904</v>
       </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W83" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>5657</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -23356,8 +24107,14 @@
       <c r="V84" t="s">
         <v>2903</v>
       </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W84" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="X84" s="3" t="s">
+        <v>5658</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -23424,8 +24181,14 @@
       <c r="V85" t="s">
         <v>2902</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W85" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="X85" s="3" t="s">
+        <v>5659</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -23492,8 +24255,14 @@
       <c r="V86" t="s">
         <v>2901</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W86" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="X86" s="3" t="s">
+        <v>5660</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -23560,8 +24329,14 @@
       <c r="V87" t="s">
         <v>2900</v>
       </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W87" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="X87" s="3" t="s">
+        <v>5661</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -23628,8 +24403,11 @@
       <c r="V88" t="s">
         <v>2899</v>
       </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W88" s="2" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -23696,8 +24474,11 @@
       <c r="V89" t="s">
         <v>2898</v>
       </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W89" s="2" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -23764,8 +24545,11 @@
       <c r="V90" t="s">
         <v>2897</v>
       </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W90" s="2" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -23832,8 +24616,11 @@
       <c r="V91" t="s">
         <v>2896</v>
       </c>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W91" s="2" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -23900,8 +24687,11 @@
       <c r="V92" t="s">
         <v>2895</v>
       </c>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W92" s="2" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -23968,8 +24758,11 @@
       <c r="V93" t="s">
         <v>2894</v>
       </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W93" s="2" t="s">
+        <v>3645</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -24036,8 +24829,11 @@
       <c r="V94" t="s">
         <v>2893</v>
       </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W94" s="2" t="s">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -24104,8 +24900,11 @@
       <c r="V95" t="s">
         <v>2892</v>
       </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W95" s="2" t="s">
+        <v>3643</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -24172,8 +24971,11 @@
       <c r="V96" t="s">
         <v>2891</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W96" s="2" t="s">
+        <v>3642</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -24240,8 +25042,11 @@
       <c r="V97" t="s">
         <v>2890</v>
       </c>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W97" s="2" t="s">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -24308,8 +25113,11 @@
       <c r="V98" t="s">
         <v>2889</v>
       </c>
-    </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W98" s="2" t="s">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>101</v>
       </c>
@@ -24376,8 +25184,11 @@
       <c r="V99" t="s">
         <v>2888</v>
       </c>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W99" s="2" t="s">
+        <v>3639</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>102</v>
       </c>
@@ -24444,8 +25255,11 @@
       <c r="V100" t="s">
         <v>2887</v>
       </c>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W100" s="2" t="s">
+        <v>3638</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>103</v>
       </c>
@@ -24512,8 +25326,11 @@
       <c r="V101" t="s">
         <v>2886</v>
       </c>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W101" s="2" t="s">
+        <v>3637</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>104</v>
       </c>
@@ -24580,8 +25397,11 @@
       <c r="V102" t="s">
         <v>2885</v>
       </c>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W102" s="2" t="s">
+        <v>3636</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -24648,8 +25468,11 @@
       <c r="V103" t="s">
         <v>2884</v>
       </c>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W103" s="2" t="s">
+        <v>3635</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>106</v>
       </c>
@@ -24716,8 +25539,11 @@
       <c r="V104" t="s">
         <v>2883</v>
       </c>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W104" s="2" t="s">
+        <v>3634</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>107</v>
       </c>
@@ -24784,8 +25610,11 @@
       <c r="V105" t="s">
         <v>2882</v>
       </c>
-    </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W105" s="2" t="s">
+        <v>3633</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>108</v>
       </c>
@@ -24852,8 +25681,11 @@
       <c r="V106" t="s">
         <v>2881</v>
       </c>
-    </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W106" s="2" t="s">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>109</v>
       </c>
@@ -24920,8 +25752,11 @@
       <c r="V107" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W107" s="2" t="s">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>110</v>
       </c>
@@ -24988,8 +25823,11 @@
       <c r="V108" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W108" s="2" t="s">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>111</v>
       </c>
@@ -25056,8 +25894,11 @@
       <c r="V109" t="s">
         <v>1333</v>
       </c>
-    </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W109" s="2" t="s">
+        <v>3629</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>112</v>
       </c>
@@ -25124,8 +25965,11 @@
       <c r="V110" t="s">
         <v>1331</v>
       </c>
-    </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W110" s="2" t="s">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>113</v>
       </c>
@@ -25192,8 +26036,11 @@
       <c r="V111" t="s">
         <v>1329</v>
       </c>
-    </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W111" s="2" t="s">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -25260,8 +26107,11 @@
       <c r="V112" t="s">
         <v>1328</v>
       </c>
-    </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W112" s="2" t="s">
+        <v>3626</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -25328,8 +26178,11 @@
       <c r="V113" t="s">
         <v>1327</v>
       </c>
-    </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W113" s="2" t="s">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -25396,8 +26249,11 @@
       <c r="V114" t="s">
         <v>1326</v>
       </c>
-    </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W114" s="2" t="s">
+        <v>3624</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -25464,8 +26320,11 @@
       <c r="V115" t="s">
         <v>1325</v>
       </c>
-    </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W115" s="2" t="s">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -25532,8 +26391,11 @@
       <c r="V116" t="s">
         <v>1324</v>
       </c>
-    </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W116" s="2" t="s">
+        <v>3622</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>119</v>
       </c>
@@ -25600,8 +26462,11 @@
       <c r="V117" t="s">
         <v>1323</v>
       </c>
-    </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W117" s="2" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -25668,8 +26533,11 @@
       <c r="V118" t="s">
         <v>1322</v>
       </c>
-    </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W118" s="2" t="s">
+        <v>3620</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -25736,8 +26604,11 @@
       <c r="V119" t="s">
         <v>1321</v>
       </c>
-    </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W119" s="2" t="s">
+        <v>3619</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>122</v>
       </c>
@@ -25804,8 +26675,11 @@
       <c r="V120" t="s">
         <v>1320</v>
       </c>
-    </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W120" s="2" t="s">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>123</v>
       </c>
@@ -25872,8 +26746,11 @@
       <c r="V121" t="s">
         <v>1319</v>
       </c>
-    </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W121" s="2" t="s">
+        <v>3617</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>124</v>
       </c>
@@ -25940,8 +26817,11 @@
       <c r="V122" t="s">
         <v>2235</v>
       </c>
-    </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W122" s="2" t="s">
+        <v>3616</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>125</v>
       </c>
@@ -26008,8 +26888,11 @@
       <c r="V123" t="s">
         <v>4190</v>
       </c>
-    </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W123" s="2" t="s">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>126</v>
       </c>
@@ -26076,8 +26959,11 @@
       <c r="V124" t="s">
         <v>4191</v>
       </c>
-    </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W124" s="2" t="s">
+        <v>3614</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>127</v>
       </c>
@@ -26144,8 +27030,11 @@
       <c r="V125" t="s">
         <v>4192</v>
       </c>
-    </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W125" s="2" t="s">
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>128</v>
       </c>
@@ -26212,8 +27101,11 @@
       <c r="V126" t="s">
         <v>4193</v>
       </c>
-    </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W126" s="2" t="s">
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>129</v>
       </c>
@@ -26280,8 +27172,11 @@
       <c r="V127" t="s">
         <v>4194</v>
       </c>
-    </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W127" s="2" t="s">
+        <v>3611</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>130</v>
       </c>
@@ -26348,8 +27243,11 @@
       <c r="V128" t="s">
         <v>4195</v>
       </c>
-    </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W128" s="2" t="s">
+        <v>3610</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>131</v>
       </c>
@@ -26416,8 +27314,11 @@
       <c r="V129" t="s">
         <v>4196</v>
       </c>
-    </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W129" s="2" t="s">
+        <v>3609</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>132</v>
       </c>
@@ -26484,8 +27385,11 @@
       <c r="V130" t="s">
         <v>4197</v>
       </c>
-    </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W130" s="2" t="s">
+        <v>3608</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>133</v>
       </c>
@@ -26552,8 +27456,11 @@
       <c r="V131" t="s">
         <v>4198</v>
       </c>
-    </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W131" s="2" t="s">
+        <v>3607</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>134</v>
       </c>
@@ -26620,8 +27527,11 @@
       <c r="V132" t="s">
         <v>4199</v>
       </c>
-    </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W132" s="2" t="s">
+        <v>3606</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>135</v>
       </c>
@@ -26688,8 +27598,11 @@
       <c r="V133" t="s">
         <v>4200</v>
       </c>
-    </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W133" s="2" t="s">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>136</v>
       </c>
@@ -26756,8 +27669,11 @@
       <c r="V134" t="s">
         <v>4201</v>
       </c>
-    </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W134" s="2" t="s">
+        <v>3604</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>137</v>
       </c>
@@ -26824,8 +27740,11 @@
       <c r="V135" t="s">
         <v>4202</v>
       </c>
-    </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W135" s="2" t="s">
+        <v>3603</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>138</v>
       </c>
@@ -26889,8 +27808,11 @@
       <c r="V136" t="s">
         <v>4203</v>
       </c>
-    </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W136" s="2" t="s">
+        <v>3602</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -26954,8 +27876,11 @@
       <c r="V137" t="s">
         <v>4204</v>
       </c>
-    </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W137" s="2" t="s">
+        <v>3601</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -27019,8 +27944,11 @@
       <c r="V138" t="s">
         <v>4205</v>
       </c>
-    </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W138" s="2" t="s">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>141</v>
       </c>
@@ -27084,8 +28012,11 @@
       <c r="V139" t="s">
         <v>4206</v>
       </c>
-    </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W139" s="2" t="s">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -27149,8 +28080,11 @@
       <c r="V140" t="s">
         <v>4207</v>
       </c>
-    </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W140" s="2" t="s">
+        <v>3598</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>143</v>
       </c>
@@ -27214,8 +28148,11 @@
       <c r="V141" t="s">
         <v>4208</v>
       </c>
-    </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W141" s="2" t="s">
+        <v>3597</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>144</v>
       </c>
@@ -27279,8 +28216,11 @@
       <c r="V142" t="s">
         <v>4209</v>
       </c>
-    </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W142" s="2" t="s">
+        <v>3596</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>145</v>
       </c>
@@ -27344,8 +28284,11 @@
       <c r="V143" t="s">
         <v>4210</v>
       </c>
-    </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W143" s="2" t="s">
+        <v>3595</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>146</v>
       </c>
@@ -27409,8 +28352,11 @@
       <c r="V144" t="s">
         <v>4211</v>
       </c>
-    </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W144" s="2" t="s">
+        <v>3594</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>147</v>
       </c>
@@ -27474,8 +28420,11 @@
       <c r="V145" t="s">
         <v>4212</v>
       </c>
-    </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W145" s="2" t="s">
+        <v>3593</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>148</v>
       </c>
@@ -27539,8 +28488,11 @@
       <c r="V146" t="s">
         <v>4213</v>
       </c>
-    </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W146" s="2" t="s">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>149</v>
       </c>
@@ -27604,8 +28556,11 @@
       <c r="V147" t="s">
         <v>4214</v>
       </c>
-    </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W147" s="2" t="s">
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -27669,8 +28624,11 @@
       <c r="V148" t="s">
         <v>4215</v>
       </c>
-    </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W148" s="2" t="s">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>151</v>
       </c>
@@ -27734,8 +28692,11 @@
       <c r="V149" t="s">
         <v>4216</v>
       </c>
-    </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W149" s="2" t="s">
+        <v>3589</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>152</v>
       </c>
@@ -27799,8 +28760,11 @@
       <c r="V150" t="s">
         <v>4217</v>
       </c>
-    </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W150" s="2" t="s">
+        <v>3588</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>153</v>
       </c>
@@ -27864,8 +28828,11 @@
       <c r="V151" t="s">
         <v>4218</v>
       </c>
-    </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W151" s="2" t="s">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>154</v>
       </c>
@@ -27929,8 +28896,11 @@
       <c r="V152" t="s">
         <v>4219</v>
       </c>
-    </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W152" s="2" t="s">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>155</v>
       </c>
@@ -27994,8 +28964,11 @@
       <c r="V153" t="s">
         <v>4220</v>
       </c>
-    </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W153" s="2" t="s">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>156</v>
       </c>
@@ -28059,8 +29032,11 @@
       <c r="V154" t="s">
         <v>4221</v>
       </c>
-    </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W154" s="2" t="s">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>157</v>
       </c>
@@ -28124,8 +29100,11 @@
       <c r="V155" t="s">
         <v>4222</v>
       </c>
-    </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W155" s="2" t="s">
+        <v>3583</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>158</v>
       </c>
@@ -28189,8 +29168,11 @@
       <c r="V156" t="s">
         <v>4223</v>
       </c>
-    </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W156" s="2" t="s">
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>159</v>
       </c>
@@ -28254,8 +29236,11 @@
       <c r="V157" t="s">
         <v>4224</v>
       </c>
-    </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W157" s="2" t="s">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>160</v>
       </c>
@@ -28319,8 +29304,11 @@
       <c r="V158" t="s">
         <v>4225</v>
       </c>
-    </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W158" s="2" t="s">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>161</v>
       </c>
@@ -28384,8 +29372,11 @@
       <c r="V159" t="s">
         <v>4226</v>
       </c>
-    </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W159" s="2" t="s">
+        <v>3579</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -28449,8 +29440,11 @@
       <c r="V160" t="s">
         <v>4227</v>
       </c>
-    </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W160" s="2" t="s">
+        <v>3578</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>163</v>
       </c>
@@ -28514,8 +29508,11 @@
       <c r="V161" t="s">
         <v>4228</v>
       </c>
-    </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W161" s="2" t="s">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>164</v>
       </c>
@@ -28579,8 +29576,11 @@
       <c r="V162" t="s">
         <v>4229</v>
       </c>
-    </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W162" s="2" t="s">
+        <v>3576</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>165</v>
       </c>
@@ -28644,8 +29644,11 @@
       <c r="V163" t="s">
         <v>4230</v>
       </c>
-    </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W163" s="2" t="s">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>166</v>
       </c>
@@ -28709,8 +29712,11 @@
       <c r="V164" t="s">
         <v>4231</v>
       </c>
-    </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W164" s="2" t="s">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>167</v>
       </c>
@@ -28774,8 +29780,11 @@
       <c r="V165" t="s">
         <v>4232</v>
       </c>
-    </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W165" s="2" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>168</v>
       </c>
@@ -28839,8 +29848,11 @@
       <c r="V166" t="s">
         <v>4233</v>
       </c>
-    </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W166" s="2" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>169</v>
       </c>
@@ -28904,8 +29916,11 @@
       <c r="V167" t="s">
         <v>4234</v>
       </c>
-    </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W167" s="2" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>170</v>
       </c>
@@ -28969,8 +29984,11 @@
       <c r="V168" t="s">
         <v>4235</v>
       </c>
-    </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W168" s="2" t="s">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>171</v>
       </c>
@@ -29034,8 +30052,11 @@
       <c r="V169" t="s">
         <v>4236</v>
       </c>
-    </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W169" s="2" t="s">
+        <v>3569</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>172</v>
       </c>
@@ -29099,8 +30120,11 @@
       <c r="V170" t="s">
         <v>4237</v>
       </c>
-    </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W170" s="2" t="s">
+        <v>3568</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>173</v>
       </c>
@@ -29164,8 +30188,11 @@
       <c r="V171" t="s">
         <v>4238</v>
       </c>
-    </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W171" s="2" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>174</v>
       </c>
@@ -29229,8 +30256,11 @@
       <c r="V172" t="s">
         <v>4239</v>
       </c>
-    </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W172" s="2" t="s">
+        <v>3566</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>175</v>
       </c>
@@ -29294,8 +30324,11 @@
       <c r="V173" t="s">
         <v>4240</v>
       </c>
-    </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W173" s="2" t="s">
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>176</v>
       </c>
@@ -29359,8 +30392,11 @@
       <c r="V174" t="s">
         <v>4241</v>
       </c>
-    </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W174" s="2" t="s">
+        <v>3564</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>177</v>
       </c>
@@ -29424,8 +30460,11 @@
       <c r="V175" t="s">
         <v>4242</v>
       </c>
-    </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W175" s="2" t="s">
+        <v>3563</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>178</v>
       </c>
@@ -29489,8 +30528,11 @@
       <c r="V176" t="s">
         <v>4243</v>
       </c>
-    </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W176" s="2" t="s">
+        <v>3562</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>179</v>
       </c>
@@ -29554,8 +30596,11 @@
       <c r="V177" t="s">
         <v>4244</v>
       </c>
-    </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W177" s="2" t="s">
+        <v>3561</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>180</v>
       </c>
@@ -29619,8 +30664,11 @@
       <c r="V178" t="s">
         <v>4245</v>
       </c>
-    </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W178" s="2" t="s">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>181</v>
       </c>
@@ -29684,8 +30732,11 @@
       <c r="V179" t="s">
         <v>4246</v>
       </c>
-    </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W179" s="2" t="s">
+        <v>3559</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>182</v>
       </c>
@@ -29749,8 +30800,11 @@
       <c r="V180" t="s">
         <v>4247</v>
       </c>
-    </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W180" s="2" t="s">
+        <v>3558</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>183</v>
       </c>
@@ -29814,8 +30868,11 @@
       <c r="V181" t="s">
         <v>4248</v>
       </c>
-    </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W181" s="2" t="s">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>184</v>
       </c>
@@ -29879,8 +30936,11 @@
       <c r="V182" t="s">
         <v>4249</v>
       </c>
-    </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W182" s="2" t="s">
+        <v>3556</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>185</v>
       </c>
@@ -29944,8 +31004,11 @@
       <c r="V183" t="s">
         <v>4250</v>
       </c>
-    </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W183" s="2" t="s">
+        <v>3555</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>186</v>
       </c>
@@ -30009,8 +31072,11 @@
       <c r="V184" t="s">
         <v>1250</v>
       </c>
-    </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W184" s="2" t="s">
+        <v>3554</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>187</v>
       </c>
@@ -30074,8 +31140,11 @@
       <c r="V185" t="s">
         <v>1249</v>
       </c>
-    </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W185" s="2" t="s">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>188</v>
       </c>
@@ -30139,8 +31208,11 @@
       <c r="V186" t="s">
         <v>1248</v>
       </c>
-    </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W186" s="2" t="s">
+        <v>3552</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>189</v>
       </c>
@@ -30204,8 +31276,11 @@
       <c r="V187" t="s">
         <v>1246</v>
       </c>
-    </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W187" s="2" t="s">
+        <v>3551</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>190</v>
       </c>
@@ -30269,8 +31344,11 @@
       <c r="V188" t="s">
         <v>1244</v>
       </c>
-    </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W188" s="2" t="s">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>191</v>
       </c>
@@ -30334,8 +31412,11 @@
       <c r="V189" t="s">
         <v>1243</v>
       </c>
-    </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W189" s="2" t="s">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>192</v>
       </c>
@@ -30399,8 +31480,11 @@
       <c r="V190" t="s">
         <v>1242</v>
       </c>
-    </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W190" s="2" t="s">
+        <v>3548</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>193</v>
       </c>
@@ -30464,8 +31548,11 @@
       <c r="V191" t="s">
         <v>1241</v>
       </c>
-    </row>
-    <row r="192" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W191" s="2" t="s">
+        <v>3547</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>194</v>
       </c>
@@ -30529,8 +31616,11 @@
       <c r="V192" t="s">
         <v>1240</v>
       </c>
-    </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W192" s="2" t="s">
+        <v>3546</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>195</v>
       </c>
@@ -30594,8 +31684,11 @@
       <c r="V193" t="s">
         <v>1239</v>
       </c>
-    </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W193" s="2" t="s">
+        <v>3545</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>196</v>
       </c>
@@ -30659,8 +31752,11 @@
       <c r="V194" t="s">
         <v>1238</v>
       </c>
-    </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W194" s="2" t="s">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>197</v>
       </c>
@@ -30724,8 +31820,11 @@
       <c r="V195" t="s">
         <v>1237</v>
       </c>
-    </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W195" s="2" t="s">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>198</v>
       </c>
@@ -30789,8 +31888,11 @@
       <c r="V196" t="s">
         <v>1236</v>
       </c>
-    </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W196" s="2" t="s">
+        <v>3542</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -30854,8 +31956,11 @@
       <c r="V197" t="s">
         <v>1235</v>
       </c>
-    </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W197" s="2" t="s">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>200</v>
       </c>
@@ -30919,8 +32024,11 @@
       <c r="V198" t="s">
         <v>1234</v>
       </c>
-    </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W198" s="2" t="s">
+        <v>3540</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>201</v>
       </c>
@@ -30984,8 +32092,11 @@
       <c r="V199" t="s">
         <v>1233</v>
       </c>
-    </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W199" s="2" t="s">
+        <v>3539</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>202</v>
       </c>
@@ -31049,8 +32160,11 @@
       <c r="V200" t="s">
         <v>4251</v>
       </c>
-    </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W200" s="2" t="s">
+        <v>3538</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>203</v>
       </c>
@@ -31111,8 +32225,11 @@
       <c r="V201" t="s">
         <v>4252</v>
       </c>
-    </row>
-    <row r="202" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W201" s="2" t="s">
+        <v>3537</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>204</v>
       </c>
@@ -31173,8 +32290,11 @@
       <c r="V202" t="s">
         <v>4253</v>
       </c>
-    </row>
-    <row r="203" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W202" s="2" t="s">
+        <v>3536</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>205</v>
       </c>
@@ -31235,8 +32355,11 @@
       <c r="V203" t="s">
         <v>4254</v>
       </c>
-    </row>
-    <row r="204" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W203" s="2" t="s">
+        <v>3535</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>206</v>
       </c>
@@ -31297,8 +32420,11 @@
       <c r="V204" t="s">
         <v>4255</v>
       </c>
-    </row>
-    <row r="205" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W204" s="2" t="s">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>207</v>
       </c>
@@ -31359,8 +32485,11 @@
       <c r="V205" t="s">
         <v>4256</v>
       </c>
-    </row>
-    <row r="206" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W205" s="2" t="s">
+        <v>3533</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>208</v>
       </c>
@@ -31421,8 +32550,11 @@
       <c r="V206" t="s">
         <v>4257</v>
       </c>
-    </row>
-    <row r="207" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W206" s="2" t="s">
+        <v>3532</v>
+      </c>
+    </row>
+    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>209</v>
       </c>
@@ -31483,8 +32615,11 @@
       <c r="V207" t="s">
         <v>4258</v>
       </c>
-    </row>
-    <row r="208" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W207" s="2" t="s">
+        <v>3531</v>
+      </c>
+    </row>
+    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>210</v>
       </c>
@@ -31545,8 +32680,11 @@
       <c r="V208" t="s">
         <v>4259</v>
       </c>
-    </row>
-    <row r="209" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W208" s="2" t="s">
+        <v>3530</v>
+      </c>
+    </row>
+    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>211</v>
       </c>
@@ -31607,8 +32745,11 @@
       <c r="V209" t="s">
         <v>4260</v>
       </c>
-    </row>
-    <row r="210" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W209" s="2" t="s">
+        <v>3529</v>
+      </c>
+    </row>
+    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>212</v>
       </c>
@@ -31669,8 +32810,11 @@
       <c r="V210" t="s">
         <v>4261</v>
       </c>
-    </row>
-    <row r="211" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W210" s="2" t="s">
+        <v>3528</v>
+      </c>
+    </row>
+    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>213</v>
       </c>
@@ -31731,8 +32875,11 @@
       <c r="V211" t="s">
         <v>4262</v>
       </c>
-    </row>
-    <row r="212" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W211" s="2" t="s">
+        <v>3527</v>
+      </c>
+    </row>
+    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>214</v>
       </c>
@@ -31793,8 +32940,11 @@
       <c r="V212" t="s">
         <v>4263</v>
       </c>
-    </row>
-    <row r="213" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W212" s="2" t="s">
+        <v>3526</v>
+      </c>
+    </row>
+    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>215</v>
       </c>
@@ -31855,8 +33005,11 @@
       <c r="V213" t="s">
         <v>4264</v>
       </c>
-    </row>
-    <row r="214" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W213" s="2" t="s">
+        <v>3525</v>
+      </c>
+    </row>
+    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>216</v>
       </c>
@@ -31917,8 +33070,11 @@
       <c r="V214" t="s">
         <v>4265</v>
       </c>
-    </row>
-    <row r="215" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W214" s="2" t="s">
+        <v>3524</v>
+      </c>
+    </row>
+    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>217</v>
       </c>
@@ -31979,8 +33135,11 @@
       <c r="V215" t="s">
         <v>4266</v>
       </c>
-    </row>
-    <row r="216" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W215" s="2" t="s">
+        <v>3523</v>
+      </c>
+    </row>
+    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>218</v>
       </c>
@@ -32041,8 +33200,11 @@
       <c r="V216" t="s">
         <v>4267</v>
       </c>
-    </row>
-    <row r="217" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W216" s="2" t="s">
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>219</v>
       </c>
@@ -32103,8 +33265,11 @@
       <c r="V217" t="s">
         <v>4268</v>
       </c>
-    </row>
-    <row r="218" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W217" s="2" t="s">
+        <v>3521</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>220</v>
       </c>
@@ -32165,8 +33330,11 @@
       <c r="V218" t="s">
         <v>4269</v>
       </c>
-    </row>
-    <row r="219" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W218" s="2" t="s">
+        <v>3520</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>221</v>
       </c>
@@ -32227,8 +33395,11 @@
       <c r="V219" t="s">
         <v>4270</v>
       </c>
-    </row>
-    <row r="220" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W219" s="2" t="s">
+        <v>3519</v>
+      </c>
+    </row>
+    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>222</v>
       </c>
@@ -32289,8 +33460,11 @@
       <c r="V220" t="s">
         <v>4271</v>
       </c>
-    </row>
-    <row r="221" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W220" s="2" t="s">
+        <v>3518</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>223</v>
       </c>
@@ -32351,8 +33525,11 @@
       <c r="V221" t="s">
         <v>4272</v>
       </c>
-    </row>
-    <row r="222" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W221" s="2" t="s">
+        <v>3517</v>
+      </c>
+    </row>
+    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>224</v>
       </c>
@@ -32413,8 +33590,11 @@
       <c r="V222" t="s">
         <v>4273</v>
       </c>
-    </row>
-    <row r="223" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W222" s="2" t="s">
+        <v>3516</v>
+      </c>
+    </row>
+    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>225</v>
       </c>
@@ -32475,8 +33655,11 @@
       <c r="V223" t="s">
         <v>4274</v>
       </c>
-    </row>
-    <row r="224" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W223" s="2" t="s">
+        <v>3515</v>
+      </c>
+    </row>
+    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>226</v>
       </c>
@@ -32537,8 +33720,11 @@
       <c r="V224" t="s">
         <v>4275</v>
       </c>
-    </row>
-    <row r="225" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W224" s="2" t="s">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>227</v>
       </c>
@@ -32599,8 +33785,11 @@
       <c r="V225" t="s">
         <v>4276</v>
       </c>
-    </row>
-    <row r="226" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W225" s="2" t="s">
+        <v>3513</v>
+      </c>
+    </row>
+    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>228</v>
       </c>
@@ -32661,8 +33850,11 @@
       <c r="V226" t="s">
         <v>4277</v>
       </c>
-    </row>
-    <row r="227" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W226" s="2" t="s">
+        <v>3512</v>
+      </c>
+    </row>
+    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>229</v>
       </c>
@@ -32723,8 +33915,11 @@
       <c r="V227" t="s">
         <v>4278</v>
       </c>
-    </row>
-    <row r="228" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W227" s="2" t="s">
+        <v>3511</v>
+      </c>
+    </row>
+    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>230</v>
       </c>
@@ -32785,8 +33980,11 @@
       <c r="V228" t="s">
         <v>4279</v>
       </c>
-    </row>
-    <row r="229" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W228" s="2" t="s">
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>231</v>
       </c>
@@ -32847,8 +34045,11 @@
       <c r="V229" t="s">
         <v>4280</v>
       </c>
-    </row>
-    <row r="230" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W229" s="2" t="s">
+        <v>3509</v>
+      </c>
+    </row>
+    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>232</v>
       </c>
@@ -32909,8 +34110,11 @@
       <c r="V230" t="s">
         <v>4281</v>
       </c>
-    </row>
-    <row r="231" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W230" s="2" t="s">
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>233</v>
       </c>
@@ -32971,8 +34175,11 @@
       <c r="V231" t="s">
         <v>4282</v>
       </c>
-    </row>
-    <row r="232" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W231" s="2" t="s">
+        <v>3507</v>
+      </c>
+    </row>
+    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>234</v>
       </c>
@@ -33033,8 +34240,11 @@
       <c r="V232" t="s">
         <v>4283</v>
       </c>
-    </row>
-    <row r="233" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W232" s="2" t="s">
+        <v>3506</v>
+      </c>
+    </row>
+    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>235</v>
       </c>
@@ -33095,8 +34305,11 @@
       <c r="V233" t="s">
         <v>4284</v>
       </c>
-    </row>
-    <row r="234" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W233" s="2" t="s">
+        <v>3505</v>
+      </c>
+    </row>
+    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>236</v>
       </c>
@@ -33157,8 +34370,11 @@
       <c r="V234" t="s">
         <v>4285</v>
       </c>
-    </row>
-    <row r="235" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W234" s="2" t="s">
+        <v>3504</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>237</v>
       </c>
@@ -33219,8 +34435,11 @@
       <c r="V235" t="s">
         <v>4286</v>
       </c>
-    </row>
-    <row r="236" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W235" s="2" t="s">
+        <v>3503</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>238</v>
       </c>
@@ -33281,8 +34500,11 @@
       <c r="V236" t="s">
         <v>4287</v>
       </c>
-    </row>
-    <row r="237" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W236" s="2" t="s">
+        <v>3502</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>239</v>
       </c>
@@ -33343,8 +34565,11 @@
       <c r="V237" t="s">
         <v>4288</v>
       </c>
-    </row>
-    <row r="238" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W237" s="2" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>240</v>
       </c>
@@ -33405,8 +34630,11 @@
       <c r="V238" t="s">
         <v>4289</v>
       </c>
-    </row>
-    <row r="239" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W238" s="2" t="s">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>241</v>
       </c>
@@ -33467,8 +34695,11 @@
       <c r="V239" t="s">
         <v>4290</v>
       </c>
-    </row>
-    <row r="240" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W239" s="2" t="s">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>242</v>
       </c>
@@ -33529,8 +34760,11 @@
       <c r="V240" t="s">
         <v>4291</v>
       </c>
-    </row>
-    <row r="241" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W240" s="2" t="s">
+        <v>3498</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>243</v>
       </c>
@@ -33591,8 +34825,11 @@
       <c r="V241" t="s">
         <v>4292</v>
       </c>
-    </row>
-    <row r="242" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W241" s="2" t="s">
+        <v>3497</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>244</v>
       </c>
@@ -33653,8 +34890,11 @@
       <c r="V242" t="s">
         <v>4293</v>
       </c>
-    </row>
-    <row r="243" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W242" s="2" t="s">
+        <v>3496</v>
+      </c>
+    </row>
+    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>245</v>
       </c>
@@ -33715,8 +34955,11 @@
       <c r="V243" t="s">
         <v>4294</v>
       </c>
-    </row>
-    <row r="244" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W243" s="2" t="s">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>246</v>
       </c>
@@ -33777,8 +35020,11 @@
       <c r="V244" t="s">
         <v>4295</v>
       </c>
-    </row>
-    <row r="245" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W244" s="2" t="s">
+        <v>3494</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>247</v>
       </c>
@@ -33839,8 +35085,11 @@
       <c r="V245" t="s">
         <v>4296</v>
       </c>
-    </row>
-    <row r="246" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W245" s="2" t="s">
+        <v>3493</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>248</v>
       </c>
@@ -33901,8 +35150,11 @@
       <c r="V246" t="s">
         <v>4297</v>
       </c>
-    </row>
-    <row r="247" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W246" s="2" t="s">
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>249</v>
       </c>
@@ -33963,8 +35215,11 @@
       <c r="V247" t="s">
         <v>4298</v>
       </c>
-    </row>
-    <row r="248" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W247" s="2" t="s">
+        <v>3491</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>250</v>
       </c>
@@ -34025,8 +35280,11 @@
       <c r="V248" t="s">
         <v>4299</v>
       </c>
-    </row>
-    <row r="249" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W248" s="2" t="s">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>251</v>
       </c>
@@ -34087,8 +35345,11 @@
       <c r="V249" t="s">
         <v>4300</v>
       </c>
-    </row>
-    <row r="250" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W249" s="2" t="s">
+        <v>3489</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>252</v>
       </c>
@@ -34149,8 +35410,11 @@
       <c r="V250" t="s">
         <v>4301</v>
       </c>
-    </row>
-    <row r="251" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W250" s="2" t="s">
+        <v>3488</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>253</v>
       </c>
@@ -34211,8 +35475,11 @@
       <c r="V251" t="s">
         <v>4302</v>
       </c>
-    </row>
-    <row r="252" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W251" s="2" t="s">
+        <v>3487</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>254</v>
       </c>
@@ -34273,8 +35540,11 @@
       <c r="V252" t="s">
         <v>4303</v>
       </c>
-    </row>
-    <row r="253" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W252" s="2" t="s">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>255</v>
       </c>
@@ -34335,8 +35605,11 @@
       <c r="V253" t="s">
         <v>4304</v>
       </c>
-    </row>
-    <row r="254" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W253" s="2" t="s">
+        <v>3485</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>256</v>
       </c>
@@ -34397,8 +35670,11 @@
       <c r="V254" t="s">
         <v>4305</v>
       </c>
-    </row>
-    <row r="255" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W254" s="2" t="s">
+        <v>3484</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>256</v>
       </c>
@@ -34459,8 +35735,11 @@
       <c r="V255" t="s">
         <v>4306</v>
       </c>
-    </row>
-    <row r="256" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W255" s="2" t="s">
+        <v>3483</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>257</v>
       </c>
@@ -34521,8 +35800,11 @@
       <c r="V256" t="s">
         <v>4307</v>
       </c>
-    </row>
-    <row r="257" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W256" s="2" t="s">
+        <v>3482</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>257</v>
       </c>
@@ -34583,8 +35865,11 @@
       <c r="V257" t="s">
         <v>4308</v>
       </c>
-    </row>
-    <row r="258" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W257" s="2" t="s">
+        <v>3481</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>258</v>
       </c>
@@ -34645,8 +35930,11 @@
       <c r="V258" t="s">
         <v>4309</v>
       </c>
-    </row>
-    <row r="259" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W258" s="2" t="s">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>259</v>
       </c>
@@ -34707,8 +35995,11 @@
       <c r="V259" t="s">
         <v>4310</v>
       </c>
-    </row>
-    <row r="260" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W259" s="2" t="s">
+        <v>3479</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>260</v>
       </c>
@@ -34769,8 +36060,11 @@
       <c r="V260" t="s">
         <v>4311</v>
       </c>
-    </row>
-    <row r="261" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W260" s="2" t="s">
+        <v>3478</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>261</v>
       </c>
@@ -34831,8 +36125,11 @@
       <c r="V261" t="s">
         <v>1166</v>
       </c>
-    </row>
-    <row r="262" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W261" s="2" t="s">
+        <v>3477</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>262</v>
       </c>
@@ -34893,8 +36190,11 @@
       <c r="V262" t="s">
         <v>1165</v>
       </c>
-    </row>
-    <row r="263" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W262" s="2" t="s">
+        <v>3476</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>263</v>
       </c>
@@ -34955,8 +36255,11 @@
       <c r="V263" t="s">
         <v>1164</v>
       </c>
-    </row>
-    <row r="264" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W263" s="2" t="s">
+        <v>3475</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>264</v>
       </c>
@@ -35017,8 +36320,11 @@
       <c r="V264" t="s">
         <v>1162</v>
       </c>
-    </row>
-    <row r="265" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W264" s="2" t="s">
+        <v>3474</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>265</v>
       </c>
@@ -35079,8 +36385,11 @@
       <c r="V265" t="s">
         <v>1160</v>
       </c>
-    </row>
-    <row r="266" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W265" s="2" t="s">
+        <v>3473</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>266</v>
       </c>
@@ -35141,8 +36450,11 @@
       <c r="V266" t="s">
         <v>1159</v>
       </c>
-    </row>
-    <row r="267" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W266" s="2" t="s">
+        <v>3472</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>267</v>
       </c>
@@ -35203,8 +36515,11 @@
       <c r="V267" t="s">
         <v>1158</v>
       </c>
-    </row>
-    <row r="268" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W267" s="2" t="s">
+        <v>3471</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>268</v>
       </c>
@@ -35265,8 +36580,11 @@
       <c r="V268" t="s">
         <v>1157</v>
       </c>
-    </row>
-    <row r="269" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W268" s="2" t="s">
+        <v>3470</v>
+      </c>
+    </row>
+    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>269</v>
       </c>
@@ -35327,8 +36645,11 @@
       <c r="V269" t="s">
         <v>1156</v>
       </c>
-    </row>
-    <row r="270" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W269" s="2" t="s">
+        <v>3469</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>270</v>
       </c>
@@ -35389,8 +36710,11 @@
       <c r="V270" t="s">
         <v>1155</v>
       </c>
-    </row>
-    <row r="271" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W270" s="2" t="s">
+        <v>3468</v>
+      </c>
+    </row>
+    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>271</v>
       </c>
@@ -35451,8 +36775,11 @@
       <c r="V271" t="s">
         <v>1154</v>
       </c>
-    </row>
-    <row r="272" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W271" s="2" t="s">
+        <v>3467</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>272</v>
       </c>
@@ -35513,8 +36840,11 @@
       <c r="V272" t="s">
         <v>1153</v>
       </c>
-    </row>
-    <row r="273" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W272" s="2" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>273</v>
       </c>
@@ -35575,8 +36905,11 @@
       <c r="V273" t="s">
         <v>1152</v>
       </c>
-    </row>
-    <row r="274" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W273" s="2" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>274</v>
       </c>
@@ -35637,8 +36970,11 @@
       <c r="V274" t="s">
         <v>1151</v>
       </c>
-    </row>
-    <row r="275" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W274" s="2" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>275</v>
       </c>
@@ -35699,8 +37035,11 @@
       <c r="V275" t="s">
         <v>1150</v>
       </c>
-    </row>
-    <row r="276" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W275" s="2" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>276</v>
       </c>
@@ -35762,7 +37101,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="277" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>277</v>
       </c>
@@ -35824,7 +37163,7 @@
         <v>4312</v>
       </c>
     </row>
-    <row r="278" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>278</v>
       </c>
@@ -35886,7 +37225,7 @@
         <v>4313</v>
       </c>
     </row>
-    <row r="279" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>279</v>
       </c>
@@ -35948,7 +37287,7 @@
         <v>4314</v>
       </c>
     </row>
-    <row r="280" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>280</v>
       </c>
@@ -36010,7 +37349,7 @@
         <v>4315</v>
       </c>
     </row>
-    <row r="281" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>281</v>
       </c>
@@ -36072,7 +37411,7 @@
         <v>4316</v>
       </c>
     </row>
-    <row r="282" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>282</v>
       </c>
@@ -36134,7 +37473,7 @@
         <v>4317</v>
       </c>
     </row>
-    <row r="283" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>283</v>
       </c>
@@ -36196,7 +37535,7 @@
         <v>4318</v>
       </c>
     </row>
-    <row r="284" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>284</v>
       </c>
@@ -36255,7 +37594,7 @@
         <v>4319</v>
       </c>
     </row>
-    <row r="285" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>285</v>
       </c>
@@ -36314,7 +37653,7 @@
         <v>4320</v>
       </c>
     </row>
-    <row r="286" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>286</v>
       </c>
@@ -36373,7 +37712,7 @@
         <v>4321</v>
       </c>
     </row>
-    <row r="287" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>287</v>
       </c>
@@ -36432,7 +37771,7 @@
         <v>4322</v>
       </c>
     </row>
-    <row r="288" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>287</v>
       </c>

--- a/Excel/Allplanttaglist.xlsx
+++ b/Excel/Allplanttaglist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel-Files\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F773185-AE79-474B-93AA-72584906CC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F6D32C-E68A-4461-85D9-8134B536F943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{0DFC0680-056B-49A9-993E-B17935078FFA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14246" uniqueCount="5662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14654" uniqueCount="5663">
   <si>
     <t>CSPPL</t>
   </si>
@@ -17020,6 +17020,9 @@
   </si>
   <si>
     <t>SLDC_SERVER2_ON</t>
+  </si>
+  <si>
+    <t>MIS</t>
   </si>
 </sst>
 </file>
@@ -17510,11 +17513,9 @@
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -17870,7 +17871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7382AB7-75C8-44B4-BF78-34EC17E0275A}">
-  <dimension ref="A1:X964"/>
+  <dimension ref="A1:Y964"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -17896,9 +17897,10 @@
     <col min="22" max="22" width="19.42578125" customWidth="1"/>
     <col min="23" max="23" width="20.5703125" customWidth="1"/>
     <col min="24" max="24" width="16.140625" customWidth="1"/>
+    <col min="25" max="25" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4176</v>
       </c>
@@ -17971,8 +17973,11 @@
       <c r="X1" s="1" t="s">
         <v>5580</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y1" s="1" t="s">
+        <v>5662</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -18039,14 +18044,17 @@
       <c r="V2" t="s">
         <v>1444</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" t="s">
         <v>1444</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" t="s">
         <v>5581</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y2" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -18113,14 +18121,17 @@
       <c r="V3" t="s">
         <v>4131</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" t="s">
         <v>1443</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" t="s">
         <v>5582</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y3" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -18187,14 +18198,17 @@
       <c r="V4" t="s">
         <v>1442</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="W4" t="s">
         <v>1442</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="X4" t="s">
         <v>5583</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y4" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -18261,14 +18275,17 @@
       <c r="V5" t="s">
         <v>4132</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="W5" t="s">
         <v>1441</v>
       </c>
-      <c r="X5" s="3" t="s">
+      <c r="X5" t="s">
         <v>5584</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y5" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -18335,14 +18352,17 @@
       <c r="V6" t="s">
         <v>1440</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="W6" t="s">
         <v>1440</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="X6" t="s">
         <v>5585</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y6" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -18409,14 +18429,17 @@
       <c r="V7" t="s">
         <v>1439</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W7" t="s">
         <v>1439</v>
       </c>
-      <c r="X7" s="3" t="s">
+      <c r="X7" t="s">
         <v>5586</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y7" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -18483,14 +18506,17 @@
       <c r="V8" t="s">
         <v>1438</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="W8" t="s">
         <v>1438</v>
       </c>
-      <c r="X8" s="3" t="s">
+      <c r="X8" t="s">
         <v>5587</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y8" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -18557,14 +18583,17 @@
       <c r="V9" t="s">
         <v>1437</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="W9" t="s">
         <v>1437</v>
       </c>
-      <c r="X9" s="3" t="s">
+      <c r="X9" t="s">
         <v>5588</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y9" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -18631,14 +18660,17 @@
       <c r="V10" t="s">
         <v>1436</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="W10" t="s">
         <v>1436</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="X10" t="s">
         <v>5589</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y10" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -18705,14 +18737,17 @@
       <c r="V11" t="s">
         <v>1431</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="W11" t="s">
         <v>1431</v>
       </c>
-      <c r="X11" s="3" t="s">
+      <c r="X11" t="s">
         <v>5590</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y11" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -18779,14 +18814,17 @@
       <c r="V12" t="s">
         <v>1430</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="W12" t="s">
         <v>1430</v>
       </c>
-      <c r="X12" s="3" t="s">
+      <c r="X12" t="s">
         <v>5591</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y12" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -18853,14 +18891,17 @@
       <c r="V13" t="s">
         <v>1429</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="W13" t="s">
         <v>1429</v>
       </c>
-      <c r="X13" s="3" t="s">
+      <c r="X13" t="s">
         <v>5592</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y13" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -18927,14 +18968,17 @@
       <c r="V14" t="s">
         <v>1428</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="W14" t="s">
         <v>1428</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="X14" t="s">
         <v>5593</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y14" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -19001,14 +19045,17 @@
       <c r="V15" t="s">
         <v>1427</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="W15" t="s">
         <v>1427</v>
       </c>
-      <c r="X15" s="3" t="s">
+      <c r="X15" t="s">
         <v>5594</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y15" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -19075,14 +19122,17 @@
       <c r="V16" t="s">
         <v>1426</v>
       </c>
-      <c r="W16" s="2" t="s">
+      <c r="W16" t="s">
         <v>1426</v>
       </c>
-      <c r="X16" s="3" t="s">
+      <c r="X16" t="s">
         <v>5595</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y16" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -19149,14 +19199,17 @@
       <c r="V17" t="s">
         <v>1425</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="W17" t="s">
         <v>1425</v>
       </c>
-      <c r="X17" s="3" t="s">
+      <c r="X17" t="s">
         <v>5596</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y17" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -19223,14 +19276,17 @@
       <c r="V18" t="s">
         <v>1424</v>
       </c>
-      <c r="W18" s="2" t="s">
+      <c r="W18" t="s">
         <v>1424</v>
       </c>
-      <c r="X18" s="3" t="s">
+      <c r="X18" t="s">
         <v>5597</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y18" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -19297,14 +19353,17 @@
       <c r="V19" t="s">
         <v>1423</v>
       </c>
-      <c r="W19" s="2" t="s">
+      <c r="W19" t="s">
         <v>1423</v>
       </c>
-      <c r="X19" s="3" t="s">
+      <c r="X19" t="s">
         <v>5598</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y19" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -19371,14 +19430,17 @@
       <c r="V20" t="s">
         <v>1422</v>
       </c>
-      <c r="W20" s="2" t="s">
+      <c r="W20" t="s">
         <v>1422</v>
       </c>
-      <c r="X20" s="3" t="s">
+      <c r="X20" t="s">
         <v>5599</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y20" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -19445,14 +19507,17 @@
       <c r="V21" t="s">
         <v>1421</v>
       </c>
-      <c r="W21" s="2" t="s">
+      <c r="W21" t="s">
         <v>1421</v>
       </c>
-      <c r="X21" s="3" t="s">
+      <c r="X21" t="s">
         <v>5600</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y21" t="s">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -19519,14 +19584,17 @@
       <c r="V22" t="s">
         <v>1420</v>
       </c>
-      <c r="W22" s="2" t="s">
+      <c r="W22" t="s">
         <v>1420</v>
       </c>
-      <c r="X22" s="3" t="s">
+      <c r="X22" t="s">
         <v>5601</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y22" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -19593,14 +19661,17 @@
       <c r="V23" t="s">
         <v>1419</v>
       </c>
-      <c r="W23" s="2" t="s">
+      <c r="W23" t="s">
         <v>1419</v>
       </c>
-      <c r="X23" s="3" t="s">
+      <c r="X23" t="s">
         <v>5602</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y23" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -19667,14 +19738,17 @@
       <c r="V24" t="s">
         <v>1418</v>
       </c>
-      <c r="W24" s="2" t="s">
+      <c r="W24" t="s">
         <v>1418</v>
       </c>
-      <c r="X24" s="3" t="s">
+      <c r="X24" t="s">
         <v>5603</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y24" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -19741,14 +19815,17 @@
       <c r="V25" t="s">
         <v>1417</v>
       </c>
-      <c r="W25" s="2" t="s">
+      <c r="W25" t="s">
         <v>1417</v>
       </c>
-      <c r="X25" s="3" t="s">
+      <c r="X25" t="s">
         <v>5604</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y25" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -19815,14 +19892,17 @@
       <c r="V26" t="s">
         <v>1416</v>
       </c>
-      <c r="W26" s="2" t="s">
+      <c r="W26" t="s">
         <v>1416</v>
       </c>
-      <c r="X26" s="3" t="s">
+      <c r="X26" t="s">
         <v>5605</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y26" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -19889,14 +19969,17 @@
       <c r="V27" t="s">
         <v>1415</v>
       </c>
-      <c r="W27" s="2" t="s">
+      <c r="W27" t="s">
         <v>1415</v>
       </c>
-      <c r="X27" s="3" t="s">
+      <c r="X27" t="s">
         <v>5606</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y27" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -19963,14 +20046,17 @@
       <c r="V28" t="s">
         <v>1414</v>
       </c>
-      <c r="W28" s="2" t="s">
+      <c r="W28" t="s">
         <v>1414</v>
       </c>
-      <c r="X28" s="3" t="s">
+      <c r="X28" t="s">
         <v>5607</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y28" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -20037,14 +20123,17 @@
       <c r="V29" t="s">
         <v>1413</v>
       </c>
-      <c r="W29" s="2" t="s">
+      <c r="W29" t="s">
         <v>1413</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="X29" t="s">
         <v>5608</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y29" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -20111,14 +20200,17 @@
       <c r="V30" t="s">
         <v>1412</v>
       </c>
-      <c r="W30" s="2" t="s">
+      <c r="W30" t="s">
         <v>1412</v>
       </c>
-      <c r="X30" s="3" t="s">
+      <c r="X30" t="s">
         <v>5609</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y30" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -20185,14 +20277,17 @@
       <c r="V31" t="s">
         <v>1411</v>
       </c>
-      <c r="W31" s="2" t="s">
+      <c r="W31" t="s">
         <v>1411</v>
       </c>
-      <c r="X31" s="3" t="s">
+      <c r="X31" t="s">
         <v>2902</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y31" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -20259,14 +20354,17 @@
       <c r="V32" t="s">
         <v>1410</v>
       </c>
-      <c r="W32" s="2" t="s">
+      <c r="W32" t="s">
         <v>1410</v>
       </c>
-      <c r="X32" s="3" t="s">
+      <c r="X32" t="s">
         <v>2899</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y32" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -20333,14 +20431,17 @@
       <c r="V33" t="s">
         <v>1409</v>
       </c>
-      <c r="W33" s="2" t="s">
+      <c r="W33" t="s">
         <v>1409</v>
       </c>
-      <c r="X33" s="3" t="s">
+      <c r="X33" t="s">
         <v>2903</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y33" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -20407,14 +20508,17 @@
       <c r="V34" t="s">
         <v>1408</v>
       </c>
-      <c r="W34" s="2" t="s">
+      <c r="W34" t="s">
         <v>1408</v>
       </c>
-      <c r="X34" s="3" t="s">
+      <c r="X34" t="s">
         <v>2887</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y34" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -20481,14 +20585,17 @@
       <c r="V35" t="s">
         <v>1407</v>
       </c>
-      <c r="W35" s="2" t="s">
+      <c r="W35" t="s">
         <v>1407</v>
       </c>
-      <c r="X35" s="3" t="s">
+      <c r="X35" t="s">
         <v>2886</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y35" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -20555,14 +20662,17 @@
       <c r="V36" t="s">
         <v>1406</v>
       </c>
-      <c r="W36" s="2" t="s">
+      <c r="W36" t="s">
         <v>1406</v>
       </c>
-      <c r="X36" s="3" t="s">
+      <c r="X36" t="s">
         <v>5610</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y36" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -20629,14 +20739,17 @@
       <c r="V37" t="s">
         <v>1405</v>
       </c>
-      <c r="W37" s="2" t="s">
+      <c r="W37" t="s">
         <v>1405</v>
       </c>
-      <c r="X37" s="3" t="s">
+      <c r="X37" t="s">
         <v>5611</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y37" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -20703,14 +20816,17 @@
       <c r="V38" t="s">
         <v>1404</v>
       </c>
-      <c r="W38" s="2" t="s">
+      <c r="W38" t="s">
         <v>1404</v>
       </c>
-      <c r="X38" s="3" t="s">
+      <c r="X38" t="s">
         <v>5612</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y38" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -20777,14 +20893,17 @@
       <c r="V39" t="s">
         <v>1403</v>
       </c>
-      <c r="W39" s="2" t="s">
+      <c r="W39" t="s">
         <v>1403</v>
       </c>
-      <c r="X39" s="3" t="s">
+      <c r="X39" t="s">
         <v>5613</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y39" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -20851,14 +20970,17 @@
       <c r="V40" t="s">
         <v>1402</v>
       </c>
-      <c r="W40" s="2" t="s">
+      <c r="W40" t="s">
         <v>1402</v>
       </c>
-      <c r="X40" s="3" t="s">
+      <c r="X40" t="s">
         <v>5614</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y40" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -20925,14 +21047,17 @@
       <c r="V41" t="s">
         <v>1401</v>
       </c>
-      <c r="W41" s="2" t="s">
+      <c r="W41" t="s">
         <v>1401</v>
       </c>
-      <c r="X41" s="3" t="s">
+      <c r="X41" t="s">
         <v>5615</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y41" t="s">
+        <v>4801</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -20999,14 +21124,17 @@
       <c r="V42" t="s">
         <v>1400</v>
       </c>
-      <c r="W42" s="2" t="s">
+      <c r="W42" t="s">
         <v>1400</v>
       </c>
-      <c r="X42" s="3" t="s">
+      <c r="X42" t="s">
         <v>5616</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y42" t="s">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -21073,14 +21201,17 @@
       <c r="V43" t="s">
         <v>2920</v>
       </c>
-      <c r="W43" s="2" t="s">
+      <c r="W43" t="s">
         <v>2912</v>
       </c>
-      <c r="X43" s="3" t="s">
+      <c r="X43" t="s">
         <v>5617</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y43" t="s">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -21147,14 +21278,17 @@
       <c r="V44" t="s">
         <v>2919</v>
       </c>
-      <c r="W44" s="2" t="s">
+      <c r="W44" t="s">
         <v>2911</v>
       </c>
-      <c r="X44" s="3" t="s">
+      <c r="X44" t="s">
         <v>5618</v>
       </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y44" t="s">
+        <v>2918</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -21221,14 +21355,17 @@
       <c r="V45" t="s">
         <v>2918</v>
       </c>
-      <c r="W45" s="2" t="s">
+      <c r="W45" t="s">
         <v>2910</v>
       </c>
-      <c r="X45" s="3" t="s">
+      <c r="X45" t="s">
         <v>5619</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y45" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -21295,14 +21432,17 @@
       <c r="V46" t="s">
         <v>2917</v>
       </c>
-      <c r="W46" s="2" t="s">
+      <c r="W46" t="s">
         <v>2909</v>
       </c>
-      <c r="X46" s="3" t="s">
+      <c r="X46" t="s">
         <v>5620</v>
       </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y46" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -21369,14 +21509,17 @@
       <c r="V47" t="s">
         <v>2916</v>
       </c>
-      <c r="W47" s="2" t="s">
+      <c r="W47" t="s">
         <v>2908</v>
       </c>
-      <c r="X47" s="3" t="s">
+      <c r="X47" t="s">
         <v>5621</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y47" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -21443,14 +21586,17 @@
       <c r="V48" t="s">
         <v>2915</v>
       </c>
-      <c r="W48" s="2" t="s">
+      <c r="W48" t="s">
         <v>2907</v>
       </c>
-      <c r="X48" s="3" t="s">
+      <c r="X48" t="s">
         <v>5622</v>
       </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y48" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -21517,14 +21663,17 @@
       <c r="V49" t="s">
         <v>1393</v>
       </c>
-      <c r="W49" s="2" t="s">
+      <c r="W49" t="s">
         <v>2906</v>
       </c>
-      <c r="X49" s="3" t="s">
+      <c r="X49" t="s">
         <v>5623</v>
       </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y49" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -21591,14 +21740,17 @@
       <c r="V50" t="s">
         <v>1392</v>
       </c>
-      <c r="W50" s="2" t="s">
+      <c r="W50" t="s">
         <v>2905</v>
       </c>
-      <c r="X50" s="3" t="s">
+      <c r="X50" t="s">
         <v>5624</v>
       </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y50" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -21665,14 +21817,17 @@
       <c r="V51" t="s">
         <v>1391</v>
       </c>
-      <c r="W51" s="2" t="s">
+      <c r="W51" t="s">
         <v>2904</v>
       </c>
-      <c r="X51" s="3" t="s">
+      <c r="X51" t="s">
         <v>5625</v>
       </c>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y51" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -21739,14 +21894,17 @@
       <c r="V52" t="s">
         <v>1390</v>
       </c>
-      <c r="W52" s="2" t="s">
+      <c r="W52" t="s">
         <v>2903</v>
       </c>
-      <c r="X52" s="3" t="s">
+      <c r="X52" t="s">
         <v>5626</v>
       </c>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y52" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -21813,14 +21971,17 @@
       <c r="V53" t="s">
         <v>1389</v>
       </c>
-      <c r="W53" s="2" t="s">
+      <c r="W53" t="s">
         <v>2902</v>
       </c>
-      <c r="X53" s="3" t="s">
+      <c r="X53" t="s">
         <v>5627</v>
       </c>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y53" t="s">
+        <v>4802</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -21887,14 +22048,17 @@
       <c r="V54" t="s">
         <v>2914</v>
       </c>
-      <c r="W54" s="2" t="s">
+      <c r="W54" t="s">
         <v>2901</v>
       </c>
-      <c r="X54" s="3" t="s">
+      <c r="X54" t="s">
         <v>5628</v>
       </c>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y54" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -21961,14 +22125,17 @@
       <c r="V55" t="s">
         <v>2913</v>
       </c>
-      <c r="W55" s="2" t="s">
+      <c r="W55" t="s">
         <v>2900</v>
       </c>
-      <c r="X55" s="3" t="s">
+      <c r="X55" t="s">
         <v>5629</v>
       </c>
-    </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y55" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -22035,14 +22202,17 @@
       <c r="V56" t="s">
         <v>1386</v>
       </c>
-      <c r="W56" s="2" t="s">
+      <c r="W56" t="s">
         <v>2899</v>
       </c>
-      <c r="X56" s="3" t="s">
+      <c r="X56" t="s">
         <v>5630</v>
       </c>
-    </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y56" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -22109,14 +22279,17 @@
       <c r="V57" t="s">
         <v>1385</v>
       </c>
-      <c r="W57" s="2" t="s">
+      <c r="W57" t="s">
         <v>2898</v>
       </c>
-      <c r="X57" s="3" t="s">
+      <c r="X57" t="s">
         <v>5631</v>
       </c>
-    </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y57" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -22183,14 +22356,17 @@
       <c r="V58" t="s">
         <v>1384</v>
       </c>
-      <c r="W58" s="2" t="s">
+      <c r="W58" t="s">
         <v>2897</v>
       </c>
-      <c r="X58" s="3" t="s">
+      <c r="X58" t="s">
         <v>5632</v>
       </c>
-    </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y58" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -22257,14 +22433,17 @@
       <c r="V59" t="s">
         <v>1383</v>
       </c>
-      <c r="W59" s="2" t="s">
+      <c r="W59" t="s">
         <v>2896</v>
       </c>
-      <c r="X59" s="3" t="s">
+      <c r="X59" t="s">
         <v>5633</v>
       </c>
-    </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y59" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -22331,14 +22510,17 @@
       <c r="V60" t="s">
         <v>1382</v>
       </c>
-      <c r="W60" s="2" t="s">
+      <c r="W60" t="s">
         <v>2895</v>
       </c>
-      <c r="X60" s="3" t="s">
+      <c r="X60" t="s">
         <v>5634</v>
       </c>
-    </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y60" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -22405,14 +22587,17 @@
       <c r="V61" t="s">
         <v>1381</v>
       </c>
-      <c r="W61" s="2" t="s">
+      <c r="W61" t="s">
         <v>2894</v>
       </c>
-      <c r="X61" s="3" t="s">
+      <c r="X61" t="s">
         <v>5635</v>
       </c>
-    </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y61" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -22479,14 +22664,17 @@
       <c r="V62" t="s">
         <v>1380</v>
       </c>
-      <c r="W62" s="2" t="s">
+      <c r="W62" t="s">
         <v>2893</v>
       </c>
-      <c r="X62" s="3" t="s">
+      <c r="X62" t="s">
         <v>5636</v>
       </c>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y62" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -22553,14 +22741,17 @@
       <c r="V63" t="s">
         <v>1379</v>
       </c>
-      <c r="W63" s="2" t="s">
+      <c r="W63" t="s">
         <v>2892</v>
       </c>
-      <c r="X63" s="3" t="s">
+      <c r="X63" t="s">
         <v>5637</v>
       </c>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y63" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -22627,14 +22818,17 @@
       <c r="V64" t="s">
         <v>1378</v>
       </c>
-      <c r="W64" s="2" t="s">
+      <c r="W64" t="s">
         <v>2891</v>
       </c>
-      <c r="X64" s="3" t="s">
+      <c r="X64" t="s">
         <v>5638</v>
       </c>
-    </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y64" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -22701,14 +22895,17 @@
       <c r="V65" t="s">
         <v>1377</v>
       </c>
-      <c r="W65" s="2" t="s">
+      <c r="W65" t="s">
         <v>2890</v>
       </c>
-      <c r="X65" s="3" t="s">
+      <c r="X65" t="s">
         <v>5639</v>
       </c>
-    </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y65" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -22775,14 +22972,17 @@
       <c r="V66" t="s">
         <v>1376</v>
       </c>
-      <c r="W66" s="2" t="s">
+      <c r="W66" t="s">
         <v>2889</v>
       </c>
-      <c r="X66" s="3" t="s">
+      <c r="X66" t="s">
         <v>5640</v>
       </c>
-    </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y66" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -22849,14 +23049,17 @@
       <c r="V67" t="s">
         <v>1375</v>
       </c>
-      <c r="W67" s="2" t="s">
+      <c r="W67" t="s">
         <v>2888</v>
       </c>
-      <c r="X67" s="3" t="s">
+      <c r="X67" t="s">
         <v>5641</v>
       </c>
-    </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y67" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -22923,14 +23126,17 @@
       <c r="V68" t="s">
         <v>1374</v>
       </c>
-      <c r="W68" s="2" t="s">
+      <c r="W68" t="s">
         <v>2887</v>
       </c>
-      <c r="X68" s="3" t="s">
+      <c r="X68" t="s">
         <v>5642</v>
       </c>
-    </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y68" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -22997,14 +23203,17 @@
       <c r="V69" t="s">
         <v>1373</v>
       </c>
-      <c r="W69" s="2" t="s">
+      <c r="W69" t="s">
         <v>2886</v>
       </c>
-      <c r="X69" s="3" t="s">
+      <c r="X69" t="s">
         <v>5643</v>
       </c>
-    </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y69" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -23071,14 +23280,17 @@
       <c r="V70" t="s">
         <v>1372</v>
       </c>
-      <c r="W70" s="2" t="s">
+      <c r="W70" t="s">
         <v>2885</v>
       </c>
-      <c r="X70" s="3" t="s">
+      <c r="X70" t="s">
         <v>5644</v>
       </c>
-    </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y70" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -23145,14 +23357,17 @@
       <c r="V71" t="s">
         <v>1371</v>
       </c>
-      <c r="W71" s="2" t="s">
+      <c r="W71" t="s">
         <v>2884</v>
       </c>
-      <c r="X71" s="3" t="s">
+      <c r="X71" t="s">
         <v>5645</v>
       </c>
-    </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y71" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -23219,14 +23434,17 @@
       <c r="V72" t="s">
         <v>1370</v>
       </c>
-      <c r="W72" s="2" t="s">
+      <c r="W72" t="s">
         <v>2883</v>
       </c>
-      <c r="X72" s="3" t="s">
+      <c r="X72" t="s">
         <v>5646</v>
       </c>
-    </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y72" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -23293,14 +23511,17 @@
       <c r="V73" t="s">
         <v>1369</v>
       </c>
-      <c r="W73" s="2" t="s">
+      <c r="W73" t="s">
         <v>2882</v>
       </c>
-      <c r="X73" s="3" t="s">
+      <c r="X73" t="s">
         <v>5647</v>
       </c>
-    </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y73" t="s">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -23367,14 +23588,17 @@
       <c r="V74" t="s">
         <v>1368</v>
       </c>
-      <c r="W74" s="2" t="s">
+      <c r="W74" t="s">
         <v>2881</v>
       </c>
-      <c r="X74" s="3" t="s">
+      <c r="X74" t="s">
         <v>5648</v>
       </c>
-    </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y74" t="s">
+        <v>4812</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -23441,14 +23665,17 @@
       <c r="V75" t="s">
         <v>2912</v>
       </c>
-      <c r="W75" s="2" t="s">
+      <c r="W75" t="s">
         <v>1334</v>
       </c>
-      <c r="X75" s="3" t="s">
+      <c r="X75" t="s">
         <v>5649</v>
       </c>
-    </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y75" t="s">
+        <v>4813</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -23515,14 +23742,17 @@
       <c r="V76" t="s">
         <v>2911</v>
       </c>
-      <c r="W76" s="2" t="s">
+      <c r="W76" t="s">
         <v>2235</v>
       </c>
-      <c r="X76" s="3" t="s">
+      <c r="X76" t="s">
         <v>5650</v>
       </c>
-    </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y76" t="s">
+        <v>4814</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -23589,14 +23819,17 @@
       <c r="V77" t="s">
         <v>2910</v>
       </c>
-      <c r="W77" s="2" t="s">
+      <c r="W77" t="s">
         <v>1333</v>
       </c>
-      <c r="X77" s="3" t="s">
+      <c r="X77" t="s">
         <v>5651</v>
       </c>
-    </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y77" t="s">
+        <v>4815</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -23663,14 +23896,17 @@
       <c r="V78" t="s">
         <v>2909</v>
       </c>
-      <c r="W78" s="2" t="s">
+      <c r="W78" t="s">
         <v>3648</v>
       </c>
-      <c r="X78" s="3" t="s">
+      <c r="X78" t="s">
         <v>5652</v>
       </c>
-    </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y78" t="s">
+        <v>4816</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -23737,14 +23973,17 @@
       <c r="V79" t="s">
         <v>2908</v>
       </c>
-      <c r="W79" s="2" t="s">
+      <c r="W79" t="s">
         <v>3647</v>
       </c>
-      <c r="X79" s="3" t="s">
+      <c r="X79" t="s">
         <v>5653</v>
       </c>
-    </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y79" t="s">
+        <v>4817</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -23811,14 +24050,17 @@
       <c r="V80" t="s">
         <v>2907</v>
       </c>
-      <c r="W80" s="2" t="s">
+      <c r="W80" t="s">
         <v>3646</v>
       </c>
-      <c r="X80" s="3" t="s">
+      <c r="X80" t="s">
         <v>5654</v>
       </c>
-    </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y80" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -23885,14 +24127,17 @@
       <c r="V81" t="s">
         <v>2906</v>
       </c>
-      <c r="W81" s="2" t="s">
+      <c r="W81" t="s">
         <v>1329</v>
       </c>
-      <c r="X81" s="3" t="s">
+      <c r="X81" t="s">
         <v>5655</v>
       </c>
-    </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y81" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -23959,14 +24204,17 @@
       <c r="V82" t="s">
         <v>2905</v>
       </c>
-      <c r="W82" s="2" t="s">
+      <c r="W82" t="s">
         <v>1328</v>
       </c>
-      <c r="X82" s="3" t="s">
+      <c r="X82" t="s">
         <v>5656</v>
       </c>
-    </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y82" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -24033,14 +24281,17 @@
       <c r="V83" t="s">
         <v>2904</v>
       </c>
-      <c r="W83" s="2" t="s">
+      <c r="W83" t="s">
         <v>1327</v>
       </c>
-      <c r="X83" s="3" t="s">
+      <c r="X83" t="s">
         <v>5657</v>
       </c>
-    </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y83" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -24107,14 +24358,17 @@
       <c r="V84" t="s">
         <v>2903</v>
       </c>
-      <c r="W84" s="2" t="s">
+      <c r="W84" t="s">
         <v>1326</v>
       </c>
-      <c r="X84" s="3" t="s">
+      <c r="X84" t="s">
         <v>5658</v>
       </c>
-    </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y84" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -24181,14 +24435,17 @@
       <c r="V85" t="s">
         <v>2902</v>
       </c>
-      <c r="W85" s="2" t="s">
+      <c r="W85" t="s">
         <v>1325</v>
       </c>
-      <c r="X85" s="3" t="s">
+      <c r="X85" t="s">
         <v>5659</v>
       </c>
-    </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y85" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -24255,14 +24512,17 @@
       <c r="V86" t="s">
         <v>2901</v>
       </c>
-      <c r="W86" s="2" t="s">
+      <c r="W86" t="s">
         <v>1324</v>
       </c>
-      <c r="X86" s="3" t="s">
+      <c r="X86" t="s">
         <v>5660</v>
       </c>
-    </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y86" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -24329,14 +24589,17 @@
       <c r="V87" t="s">
         <v>2900</v>
       </c>
-      <c r="W87" s="2" t="s">
+      <c r="W87" t="s">
         <v>1323</v>
       </c>
-      <c r="X87" s="3" t="s">
+      <c r="X87" t="s">
         <v>5661</v>
       </c>
-    </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y87" t="s">
+        <v>4818</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -24403,11 +24666,14 @@
       <c r="V88" t="s">
         <v>2899</v>
       </c>
-      <c r="W88" s="2" t="s">
+      <c r="W88" t="s">
         <v>1322</v>
       </c>
-    </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y88" t="s">
+        <v>4819</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -24474,11 +24740,14 @@
       <c r="V89" t="s">
         <v>2898</v>
       </c>
-      <c r="W89" s="2" t="s">
+      <c r="W89" t="s">
         <v>1321</v>
       </c>
-    </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y89" t="s">
+        <v>4820</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -24545,11 +24814,14 @@
       <c r="V90" t="s">
         <v>2897</v>
       </c>
-      <c r="W90" s="2" t="s">
+      <c r="W90" t="s">
         <v>1330</v>
       </c>
-    </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y90" t="s">
+        <v>4821</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -24616,11 +24888,14 @@
       <c r="V91" t="s">
         <v>2896</v>
       </c>
-      <c r="W91" s="2" t="s">
+      <c r="W91" t="s">
         <v>1320</v>
       </c>
-    </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y91" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -24687,11 +24962,14 @@
       <c r="V92" t="s">
         <v>2895</v>
       </c>
-      <c r="W92" s="2" t="s">
+      <c r="W92" t="s">
         <v>1319</v>
       </c>
-    </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y92" t="s">
+        <v>4823</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -24758,11 +25036,14 @@
       <c r="V93" t="s">
         <v>2894</v>
       </c>
-      <c r="W93" s="2" t="s">
+      <c r="W93" t="s">
         <v>3645</v>
       </c>
-    </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y93" t="s">
+        <v>4824</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -24829,11 +25110,14 @@
       <c r="V94" t="s">
         <v>2893</v>
       </c>
-      <c r="W94" s="2" t="s">
+      <c r="W94" t="s">
         <v>3644</v>
       </c>
-    </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y94" t="s">
+        <v>4825</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -24900,11 +25184,14 @@
       <c r="V95" t="s">
         <v>2892</v>
       </c>
-      <c r="W95" s="2" t="s">
+      <c r="W95" t="s">
         <v>3643</v>
       </c>
-    </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y95" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -24971,11 +25258,14 @@
       <c r="V96" t="s">
         <v>2891</v>
       </c>
-      <c r="W96" s="2" t="s">
+      <c r="W96" t="s">
         <v>3642</v>
       </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y96" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -25042,11 +25332,14 @@
       <c r="V97" t="s">
         <v>2890</v>
       </c>
-      <c r="W97" s="2" t="s">
+      <c r="W97" t="s">
         <v>3641</v>
       </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y97" t="s">
+        <v>4828</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -25113,11 +25406,14 @@
       <c r="V98" t="s">
         <v>2889</v>
       </c>
-      <c r="W98" s="2" t="s">
+      <c r="W98" t="s">
         <v>3640</v>
       </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y98" t="s">
+        <v>4829</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>101</v>
       </c>
@@ -25184,11 +25480,14 @@
       <c r="V99" t="s">
         <v>2888</v>
       </c>
-      <c r="W99" s="2" t="s">
+      <c r="W99" t="s">
         <v>3639</v>
       </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y99" t="s">
+        <v>4830</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>102</v>
       </c>
@@ -25255,11 +25554,14 @@
       <c r="V100" t="s">
         <v>2887</v>
       </c>
-      <c r="W100" s="2" t="s">
+      <c r="W100" t="s">
         <v>3638</v>
       </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y100" t="s">
+        <v>4831</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>103</v>
       </c>
@@ -25326,11 +25628,14 @@
       <c r="V101" t="s">
         <v>2886</v>
       </c>
-      <c r="W101" s="2" t="s">
+      <c r="W101" t="s">
         <v>3637</v>
       </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y101" t="s">
+        <v>4832</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>104</v>
       </c>
@@ -25397,11 +25702,14 @@
       <c r="V102" t="s">
         <v>2885</v>
       </c>
-      <c r="W102" s="2" t="s">
+      <c r="W102" t="s">
         <v>3636</v>
       </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y102" t="s">
+        <v>4833</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -25468,11 +25776,14 @@
       <c r="V103" t="s">
         <v>2884</v>
       </c>
-      <c r="W103" s="2" t="s">
+      <c r="W103" t="s">
         <v>3635</v>
       </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y103" t="s">
+        <v>4834</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>106</v>
       </c>
@@ -25539,11 +25850,14 @@
       <c r="V104" t="s">
         <v>2883</v>
       </c>
-      <c r="W104" s="2" t="s">
+      <c r="W104" t="s">
         <v>3634</v>
       </c>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y104" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>107</v>
       </c>
@@ -25610,11 +25924,14 @@
       <c r="V105" t="s">
         <v>2882</v>
       </c>
-      <c r="W105" s="2" t="s">
+      <c r="W105" t="s">
         <v>3633</v>
       </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y105" t="s">
+        <v>4836</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>108</v>
       </c>
@@ -25681,11 +25998,14 @@
       <c r="V106" t="s">
         <v>2881</v>
       </c>
-      <c r="W106" s="2" t="s">
+      <c r="W106" t="s">
         <v>3632</v>
       </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y106" t="s">
+        <v>4837</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>109</v>
       </c>
@@ -25752,11 +26072,14 @@
       <c r="V107" t="s">
         <v>1335</v>
       </c>
-      <c r="W107" s="2" t="s">
+      <c r="W107" t="s">
         <v>3631</v>
       </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y107" t="s">
+        <v>4838</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>110</v>
       </c>
@@ -25823,11 +26146,14 @@
       <c r="V108" t="s">
         <v>1334</v>
       </c>
-      <c r="W108" s="2" t="s">
+      <c r="W108" t="s">
         <v>3630</v>
       </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y108" t="s">
+        <v>4839</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>111</v>
       </c>
@@ -25894,11 +26220,14 @@
       <c r="V109" t="s">
         <v>1333</v>
       </c>
-      <c r="W109" s="2" t="s">
+      <c r="W109" t="s">
         <v>3629</v>
       </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y109" t="s">
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>112</v>
       </c>
@@ -25965,11 +26294,14 @@
       <c r="V110" t="s">
         <v>1331</v>
       </c>
-      <c r="W110" s="2" t="s">
+      <c r="W110" t="s">
         <v>3628</v>
       </c>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y110" t="s">
+        <v>4841</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>113</v>
       </c>
@@ -26036,11 +26368,14 @@
       <c r="V111" t="s">
         <v>1329</v>
       </c>
-      <c r="W111" s="2" t="s">
+      <c r="W111" t="s">
         <v>3627</v>
       </c>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y111" t="s">
+        <v>4842</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -26107,11 +26442,14 @@
       <c r="V112" t="s">
         <v>1328</v>
       </c>
-      <c r="W112" s="2" t="s">
+      <c r="W112" t="s">
         <v>3626</v>
       </c>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y112" t="s">
+        <v>4843</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -26178,11 +26516,14 @@
       <c r="V113" t="s">
         <v>1327</v>
       </c>
-      <c r="W113" s="2" t="s">
+      <c r="W113" t="s">
         <v>3625</v>
       </c>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y113" t="s">
+        <v>4844</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -26249,11 +26590,14 @@
       <c r="V114" t="s">
         <v>1326</v>
       </c>
-      <c r="W114" s="2" t="s">
+      <c r="W114" t="s">
         <v>3624</v>
       </c>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y114" t="s">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -26320,11 +26664,14 @@
       <c r="V115" t="s">
         <v>1325</v>
       </c>
-      <c r="W115" s="2" t="s">
+      <c r="W115" t="s">
         <v>3623</v>
       </c>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y115" t="s">
+        <v>4846</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -26391,11 +26738,14 @@
       <c r="V116" t="s">
         <v>1324</v>
       </c>
-      <c r="W116" s="2" t="s">
+      <c r="W116" t="s">
         <v>3622</v>
       </c>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y116" t="s">
+        <v>4847</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>119</v>
       </c>
@@ -26462,11 +26812,14 @@
       <c r="V117" t="s">
         <v>1323</v>
       </c>
-      <c r="W117" s="2" t="s">
+      <c r="W117" t="s">
         <v>3621</v>
       </c>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y117" t="s">
+        <v>4848</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -26533,11 +26886,14 @@
       <c r="V118" t="s">
         <v>1322</v>
       </c>
-      <c r="W118" s="2" t="s">
+      <c r="W118" t="s">
         <v>3620</v>
       </c>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y118" t="s">
+        <v>4849</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -26604,11 +26960,14 @@
       <c r="V119" t="s">
         <v>1321</v>
       </c>
-      <c r="W119" s="2" t="s">
+      <c r="W119" t="s">
         <v>3619</v>
       </c>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y119" t="s">
+        <v>4850</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>122</v>
       </c>
@@ -26675,11 +27034,14 @@
       <c r="V120" t="s">
         <v>1320</v>
       </c>
-      <c r="W120" s="2" t="s">
+      <c r="W120" t="s">
         <v>3618</v>
       </c>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y120" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>123</v>
       </c>
@@ -26746,11 +27108,14 @@
       <c r="V121" t="s">
         <v>1319</v>
       </c>
-      <c r="W121" s="2" t="s">
+      <c r="W121" t="s">
         <v>3617</v>
       </c>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y121" t="s">
+        <v>4852</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>124</v>
       </c>
@@ -26817,11 +27182,14 @@
       <c r="V122" t="s">
         <v>2235</v>
       </c>
-      <c r="W122" s="2" t="s">
+      <c r="W122" t="s">
         <v>3616</v>
       </c>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y122" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>125</v>
       </c>
@@ -26888,11 +27256,14 @@
       <c r="V123" t="s">
         <v>4190</v>
       </c>
-      <c r="W123" s="2" t="s">
+      <c r="W123" t="s">
         <v>3615</v>
       </c>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y123" t="s">
+        <v>4854</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>126</v>
       </c>
@@ -26959,11 +27330,14 @@
       <c r="V124" t="s">
         <v>4191</v>
       </c>
-      <c r="W124" s="2" t="s">
+      <c r="W124" t="s">
         <v>3614</v>
       </c>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y124" t="s">
+        <v>4855</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>127</v>
       </c>
@@ -27030,11 +27404,14 @@
       <c r="V125" t="s">
         <v>4192</v>
       </c>
-      <c r="W125" s="2" t="s">
+      <c r="W125" t="s">
         <v>3613</v>
       </c>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y125" t="s">
+        <v>4856</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>128</v>
       </c>
@@ -27101,11 +27478,14 @@
       <c r="V126" t="s">
         <v>4193</v>
       </c>
-      <c r="W126" s="2" t="s">
+      <c r="W126" t="s">
         <v>3612</v>
       </c>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y126" t="s">
+        <v>4857</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>129</v>
       </c>
@@ -27172,11 +27552,14 @@
       <c r="V127" t="s">
         <v>4194</v>
       </c>
-      <c r="W127" s="2" t="s">
+      <c r="W127" t="s">
         <v>3611</v>
       </c>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y127" t="s">
+        <v>4858</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>130</v>
       </c>
@@ -27243,11 +27626,14 @@
       <c r="V128" t="s">
         <v>4195</v>
       </c>
-      <c r="W128" s="2" t="s">
+      <c r="W128" t="s">
         <v>3610</v>
       </c>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y128" t="s">
+        <v>4859</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>131</v>
       </c>
@@ -27314,11 +27700,14 @@
       <c r="V129" t="s">
         <v>4196</v>
       </c>
-      <c r="W129" s="2" t="s">
+      <c r="W129" t="s">
         <v>3609</v>
       </c>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y129" t="s">
+        <v>4860</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>132</v>
       </c>
@@ -27385,11 +27774,14 @@
       <c r="V130" t="s">
         <v>4197</v>
       </c>
-      <c r="W130" s="2" t="s">
+      <c r="W130" t="s">
         <v>3608</v>
       </c>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y130" t="s">
+        <v>4861</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>133</v>
       </c>
@@ -27456,11 +27848,14 @@
       <c r="V131" t="s">
         <v>4198</v>
       </c>
-      <c r="W131" s="2" t="s">
+      <c r="W131" t="s">
         <v>3607</v>
       </c>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y131" t="s">
+        <v>4862</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>134</v>
       </c>
@@ -27527,11 +27922,14 @@
       <c r="V132" t="s">
         <v>4199</v>
       </c>
-      <c r="W132" s="2" t="s">
+      <c r="W132" t="s">
         <v>3606</v>
       </c>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y132" t="s">
+        <v>4863</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>135</v>
       </c>
@@ -27598,11 +27996,14 @@
       <c r="V133" t="s">
         <v>4200</v>
       </c>
-      <c r="W133" s="2" t="s">
+      <c r="W133" t="s">
         <v>3605</v>
       </c>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y133" t="s">
+        <v>4864</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>136</v>
       </c>
@@ -27669,11 +28070,14 @@
       <c r="V134" t="s">
         <v>4201</v>
       </c>
-      <c r="W134" s="2" t="s">
+      <c r="W134" t="s">
         <v>3604</v>
       </c>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y134" t="s">
+        <v>4865</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>137</v>
       </c>
@@ -27740,11 +28144,14 @@
       <c r="V135" t="s">
         <v>4202</v>
       </c>
-      <c r="W135" s="2" t="s">
+      <c r="W135" t="s">
         <v>3603</v>
       </c>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y135" t="s">
+        <v>4866</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>138</v>
       </c>
@@ -27808,11 +28215,14 @@
       <c r="V136" t="s">
         <v>4203</v>
       </c>
-      <c r="W136" s="2" t="s">
+      <c r="W136" t="s">
         <v>3602</v>
       </c>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y136" t="s">
+        <v>4867</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -27876,11 +28286,14 @@
       <c r="V137" t="s">
         <v>4204</v>
       </c>
-      <c r="W137" s="2" t="s">
+      <c r="W137" t="s">
         <v>3601</v>
       </c>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y137" t="s">
+        <v>4868</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -27944,11 +28357,14 @@
       <c r="V138" t="s">
         <v>4205</v>
       </c>
-      <c r="W138" s="2" t="s">
+      <c r="W138" t="s">
         <v>3600</v>
       </c>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y138" t="s">
+        <v>4869</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>141</v>
       </c>
@@ -28012,11 +28428,14 @@
       <c r="V139" t="s">
         <v>4206</v>
       </c>
-      <c r="W139" s="2" t="s">
+      <c r="W139" t="s">
         <v>3599</v>
       </c>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y139" t="s">
+        <v>4870</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -28080,11 +28499,14 @@
       <c r="V140" t="s">
         <v>4207</v>
       </c>
-      <c r="W140" s="2" t="s">
+      <c r="W140" t="s">
         <v>3598</v>
       </c>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y140" t="s">
+        <v>4871</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>143</v>
       </c>
@@ -28148,11 +28570,14 @@
       <c r="V141" t="s">
         <v>4208</v>
       </c>
-      <c r="W141" s="2" t="s">
+      <c r="W141" t="s">
         <v>3597</v>
       </c>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y141" t="s">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>144</v>
       </c>
@@ -28216,11 +28641,14 @@
       <c r="V142" t="s">
         <v>4209</v>
       </c>
-      <c r="W142" s="2" t="s">
+      <c r="W142" t="s">
         <v>3596</v>
       </c>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y142" t="s">
+        <v>4873</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>145</v>
       </c>
@@ -28284,11 +28712,14 @@
       <c r="V143" t="s">
         <v>4210</v>
       </c>
-      <c r="W143" s="2" t="s">
+      <c r="W143" t="s">
         <v>3595</v>
       </c>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y143" t="s">
+        <v>4874</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>146</v>
       </c>
@@ -28352,11 +28783,14 @@
       <c r="V144" t="s">
         <v>4211</v>
       </c>
-      <c r="W144" s="2" t="s">
+      <c r="W144" t="s">
         <v>3594</v>
       </c>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y144" t="s">
+        <v>4875</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>147</v>
       </c>
@@ -28420,11 +28854,14 @@
       <c r="V145" t="s">
         <v>4212</v>
       </c>
-      <c r="W145" s="2" t="s">
+      <c r="W145" t="s">
         <v>3593</v>
       </c>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y145" t="s">
+        <v>4876</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>148</v>
       </c>
@@ -28488,11 +28925,14 @@
       <c r="V146" t="s">
         <v>4213</v>
       </c>
-      <c r="W146" s="2" t="s">
+      <c r="W146" t="s">
         <v>3592</v>
       </c>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y146" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>149</v>
       </c>
@@ -28556,11 +28996,14 @@
       <c r="V147" t="s">
         <v>4214</v>
       </c>
-      <c r="W147" s="2" t="s">
+      <c r="W147" t="s">
         <v>3591</v>
       </c>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y147" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -28624,11 +29067,14 @@
       <c r="V148" t="s">
         <v>4215</v>
       </c>
-      <c r="W148" s="2" t="s">
+      <c r="W148" t="s">
         <v>3590</v>
       </c>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y148" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>151</v>
       </c>
@@ -28692,11 +29138,14 @@
       <c r="V149" t="s">
         <v>4216</v>
       </c>
-      <c r="W149" s="2" t="s">
+      <c r="W149" t="s">
         <v>3589</v>
       </c>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y149" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>152</v>
       </c>
@@ -28760,11 +29209,14 @@
       <c r="V150" t="s">
         <v>4217</v>
       </c>
-      <c r="W150" s="2" t="s">
+      <c r="W150" t="s">
         <v>3588</v>
       </c>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y150" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>153</v>
       </c>
@@ -28828,11 +29280,14 @@
       <c r="V151" t="s">
         <v>4218</v>
       </c>
-      <c r="W151" s="2" t="s">
+      <c r="W151" t="s">
         <v>3587</v>
       </c>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y151" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>154</v>
       </c>
@@ -28896,11 +29351,14 @@
       <c r="V152" t="s">
         <v>4219</v>
       </c>
-      <c r="W152" s="2" t="s">
+      <c r="W152" t="s">
         <v>3586</v>
       </c>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y152" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>155</v>
       </c>
@@ -28964,11 +29422,14 @@
       <c r="V153" t="s">
         <v>4220</v>
       </c>
-      <c r="W153" s="2" t="s">
+      <c r="W153" t="s">
         <v>3585</v>
       </c>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y153" t="s">
+        <v>4877</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>156</v>
       </c>
@@ -29032,11 +29493,14 @@
       <c r="V154" t="s">
         <v>4221</v>
       </c>
-      <c r="W154" s="2" t="s">
+      <c r="W154" t="s">
         <v>3584</v>
       </c>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y154" t="s">
+        <v>4878</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>157</v>
       </c>
@@ -29100,11 +29564,14 @@
       <c r="V155" t="s">
         <v>4222</v>
       </c>
-      <c r="W155" s="2" t="s">
+      <c r="W155" t="s">
         <v>3583</v>
       </c>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y155" t="s">
+        <v>4879</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>158</v>
       </c>
@@ -29168,11 +29635,14 @@
       <c r="V156" t="s">
         <v>4223</v>
       </c>
-      <c r="W156" s="2" t="s">
+      <c r="W156" t="s">
         <v>3582</v>
       </c>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y156" t="s">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>159</v>
       </c>
@@ -29236,11 +29706,14 @@
       <c r="V157" t="s">
         <v>4224</v>
       </c>
-      <c r="W157" s="2" t="s">
+      <c r="W157" t="s">
         <v>3581</v>
       </c>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y157" t="s">
+        <v>4881</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>160</v>
       </c>
@@ -29304,11 +29777,14 @@
       <c r="V158" t="s">
         <v>4225</v>
       </c>
-      <c r="W158" s="2" t="s">
+      <c r="W158" t="s">
         <v>3580</v>
       </c>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y158" t="s">
+        <v>4882</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>161</v>
       </c>
@@ -29372,11 +29848,14 @@
       <c r="V159" t="s">
         <v>4226</v>
       </c>
-      <c r="W159" s="2" t="s">
+      <c r="W159" t="s">
         <v>3579</v>
       </c>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y159" t="s">
+        <v>4883</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -29440,11 +29919,14 @@
       <c r="V160" t="s">
         <v>4227</v>
       </c>
-      <c r="W160" s="2" t="s">
+      <c r="W160" t="s">
         <v>3578</v>
       </c>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y160" t="s">
+        <v>4884</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>163</v>
       </c>
@@ -29508,11 +29990,14 @@
       <c r="V161" t="s">
         <v>4228</v>
       </c>
-      <c r="W161" s="2" t="s">
+      <c r="W161" t="s">
         <v>3577</v>
       </c>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y161" t="s">
+        <v>4885</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>164</v>
       </c>
@@ -29576,11 +30061,14 @@
       <c r="V162" t="s">
         <v>4229</v>
       </c>
-      <c r="W162" s="2" t="s">
+      <c r="W162" t="s">
         <v>3576</v>
       </c>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y162" t="s">
+        <v>4886</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>165</v>
       </c>
@@ -29644,11 +30132,14 @@
       <c r="V163" t="s">
         <v>4230</v>
       </c>
-      <c r="W163" s="2" t="s">
+      <c r="W163" t="s">
         <v>3575</v>
       </c>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y163" t="s">
+        <v>4887</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>166</v>
       </c>
@@ -29712,11 +30203,14 @@
       <c r="V164" t="s">
         <v>4231</v>
       </c>
-      <c r="W164" s="2" t="s">
+      <c r="W164" t="s">
         <v>3574</v>
       </c>
-    </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y164" t="s">
+        <v>4888</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>167</v>
       </c>
@@ -29780,11 +30274,14 @@
       <c r="V165" t="s">
         <v>4232</v>
       </c>
-      <c r="W165" s="2" t="s">
+      <c r="W165" t="s">
         <v>3573</v>
       </c>
-    </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y165" t="s">
+        <v>4889</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>168</v>
       </c>
@@ -29848,11 +30345,14 @@
       <c r="V166" t="s">
         <v>4233</v>
       </c>
-      <c r="W166" s="2" t="s">
+      <c r="W166" t="s">
         <v>3572</v>
       </c>
-    </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y166" t="s">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>169</v>
       </c>
@@ -29916,11 +30416,14 @@
       <c r="V167" t="s">
         <v>4234</v>
       </c>
-      <c r="W167" s="2" t="s">
+      <c r="W167" t="s">
         <v>3571</v>
       </c>
-    </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y167" t="s">
+        <v>4891</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>170</v>
       </c>
@@ -29984,11 +30487,14 @@
       <c r="V168" t="s">
         <v>4235</v>
       </c>
-      <c r="W168" s="2" t="s">
+      <c r="W168" t="s">
         <v>3570</v>
       </c>
-    </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y168" t="s">
+        <v>4892</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>171</v>
       </c>
@@ -30052,11 +30558,14 @@
       <c r="V169" t="s">
         <v>4236</v>
       </c>
-      <c r="W169" s="2" t="s">
+      <c r="W169" t="s">
         <v>3569</v>
       </c>
-    </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y169" t="s">
+        <v>4893</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>172</v>
       </c>
@@ -30120,11 +30629,14 @@
       <c r="V170" t="s">
         <v>4237</v>
       </c>
-      <c r="W170" s="2" t="s">
+      <c r="W170" t="s">
         <v>3568</v>
       </c>
-    </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y170" t="s">
+        <v>4894</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>173</v>
       </c>
@@ -30188,11 +30700,14 @@
       <c r="V171" t="s">
         <v>4238</v>
       </c>
-      <c r="W171" s="2" t="s">
+      <c r="W171" t="s">
         <v>3567</v>
       </c>
-    </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y171" t="s">
+        <v>4895</v>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>174</v>
       </c>
@@ -30256,11 +30771,14 @@
       <c r="V172" t="s">
         <v>4239</v>
       </c>
-      <c r="W172" s="2" t="s">
+      <c r="W172" t="s">
         <v>3566</v>
       </c>
-    </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y172" t="s">
+        <v>4896</v>
+      </c>
+    </row>
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>175</v>
       </c>
@@ -30324,11 +30842,14 @@
       <c r="V173" t="s">
         <v>4240</v>
       </c>
-      <c r="W173" s="2" t="s">
+      <c r="W173" t="s">
         <v>3565</v>
       </c>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y173" t="s">
+        <v>4897</v>
+      </c>
+    </row>
+    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>176</v>
       </c>
@@ -30392,11 +30913,14 @@
       <c r="V174" t="s">
         <v>4241</v>
       </c>
-      <c r="W174" s="2" t="s">
+      <c r="W174" t="s">
         <v>3564</v>
       </c>
-    </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y174" t="s">
+        <v>4898</v>
+      </c>
+    </row>
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>177</v>
       </c>
@@ -30460,11 +30984,14 @@
       <c r="V175" t="s">
         <v>4242</v>
       </c>
-      <c r="W175" s="2" t="s">
+      <c r="W175" t="s">
         <v>3563</v>
       </c>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y175" t="s">
+        <v>4899</v>
+      </c>
+    </row>
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>178</v>
       </c>
@@ -30528,11 +31055,14 @@
       <c r="V176" t="s">
         <v>4243</v>
       </c>
-      <c r="W176" s="2" t="s">
+      <c r="W176" t="s">
         <v>3562</v>
       </c>
-    </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y176" t="s">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>179</v>
       </c>
@@ -30596,11 +31126,14 @@
       <c r="V177" t="s">
         <v>4244</v>
       </c>
-      <c r="W177" s="2" t="s">
+      <c r="W177" t="s">
         <v>3561</v>
       </c>
-    </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y177" t="s">
+        <v>4901</v>
+      </c>
+    </row>
+    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>180</v>
       </c>
@@ -30664,11 +31197,14 @@
       <c r="V178" t="s">
         <v>4245</v>
       </c>
-      <c r="W178" s="2" t="s">
+      <c r="W178" t="s">
         <v>3560</v>
       </c>
-    </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y178" t="s">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>181</v>
       </c>
@@ -30732,11 +31268,14 @@
       <c r="V179" t="s">
         <v>4246</v>
       </c>
-      <c r="W179" s="2" t="s">
+      <c r="W179" t="s">
         <v>3559</v>
       </c>
-    </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y179" t="s">
+        <v>4903</v>
+      </c>
+    </row>
+    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>182</v>
       </c>
@@ -30800,11 +31339,14 @@
       <c r="V180" t="s">
         <v>4247</v>
       </c>
-      <c r="W180" s="2" t="s">
+      <c r="W180" t="s">
         <v>3558</v>
       </c>
-    </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y180" t="s">
+        <v>4904</v>
+      </c>
+    </row>
+    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>183</v>
       </c>
@@ -30868,11 +31410,14 @@
       <c r="V181" t="s">
         <v>4248</v>
       </c>
-      <c r="W181" s="2" t="s">
+      <c r="W181" t="s">
         <v>3557</v>
       </c>
-    </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y181" t="s">
+        <v>4905</v>
+      </c>
+    </row>
+    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>184</v>
       </c>
@@ -30936,11 +31481,14 @@
       <c r="V182" t="s">
         <v>4249</v>
       </c>
-      <c r="W182" s="2" t="s">
+      <c r="W182" t="s">
         <v>3556</v>
       </c>
-    </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y182" t="s">
+        <v>4906</v>
+      </c>
+    </row>
+    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>185</v>
       </c>
@@ -31004,11 +31552,14 @@
       <c r="V183" t="s">
         <v>4250</v>
       </c>
-      <c r="W183" s="2" t="s">
+      <c r="W183" t="s">
         <v>3555</v>
       </c>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y183" t="s">
+        <v>4907</v>
+      </c>
+    </row>
+    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>186</v>
       </c>
@@ -31072,11 +31623,14 @@
       <c r="V184" t="s">
         <v>1250</v>
       </c>
-      <c r="W184" s="2" t="s">
+      <c r="W184" t="s">
         <v>3554</v>
       </c>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y184" t="s">
+        <v>4908</v>
+      </c>
+    </row>
+    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>187</v>
       </c>
@@ -31140,11 +31694,14 @@
       <c r="V185" t="s">
         <v>1249</v>
       </c>
-      <c r="W185" s="2" t="s">
+      <c r="W185" t="s">
         <v>3553</v>
       </c>
-    </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y185" t="s">
+        <v>4909</v>
+      </c>
+    </row>
+    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>188</v>
       </c>
@@ -31208,11 +31765,14 @@
       <c r="V186" t="s">
         <v>1248</v>
       </c>
-      <c r="W186" s="2" t="s">
+      <c r="W186" t="s">
         <v>3552</v>
       </c>
-    </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y186" t="s">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>189</v>
       </c>
@@ -31276,11 +31836,14 @@
       <c r="V187" t="s">
         <v>1246</v>
       </c>
-      <c r="W187" s="2" t="s">
+      <c r="W187" t="s">
         <v>3551</v>
       </c>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y187" t="s">
+        <v>4911</v>
+      </c>
+    </row>
+    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>190</v>
       </c>
@@ -31344,11 +31907,14 @@
       <c r="V188" t="s">
         <v>1244</v>
       </c>
-      <c r="W188" s="2" t="s">
+      <c r="W188" t="s">
         <v>3550</v>
       </c>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y188" t="s">
+        <v>4912</v>
+      </c>
+    </row>
+    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>191</v>
       </c>
@@ -31412,11 +31978,14 @@
       <c r="V189" t="s">
         <v>1243</v>
       </c>
-      <c r="W189" s="2" t="s">
+      <c r="W189" t="s">
         <v>3549</v>
       </c>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y189" t="s">
+        <v>4913</v>
+      </c>
+    </row>
+    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>192</v>
       </c>
@@ -31480,11 +32049,14 @@
       <c r="V190" t="s">
         <v>1242</v>
       </c>
-      <c r="W190" s="2" t="s">
+      <c r="W190" t="s">
         <v>3548</v>
       </c>
-    </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y190" t="s">
+        <v>4914</v>
+      </c>
+    </row>
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>193</v>
       </c>
@@ -31548,11 +32120,14 @@
       <c r="V191" t="s">
         <v>1241</v>
       </c>
-      <c r="W191" s="2" t="s">
+      <c r="W191" t="s">
         <v>3547</v>
       </c>
-    </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y191" t="s">
+        <v>4915</v>
+      </c>
+    </row>
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>194</v>
       </c>
@@ -31616,11 +32191,14 @@
       <c r="V192" t="s">
         <v>1240</v>
       </c>
-      <c r="W192" s="2" t="s">
+      <c r="W192" t="s">
         <v>3546</v>
       </c>
-    </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y192" t="s">
+        <v>4916</v>
+      </c>
+    </row>
+    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>195</v>
       </c>
@@ -31684,11 +32262,14 @@
       <c r="V193" t="s">
         <v>1239</v>
       </c>
-      <c r="W193" s="2" t="s">
+      <c r="W193" t="s">
         <v>3545</v>
       </c>
-    </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y193" t="s">
+        <v>4917</v>
+      </c>
+    </row>
+    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>196</v>
       </c>
@@ -31752,11 +32333,14 @@
       <c r="V194" t="s">
         <v>1238</v>
       </c>
-      <c r="W194" s="2" t="s">
+      <c r="W194" t="s">
         <v>3544</v>
       </c>
-    </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y194" t="s">
+        <v>4918</v>
+      </c>
+    </row>
+    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>197</v>
       </c>
@@ -31820,11 +32404,14 @@
       <c r="V195" t="s">
         <v>1237</v>
       </c>
-      <c r="W195" s="2" t="s">
+      <c r="W195" t="s">
         <v>3543</v>
       </c>
-    </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y195" t="s">
+        <v>4919</v>
+      </c>
+    </row>
+    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>198</v>
       </c>
@@ -31888,11 +32475,14 @@
       <c r="V196" t="s">
         <v>1236</v>
       </c>
-      <c r="W196" s="2" t="s">
+      <c r="W196" t="s">
         <v>3542</v>
       </c>
-    </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y196" t="s">
+        <v>4920</v>
+      </c>
+    </row>
+    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -31956,11 +32546,14 @@
       <c r="V197" t="s">
         <v>1235</v>
       </c>
-      <c r="W197" s="2" t="s">
+      <c r="W197" t="s">
         <v>3541</v>
       </c>
-    </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y197" t="s">
+        <v>4921</v>
+      </c>
+    </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>200</v>
       </c>
@@ -32024,11 +32617,14 @@
       <c r="V198" t="s">
         <v>1234</v>
       </c>
-      <c r="W198" s="2" t="s">
+      <c r="W198" t="s">
         <v>3540</v>
       </c>
-    </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y198" t="s">
+        <v>4922</v>
+      </c>
+    </row>
+    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>201</v>
       </c>
@@ -32092,11 +32688,14 @@
       <c r="V199" t="s">
         <v>1233</v>
       </c>
-      <c r="W199" s="2" t="s">
+      <c r="W199" t="s">
         <v>3539</v>
       </c>
-    </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y199" t="s">
+        <v>4923</v>
+      </c>
+    </row>
+    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>202</v>
       </c>
@@ -32160,11 +32759,14 @@
       <c r="V200" t="s">
         <v>4251</v>
       </c>
-      <c r="W200" s="2" t="s">
+      <c r="W200" t="s">
         <v>3538</v>
       </c>
-    </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y200" t="s">
+        <v>4924</v>
+      </c>
+    </row>
+    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>203</v>
       </c>
@@ -32225,11 +32827,14 @@
       <c r="V201" t="s">
         <v>4252</v>
       </c>
-      <c r="W201" s="2" t="s">
+      <c r="W201" t="s">
         <v>3537</v>
       </c>
-    </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y201" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>204</v>
       </c>
@@ -32290,11 +32895,14 @@
       <c r="V202" t="s">
         <v>4253</v>
       </c>
-      <c r="W202" s="2" t="s">
+      <c r="W202" t="s">
         <v>3536</v>
       </c>
-    </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y202" t="s">
+        <v>4926</v>
+      </c>
+    </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>205</v>
       </c>
@@ -32355,11 +32963,14 @@
       <c r="V203" t="s">
         <v>4254</v>
       </c>
-      <c r="W203" s="2" t="s">
+      <c r="W203" t="s">
         <v>3535</v>
       </c>
-    </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y203" t="s">
+        <v>4927</v>
+      </c>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>206</v>
       </c>
@@ -32420,11 +33031,14 @@
       <c r="V204" t="s">
         <v>4255</v>
       </c>
-      <c r="W204" s="2" t="s">
+      <c r="W204" t="s">
         <v>3534</v>
       </c>
-    </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y204" t="s">
+        <v>4928</v>
+      </c>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>207</v>
       </c>
@@ -32485,11 +33099,14 @@
       <c r="V205" t="s">
         <v>4256</v>
       </c>
-      <c r="W205" s="2" t="s">
+      <c r="W205" t="s">
         <v>3533</v>
       </c>
-    </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y205" t="s">
+        <v>4929</v>
+      </c>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>208</v>
       </c>
@@ -32550,11 +33167,14 @@
       <c r="V206" t="s">
         <v>4257</v>
       </c>
-      <c r="W206" s="2" t="s">
+      <c r="W206" t="s">
         <v>3532</v>
       </c>
-    </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y206" t="s">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>209</v>
       </c>
@@ -32615,11 +33235,14 @@
       <c r="V207" t="s">
         <v>4258</v>
       </c>
-      <c r="W207" s="2" t="s">
+      <c r="W207" t="s">
         <v>3531</v>
       </c>
-    </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y207" t="s">
+        <v>4931</v>
+      </c>
+    </row>
+    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>210</v>
       </c>
@@ -32680,11 +33303,14 @@
       <c r="V208" t="s">
         <v>4259</v>
       </c>
-      <c r="W208" s="2" t="s">
+      <c r="W208" t="s">
         <v>3530</v>
       </c>
-    </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y208" t="s">
+        <v>4932</v>
+      </c>
+    </row>
+    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>211</v>
       </c>
@@ -32745,11 +33371,14 @@
       <c r="V209" t="s">
         <v>4260</v>
       </c>
-      <c r="W209" s="2" t="s">
+      <c r="W209" t="s">
         <v>3529</v>
       </c>
-    </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y209" t="s">
+        <v>4933</v>
+      </c>
+    </row>
+    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>212</v>
       </c>
@@ -32810,11 +33439,14 @@
       <c r="V210" t="s">
         <v>4261</v>
       </c>
-      <c r="W210" s="2" t="s">
+      <c r="W210" t="s">
         <v>3528</v>
       </c>
-    </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y210" t="s">
+        <v>4934</v>
+      </c>
+    </row>
+    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>213</v>
       </c>
@@ -32875,11 +33507,14 @@
       <c r="V211" t="s">
         <v>4262</v>
       </c>
-      <c r="W211" s="2" t="s">
+      <c r="W211" t="s">
         <v>3527</v>
       </c>
-    </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y211" t="s">
+        <v>4935</v>
+      </c>
+    </row>
+    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>214</v>
       </c>
@@ -32940,11 +33575,14 @@
       <c r="V212" t="s">
         <v>4263</v>
       </c>
-      <c r="W212" s="2" t="s">
+      <c r="W212" t="s">
         <v>3526</v>
       </c>
-    </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y212" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>215</v>
       </c>
@@ -33005,11 +33643,14 @@
       <c r="V213" t="s">
         <v>4264</v>
       </c>
-      <c r="W213" s="2" t="s">
+      <c r="W213" t="s">
         <v>3525</v>
       </c>
-    </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y213" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>216</v>
       </c>
@@ -33070,11 +33711,14 @@
       <c r="V214" t="s">
         <v>4265</v>
       </c>
-      <c r="W214" s="2" t="s">
+      <c r="W214" t="s">
         <v>3524</v>
       </c>
-    </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y214" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>217</v>
       </c>
@@ -33135,11 +33779,14 @@
       <c r="V215" t="s">
         <v>4266</v>
       </c>
-      <c r="W215" s="2" t="s">
+      <c r="W215" t="s">
         <v>3523</v>
       </c>
-    </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y215" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>218</v>
       </c>
@@ -33200,11 +33847,14 @@
       <c r="V216" t="s">
         <v>4267</v>
       </c>
-      <c r="W216" s="2" t="s">
+      <c r="W216" t="s">
         <v>3522</v>
       </c>
-    </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y216" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>219</v>
       </c>
@@ -33265,11 +33915,14 @@
       <c r="V217" t="s">
         <v>4268</v>
       </c>
-      <c r="W217" s="2" t="s">
+      <c r="W217" t="s">
         <v>3521</v>
       </c>
-    </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y217" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>220</v>
       </c>
@@ -33330,11 +33983,14 @@
       <c r="V218" t="s">
         <v>4269</v>
       </c>
-      <c r="W218" s="2" t="s">
+      <c r="W218" t="s">
         <v>3520</v>
       </c>
-    </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y218" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>221</v>
       </c>
@@ -33395,11 +34051,14 @@
       <c r="V219" t="s">
         <v>4270</v>
       </c>
-      <c r="W219" s="2" t="s">
+      <c r="W219" t="s">
         <v>3519</v>
       </c>
-    </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y219" t="s">
+        <v>4936</v>
+      </c>
+    </row>
+    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>222</v>
       </c>
@@ -33460,11 +34119,14 @@
       <c r="V220" t="s">
         <v>4271</v>
       </c>
-      <c r="W220" s="2" t="s">
+      <c r="W220" t="s">
         <v>3518</v>
       </c>
-    </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y220" t="s">
+        <v>4937</v>
+      </c>
+    </row>
+    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>223</v>
       </c>
@@ -33525,11 +34187,14 @@
       <c r="V221" t="s">
         <v>4272</v>
       </c>
-      <c r="W221" s="2" t="s">
+      <c r="W221" t="s">
         <v>3517</v>
       </c>
-    </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y221" t="s">
+        <v>4938</v>
+      </c>
+    </row>
+    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>224</v>
       </c>
@@ -33590,11 +34255,14 @@
       <c r="V222" t="s">
         <v>4273</v>
       </c>
-      <c r="W222" s="2" t="s">
+      <c r="W222" t="s">
         <v>3516</v>
       </c>
-    </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y222" t="s">
+        <v>4939</v>
+      </c>
+    </row>
+    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>225</v>
       </c>
@@ -33655,11 +34323,14 @@
       <c r="V223" t="s">
         <v>4274</v>
       </c>
-      <c r="W223" s="2" t="s">
+      <c r="W223" t="s">
         <v>3515</v>
       </c>
-    </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y223" t="s">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>226</v>
       </c>
@@ -33720,11 +34391,14 @@
       <c r="V224" t="s">
         <v>4275</v>
       </c>
-      <c r="W224" s="2" t="s">
+      <c r="W224" t="s">
         <v>3514</v>
       </c>
-    </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y224" t="s">
+        <v>4941</v>
+      </c>
+    </row>
+    <row r="225" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>227</v>
       </c>
@@ -33785,11 +34459,14 @@
       <c r="V225" t="s">
         <v>4276</v>
       </c>
-      <c r="W225" s="2" t="s">
+      <c r="W225" t="s">
         <v>3513</v>
       </c>
-    </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y225" t="s">
+        <v>4942</v>
+      </c>
+    </row>
+    <row r="226" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>228</v>
       </c>
@@ -33850,11 +34527,14 @@
       <c r="V226" t="s">
         <v>4277</v>
       </c>
-      <c r="W226" s="2" t="s">
+      <c r="W226" t="s">
         <v>3512</v>
       </c>
-    </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y226" t="s">
+        <v>4943</v>
+      </c>
+    </row>
+    <row r="227" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>229</v>
       </c>
@@ -33915,11 +34595,14 @@
       <c r="V227" t="s">
         <v>4278</v>
       </c>
-      <c r="W227" s="2" t="s">
+      <c r="W227" t="s">
         <v>3511</v>
       </c>
-    </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y227" t="s">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="228" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>230</v>
       </c>
@@ -33980,11 +34663,14 @@
       <c r="V228" t="s">
         <v>4279</v>
       </c>
-      <c r="W228" s="2" t="s">
+      <c r="W228" t="s">
         <v>3510</v>
       </c>
-    </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y228" t="s">
+        <v>4945</v>
+      </c>
+    </row>
+    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>231</v>
       </c>
@@ -34045,11 +34731,14 @@
       <c r="V229" t="s">
         <v>4280</v>
       </c>
-      <c r="W229" s="2" t="s">
+      <c r="W229" t="s">
         <v>3509</v>
       </c>
-    </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y229" t="s">
+        <v>4946</v>
+      </c>
+    </row>
+    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>232</v>
       </c>
@@ -34110,11 +34799,14 @@
       <c r="V230" t="s">
         <v>4281</v>
       </c>
-      <c r="W230" s="2" t="s">
+      <c r="W230" t="s">
         <v>3508</v>
       </c>
-    </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y230" t="s">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>233</v>
       </c>
@@ -34175,11 +34867,14 @@
       <c r="V231" t="s">
         <v>4282</v>
       </c>
-      <c r="W231" s="2" t="s">
+      <c r="W231" t="s">
         <v>3507</v>
       </c>
-    </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y231" t="s">
+        <v>4948</v>
+      </c>
+    </row>
+    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>234</v>
       </c>
@@ -34240,11 +34935,14 @@
       <c r="V232" t="s">
         <v>4283</v>
       </c>
-      <c r="W232" s="2" t="s">
+      <c r="W232" t="s">
         <v>3506</v>
       </c>
-    </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y232" t="s">
+        <v>4949</v>
+      </c>
+    </row>
+    <row r="233" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>235</v>
       </c>
@@ -34305,11 +35003,14 @@
       <c r="V233" t="s">
         <v>4284</v>
       </c>
-      <c r="W233" s="2" t="s">
+      <c r="W233" t="s">
         <v>3505</v>
       </c>
-    </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y233" t="s">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="234" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>236</v>
       </c>
@@ -34370,11 +35071,14 @@
       <c r="V234" t="s">
         <v>4285</v>
       </c>
-      <c r="W234" s="2" t="s">
+      <c r="W234" t="s">
         <v>3504</v>
       </c>
-    </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y234" t="s">
+        <v>4951</v>
+      </c>
+    </row>
+    <row r="235" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>237</v>
       </c>
@@ -34435,11 +35139,14 @@
       <c r="V235" t="s">
         <v>4286</v>
       </c>
-      <c r="W235" s="2" t="s">
+      <c r="W235" t="s">
         <v>3503</v>
       </c>
-    </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y235" t="s">
+        <v>4952</v>
+      </c>
+    </row>
+    <row r="236" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>238</v>
       </c>
@@ -34500,11 +35207,14 @@
       <c r="V236" t="s">
         <v>4287</v>
       </c>
-      <c r="W236" s="2" t="s">
+      <c r="W236" t="s">
         <v>3502</v>
       </c>
-    </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y236" t="s">
+        <v>4953</v>
+      </c>
+    </row>
+    <row r="237" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>239</v>
       </c>
@@ -34565,11 +35275,14 @@
       <c r="V237" t="s">
         <v>4288</v>
       </c>
-      <c r="W237" s="2" t="s">
+      <c r="W237" t="s">
         <v>3501</v>
       </c>
-    </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y237" t="s">
+        <v>4954</v>
+      </c>
+    </row>
+    <row r="238" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>240</v>
       </c>
@@ -34630,11 +35343,14 @@
       <c r="V238" t="s">
         <v>4289</v>
       </c>
-      <c r="W238" s="2" t="s">
+      <c r="W238" t="s">
         <v>3500</v>
       </c>
-    </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y238" t="s">
+        <v>4955</v>
+      </c>
+    </row>
+    <row r="239" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>241</v>
       </c>
@@ -34695,11 +35411,14 @@
       <c r="V239" t="s">
         <v>4290</v>
       </c>
-      <c r="W239" s="2" t="s">
+      <c r="W239" t="s">
         <v>3499</v>
       </c>
-    </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y239" t="s">
+        <v>4956</v>
+      </c>
+    </row>
+    <row r="240" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>242</v>
       </c>
@@ -34760,11 +35479,14 @@
       <c r="V240" t="s">
         <v>4291</v>
       </c>
-      <c r="W240" s="2" t="s">
+      <c r="W240" t="s">
         <v>3498</v>
       </c>
-    </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y240" t="s">
+        <v>4957</v>
+      </c>
+    </row>
+    <row r="241" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>243</v>
       </c>
@@ -34825,11 +35547,14 @@
       <c r="V241" t="s">
         <v>4292</v>
       </c>
-      <c r="W241" s="2" t="s">
+      <c r="W241" t="s">
         <v>3497</v>
       </c>
-    </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y241" t="s">
+        <v>4958</v>
+      </c>
+    </row>
+    <row r="242" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>244</v>
       </c>
@@ -34890,11 +35615,14 @@
       <c r="V242" t="s">
         <v>4293</v>
       </c>
-      <c r="W242" s="2" t="s">
+      <c r="W242" t="s">
         <v>3496</v>
       </c>
-    </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y242" t="s">
+        <v>4959</v>
+      </c>
+    </row>
+    <row r="243" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>245</v>
       </c>
@@ -34955,11 +35683,14 @@
       <c r="V243" t="s">
         <v>4294</v>
       </c>
-      <c r="W243" s="2" t="s">
+      <c r="W243" t="s">
         <v>3495</v>
       </c>
-    </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y243" t="s">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="244" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>246</v>
       </c>
@@ -35020,11 +35751,14 @@
       <c r="V244" t="s">
         <v>4295</v>
       </c>
-      <c r="W244" s="2" t="s">
+      <c r="W244" t="s">
         <v>3494</v>
       </c>
-    </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y244" t="s">
+        <v>4961</v>
+      </c>
+    </row>
+    <row r="245" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>247</v>
       </c>
@@ -35085,11 +35819,14 @@
       <c r="V245" t="s">
         <v>4296</v>
       </c>
-      <c r="W245" s="2" t="s">
+      <c r="W245" t="s">
         <v>3493</v>
       </c>
-    </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y245" t="s">
+        <v>4962</v>
+      </c>
+    </row>
+    <row r="246" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>248</v>
       </c>
@@ -35150,11 +35887,14 @@
       <c r="V246" t="s">
         <v>4297</v>
       </c>
-      <c r="W246" s="2" t="s">
+      <c r="W246" t="s">
         <v>3492</v>
       </c>
-    </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y246" t="s">
+        <v>4963</v>
+      </c>
+    </row>
+    <row r="247" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>249</v>
       </c>
@@ -35215,11 +35955,14 @@
       <c r="V247" t="s">
         <v>4298</v>
       </c>
-      <c r="W247" s="2" t="s">
+      <c r="W247" t="s">
         <v>3491</v>
       </c>
-    </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y247" t="s">
+        <v>4964</v>
+      </c>
+    </row>
+    <row r="248" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>250</v>
       </c>
@@ -35280,11 +36023,14 @@
       <c r="V248" t="s">
         <v>4299</v>
       </c>
-      <c r="W248" s="2" t="s">
+      <c r="W248" t="s">
         <v>3490</v>
       </c>
-    </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y248" t="s">
+        <v>4965</v>
+      </c>
+    </row>
+    <row r="249" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>251</v>
       </c>
@@ -35345,11 +36091,14 @@
       <c r="V249" t="s">
         <v>4300</v>
       </c>
-      <c r="W249" s="2" t="s">
+      <c r="W249" t="s">
         <v>3489</v>
       </c>
-    </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y249" t="s">
+        <v>4966</v>
+      </c>
+    </row>
+    <row r="250" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>252</v>
       </c>
@@ -35410,11 +36159,14 @@
       <c r="V250" t="s">
         <v>4301</v>
       </c>
-      <c r="W250" s="2" t="s">
+      <c r="W250" t="s">
         <v>3488</v>
       </c>
-    </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y250" t="s">
+        <v>4967</v>
+      </c>
+    </row>
+    <row r="251" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>253</v>
       </c>
@@ -35475,11 +36227,14 @@
       <c r="V251" t="s">
         <v>4302</v>
       </c>
-      <c r="W251" s="2" t="s">
+      <c r="W251" t="s">
         <v>3487</v>
       </c>
-    </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y251" t="s">
+        <v>4968</v>
+      </c>
+    </row>
+    <row r="252" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>254</v>
       </c>
@@ -35540,11 +36295,14 @@
       <c r="V252" t="s">
         <v>4303</v>
       </c>
-      <c r="W252" s="2" t="s">
+      <c r="W252" t="s">
         <v>3486</v>
       </c>
-    </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y252" t="s">
+        <v>4969</v>
+      </c>
+    </row>
+    <row r="253" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>255</v>
       </c>
@@ -35605,11 +36363,14 @@
       <c r="V253" t="s">
         <v>4304</v>
       </c>
-      <c r="W253" s="2" t="s">
+      <c r="W253" t="s">
         <v>3485</v>
       </c>
-    </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y253" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="254" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>256</v>
       </c>
@@ -35670,11 +36431,14 @@
       <c r="V254" t="s">
         <v>4305</v>
       </c>
-      <c r="W254" s="2" t="s">
+      <c r="W254" t="s">
         <v>3484</v>
       </c>
-    </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y254" t="s">
+        <v>4971</v>
+      </c>
+    </row>
+    <row r="255" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>256</v>
       </c>
@@ -35735,11 +36499,14 @@
       <c r="V255" t="s">
         <v>4306</v>
       </c>
-      <c r="W255" s="2" t="s">
+      <c r="W255" t="s">
         <v>3483</v>
       </c>
-    </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y255" t="s">
+        <v>4972</v>
+      </c>
+    </row>
+    <row r="256" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>257</v>
       </c>
@@ -35800,11 +36567,14 @@
       <c r="V256" t="s">
         <v>4307</v>
       </c>
-      <c r="W256" s="2" t="s">
+      <c r="W256" t="s">
         <v>3482</v>
       </c>
-    </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y256" t="s">
+        <v>4973</v>
+      </c>
+    </row>
+    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>257</v>
       </c>
@@ -35865,11 +36635,14 @@
       <c r="V257" t="s">
         <v>4308</v>
       </c>
-      <c r="W257" s="2" t="s">
+      <c r="W257" t="s">
         <v>3481</v>
       </c>
-    </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y257" t="s">
+        <v>4974</v>
+      </c>
+    </row>
+    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>258</v>
       </c>
@@ -35930,11 +36703,14 @@
       <c r="V258" t="s">
         <v>4309</v>
       </c>
-      <c r="W258" s="2" t="s">
+      <c r="W258" t="s">
         <v>3480</v>
       </c>
-    </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y258" t="s">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>259</v>
       </c>
@@ -35995,11 +36771,14 @@
       <c r="V259" t="s">
         <v>4310</v>
       </c>
-      <c r="W259" s="2" t="s">
+      <c r="W259" t="s">
         <v>3479</v>
       </c>
-    </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y259" t="s">
+        <v>4976</v>
+      </c>
+    </row>
+    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>260</v>
       </c>
@@ -36060,11 +36839,14 @@
       <c r="V260" t="s">
         <v>4311</v>
       </c>
-      <c r="W260" s="2" t="s">
+      <c r="W260" t="s">
         <v>3478</v>
       </c>
-    </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y260" t="s">
+        <v>4977</v>
+      </c>
+    </row>
+    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>261</v>
       </c>
@@ -36125,11 +36907,14 @@
       <c r="V261" t="s">
         <v>1166</v>
       </c>
-      <c r="W261" s="2" t="s">
+      <c r="W261" t="s">
         <v>3477</v>
       </c>
-    </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y261" t="s">
+        <v>4978</v>
+      </c>
+    </row>
+    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>262</v>
       </c>
@@ -36190,11 +36975,14 @@
       <c r="V262" t="s">
         <v>1165</v>
       </c>
-      <c r="W262" s="2" t="s">
+      <c r="W262" t="s">
         <v>3476</v>
       </c>
-    </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y262" t="s">
+        <v>4979</v>
+      </c>
+    </row>
+    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>263</v>
       </c>
@@ -36255,11 +37043,14 @@
       <c r="V263" t="s">
         <v>1164</v>
       </c>
-      <c r="W263" s="2" t="s">
+      <c r="W263" t="s">
         <v>3475</v>
       </c>
-    </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y263" t="s">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>264</v>
       </c>
@@ -36320,11 +37111,14 @@
       <c r="V264" t="s">
         <v>1162</v>
       </c>
-      <c r="W264" s="2" t="s">
+      <c r="W264" t="s">
         <v>3474</v>
       </c>
-    </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y264" t="s">
+        <v>4981</v>
+      </c>
+    </row>
+    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>265</v>
       </c>
@@ -36385,11 +37179,14 @@
       <c r="V265" t="s">
         <v>1160</v>
       </c>
-      <c r="W265" s="2" t="s">
+      <c r="W265" t="s">
         <v>3473</v>
       </c>
-    </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y265" t="s">
+        <v>4982</v>
+      </c>
+    </row>
+    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>266</v>
       </c>
@@ -36450,11 +37247,14 @@
       <c r="V266" t="s">
         <v>1159</v>
       </c>
-      <c r="W266" s="2" t="s">
+      <c r="W266" t="s">
         <v>3472</v>
       </c>
-    </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y266" t="s">
+        <v>4983</v>
+      </c>
+    </row>
+    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>267</v>
       </c>
@@ -36515,11 +37315,14 @@
       <c r="V267" t="s">
         <v>1158</v>
       </c>
-      <c r="W267" s="2" t="s">
+      <c r="W267" t="s">
         <v>3471</v>
       </c>
-    </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y267" t="s">
+        <v>4984</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>268</v>
       </c>
@@ -36580,11 +37383,14 @@
       <c r="V268" t="s">
         <v>1157</v>
       </c>
-      <c r="W268" s="2" t="s">
+      <c r="W268" t="s">
         <v>3470</v>
       </c>
-    </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y268" t="s">
+        <v>4985</v>
+      </c>
+    </row>
+    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>269</v>
       </c>
@@ -36645,11 +37451,14 @@
       <c r="V269" t="s">
         <v>1156</v>
       </c>
-      <c r="W269" s="2" t="s">
+      <c r="W269" t="s">
         <v>3469</v>
       </c>
-    </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y269" t="s">
+        <v>4986</v>
+      </c>
+    </row>
+    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>270</v>
       </c>
@@ -36710,11 +37519,14 @@
       <c r="V270" t="s">
         <v>1155</v>
       </c>
-      <c r="W270" s="2" t="s">
+      <c r="W270" t="s">
         <v>3468</v>
       </c>
-    </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y270" t="s">
+        <v>4987</v>
+      </c>
+    </row>
+    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>271</v>
       </c>
@@ -36775,11 +37587,14 @@
       <c r="V271" t="s">
         <v>1154</v>
       </c>
-      <c r="W271" s="2" t="s">
+      <c r="W271" t="s">
         <v>3467</v>
       </c>
-    </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y271" t="s">
+        <v>4988</v>
+      </c>
+    </row>
+    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>272</v>
       </c>
@@ -36840,11 +37655,14 @@
       <c r="V272" t="s">
         <v>1153</v>
       </c>
-      <c r="W272" s="2" t="s">
+      <c r="W272" t="s">
         <v>1435</v>
       </c>
-    </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y272" t="s">
+        <v>4989</v>
+      </c>
+    </row>
+    <row r="273" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>273</v>
       </c>
@@ -36905,11 +37723,14 @@
       <c r="V273" t="s">
         <v>1152</v>
       </c>
-      <c r="W273" s="2" t="s">
+      <c r="W273" t="s">
         <v>1434</v>
       </c>
-    </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y273" t="s">
+        <v>4990</v>
+      </c>
+    </row>
+    <row r="274" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>274</v>
       </c>
@@ -36970,11 +37791,14 @@
       <c r="V274" t="s">
         <v>1151</v>
       </c>
-      <c r="W274" s="2" t="s">
+      <c r="W274" t="s">
         <v>1433</v>
       </c>
-    </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y274" t="s">
+        <v>4991</v>
+      </c>
+    </row>
+    <row r="275" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>275</v>
       </c>
@@ -37035,11 +37859,14 @@
       <c r="V275" t="s">
         <v>1150</v>
       </c>
-      <c r="W275" s="2" t="s">
+      <c r="W275" t="s">
         <v>1432</v>
       </c>
-    </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y275" t="s">
+        <v>4992</v>
+      </c>
+    </row>
+    <row r="276" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>276</v>
       </c>
@@ -37100,8 +37927,11 @@
       <c r="V276" t="s">
         <v>1149</v>
       </c>
-    </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y276" t="s">
+        <v>4993</v>
+      </c>
+    </row>
+    <row r="277" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>277</v>
       </c>
@@ -37162,8 +37992,11 @@
       <c r="V277" t="s">
         <v>4312</v>
       </c>
-    </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y277" t="s">
+        <v>4994</v>
+      </c>
+    </row>
+    <row r="278" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>278</v>
       </c>
@@ -37224,8 +38057,11 @@
       <c r="V278" t="s">
         <v>4313</v>
       </c>
-    </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y278" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="279" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>279</v>
       </c>
@@ -37286,8 +38122,11 @@
       <c r="V279" t="s">
         <v>4314</v>
       </c>
-    </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y279" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="280" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>280</v>
       </c>
@@ -37348,8 +38187,11 @@
       <c r="V280" t="s">
         <v>4315</v>
       </c>
-    </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y280" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="281" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>281</v>
       </c>
@@ -37410,8 +38252,11 @@
       <c r="V281" t="s">
         <v>4316</v>
       </c>
-    </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y281" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="282" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>282</v>
       </c>
@@ -37472,8 +38317,11 @@
       <c r="V282" t="s">
         <v>4317</v>
       </c>
-    </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y282" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="283" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>283</v>
       </c>
@@ -37534,8 +38382,11 @@
       <c r="V283" t="s">
         <v>4318</v>
       </c>
-    </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y283" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="284" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>284</v>
       </c>
@@ -37593,8 +38444,11 @@
       <c r="V284" t="s">
         <v>4319</v>
       </c>
-    </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y284" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="285" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>285</v>
       </c>
@@ -37652,8 +38506,11 @@
       <c r="V285" t="s">
         <v>4320</v>
       </c>
-    </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y285" t="s">
+        <v>4995</v>
+      </c>
+    </row>
+    <row r="286" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>286</v>
       </c>
@@ -37711,8 +38568,11 @@
       <c r="V286" t="s">
         <v>4321</v>
       </c>
-    </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y286" t="s">
+        <v>4996</v>
+      </c>
+    </row>
+    <row r="287" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>287</v>
       </c>
@@ -37770,8 +38630,11 @@
       <c r="V287" t="s">
         <v>4322</v>
       </c>
-    </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y287" t="s">
+        <v>4997</v>
+      </c>
+    </row>
+    <row r="288" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>287</v>
       </c>
@@ -37829,8 +38692,11 @@
       <c r="V288" t="s">
         <v>4323</v>
       </c>
-    </row>
-    <row r="289" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y288" t="s">
+        <v>4998</v>
+      </c>
+    </row>
+    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>288</v>
       </c>
@@ -37888,8 +38754,11 @@
       <c r="V289" t="s">
         <v>4324</v>
       </c>
-    </row>
-    <row r="290" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y289" t="s">
+        <v>4999</v>
+      </c>
+    </row>
+    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>288</v>
       </c>
@@ -37947,8 +38816,11 @@
       <c r="V290" t="s">
         <v>4325</v>
       </c>
-    </row>
-    <row r="291" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y290" t="s">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>289</v>
       </c>
@@ -38006,8 +38878,11 @@
       <c r="V291" t="s">
         <v>4326</v>
       </c>
-    </row>
-    <row r="292" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y291" t="s">
+        <v>5001</v>
+      </c>
+    </row>
+    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>290</v>
       </c>
@@ -38065,8 +38940,11 @@
       <c r="V292" t="s">
         <v>4327</v>
       </c>
-    </row>
-    <row r="293" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y292" t="s">
+        <v>5002</v>
+      </c>
+    </row>
+    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>291</v>
       </c>
@@ -38124,8 +39002,11 @@
       <c r="V293" t="s">
         <v>4328</v>
       </c>
-    </row>
-    <row r="294" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y293" t="s">
+        <v>5003</v>
+      </c>
+    </row>
+    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>292</v>
       </c>
@@ -38183,8 +39064,11 @@
       <c r="V294" t="s">
         <v>4329</v>
       </c>
-    </row>
-    <row r="295" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y294" t="s">
+        <v>5004</v>
+      </c>
+    </row>
+    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>293</v>
       </c>
@@ -38242,8 +39126,11 @@
       <c r="V295" t="s">
         <v>4330</v>
       </c>
-    </row>
-    <row r="296" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y295" t="s">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>294</v>
       </c>
@@ -38301,8 +39188,11 @@
       <c r="V296" t="s">
         <v>4331</v>
       </c>
-    </row>
-    <row r="297" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y296" t="s">
+        <v>5006</v>
+      </c>
+    </row>
+    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>295</v>
       </c>
@@ -38360,8 +39250,11 @@
       <c r="V297" t="s">
         <v>4332</v>
       </c>
-    </row>
-    <row r="298" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y297" t="s">
+        <v>5007</v>
+      </c>
+    </row>
+    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>296</v>
       </c>
@@ -38419,8 +39312,11 @@
       <c r="V298" t="s">
         <v>4333</v>
       </c>
-    </row>
-    <row r="299" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y298" t="s">
+        <v>5008</v>
+      </c>
+    </row>
+    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>297</v>
       </c>
@@ -38478,8 +39374,11 @@
       <c r="V299" t="s">
         <v>4334</v>
       </c>
-    </row>
-    <row r="300" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y299" t="s">
+        <v>5009</v>
+      </c>
+    </row>
+    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>298</v>
       </c>
@@ -38537,8 +39436,11 @@
       <c r="V300" t="s">
         <v>4335</v>
       </c>
-    </row>
-    <row r="301" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y300" t="s">
+        <v>5010</v>
+      </c>
+    </row>
+    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>299</v>
       </c>
@@ -38596,8 +39498,11 @@
       <c r="V301" t="s">
         <v>4336</v>
       </c>
-    </row>
-    <row r="302" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y301" t="s">
+        <v>5011</v>
+      </c>
+    </row>
+    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>300</v>
       </c>
@@ -38655,8 +39560,11 @@
       <c r="V302" t="s">
         <v>4337</v>
       </c>
-    </row>
-    <row r="303" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y302" t="s">
+        <v>5012</v>
+      </c>
+    </row>
+    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>301</v>
       </c>
@@ -38714,8 +39622,11 @@
       <c r="V303" t="s">
         <v>4338</v>
       </c>
-    </row>
-    <row r="304" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y303" t="s">
+        <v>5013</v>
+      </c>
+    </row>
+    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>302</v>
       </c>
@@ -38773,8 +39684,11 @@
       <c r="V304" t="s">
         <v>4339</v>
       </c>
-    </row>
-    <row r="305" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y304" t="s">
+        <v>5014</v>
+      </c>
+    </row>
+    <row r="305" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>303</v>
       </c>
@@ -38832,8 +39746,11 @@
       <c r="V305" t="s">
         <v>4340</v>
       </c>
-    </row>
-    <row r="306" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y305" t="s">
+        <v>5015</v>
+      </c>
+    </row>
+    <row r="306" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>304</v>
       </c>
@@ -38891,8 +39808,11 @@
       <c r="V306" t="s">
         <v>4341</v>
       </c>
-    </row>
-    <row r="307" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y306" t="s">
+        <v>5016</v>
+      </c>
+    </row>
+    <row r="307" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>305</v>
       </c>
@@ -38950,8 +39870,11 @@
       <c r="V307" t="s">
         <v>4342</v>
       </c>
-    </row>
-    <row r="308" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y307" t="s">
+        <v>5017</v>
+      </c>
+    </row>
+    <row r="308" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>306</v>
       </c>
@@ -39009,8 +39932,11 @@
       <c r="V308" t="s">
         <v>4343</v>
       </c>
-    </row>
-    <row r="309" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y308" t="s">
+        <v>5018</v>
+      </c>
+    </row>
+    <row r="309" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>307</v>
       </c>
@@ -39068,8 +39994,11 @@
       <c r="V309" t="s">
         <v>4344</v>
       </c>
-    </row>
-    <row r="310" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y309" t="s">
+        <v>5019</v>
+      </c>
+    </row>
+    <row r="310" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>308</v>
       </c>
@@ -39127,8 +40056,11 @@
       <c r="V310" t="s">
         <v>4345</v>
       </c>
-    </row>
-    <row r="311" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y310" t="s">
+        <v>5020</v>
+      </c>
+    </row>
+    <row r="311" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>309</v>
       </c>
@@ -39186,8 +40118,11 @@
       <c r="V311" t="s">
         <v>4346</v>
       </c>
-    </row>
-    <row r="312" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y311" t="s">
+        <v>5021</v>
+      </c>
+    </row>
+    <row r="312" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>310</v>
       </c>
@@ -39245,8 +40180,11 @@
       <c r="V312" t="s">
         <v>4347</v>
       </c>
-    </row>
-    <row r="313" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y312" t="s">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="313" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>311</v>
       </c>
@@ -39304,8 +40242,11 @@
       <c r="V313" t="s">
         <v>4348</v>
       </c>
-    </row>
-    <row r="314" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y313" t="s">
+        <v>5023</v>
+      </c>
+    </row>
+    <row r="314" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>312</v>
       </c>
@@ -39363,8 +40304,11 @@
       <c r="V314" t="s">
         <v>4349</v>
       </c>
-    </row>
-    <row r="315" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y314" t="s">
+        <v>5024</v>
+      </c>
+    </row>
+    <row r="315" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>313</v>
       </c>
@@ -39422,8 +40366,11 @@
       <c r="V315" t="s">
         <v>4350</v>
       </c>
-    </row>
-    <row r="316" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y315" t="s">
+        <v>5025</v>
+      </c>
+    </row>
+    <row r="316" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>314</v>
       </c>
@@ -39481,8 +40428,11 @@
       <c r="V316" t="s">
         <v>4351</v>
       </c>
-    </row>
-    <row r="317" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y316" t="s">
+        <v>5026</v>
+      </c>
+    </row>
+    <row r="317" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>315</v>
       </c>
@@ -39540,8 +40490,11 @@
       <c r="V317" t="s">
         <v>4352</v>
       </c>
-    </row>
-    <row r="318" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y317" t="s">
+        <v>5027</v>
+      </c>
+    </row>
+    <row r="318" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>316</v>
       </c>
@@ -39599,8 +40552,11 @@
       <c r="V318" t="s">
         <v>4353</v>
       </c>
-    </row>
-    <row r="319" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y318" t="s">
+        <v>5028</v>
+      </c>
+    </row>
+    <row r="319" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>317</v>
       </c>
@@ -39658,8 +40614,11 @@
       <c r="V319" t="s">
         <v>4354</v>
       </c>
-    </row>
-    <row r="320" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y319" t="s">
+        <v>5029</v>
+      </c>
+    </row>
+    <row r="320" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>318</v>
       </c>
@@ -39717,8 +40676,11 @@
       <c r="V320" t="s">
         <v>4355</v>
       </c>
-    </row>
-    <row r="321" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y320" t="s">
+        <v>5030</v>
+      </c>
+    </row>
+    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>319</v>
       </c>
@@ -39776,8 +40738,11 @@
       <c r="V321" t="s">
         <v>4356</v>
       </c>
-    </row>
-    <row r="322" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y321" t="s">
+        <v>5031</v>
+      </c>
+    </row>
+    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>320</v>
       </c>
@@ -39835,8 +40800,11 @@
       <c r="V322" t="s">
         <v>4357</v>
       </c>
-    </row>
-    <row r="323" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y322" t="s">
+        <v>5032</v>
+      </c>
+    </row>
+    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>321</v>
       </c>
@@ -39894,8 +40862,11 @@
       <c r="V323" t="s">
         <v>4358</v>
       </c>
-    </row>
-    <row r="324" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y323" t="s">
+        <v>5033</v>
+      </c>
+    </row>
+    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>322</v>
       </c>
@@ -39953,8 +40924,11 @@
       <c r="V324" t="s">
         <v>4359</v>
       </c>
-    </row>
-    <row r="325" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y324" t="s">
+        <v>5034</v>
+      </c>
+    </row>
+    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>323</v>
       </c>
@@ -40012,8 +40986,11 @@
       <c r="V325" t="s">
         <v>4360</v>
       </c>
-    </row>
-    <row r="326" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y325" t="s">
+        <v>5035</v>
+      </c>
+    </row>
+    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>324</v>
       </c>
@@ -40071,8 +41048,11 @@
       <c r="V326" t="s">
         <v>4361</v>
       </c>
-    </row>
-    <row r="327" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y326" t="s">
+        <v>5036</v>
+      </c>
+    </row>
+    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>325</v>
       </c>
@@ -40130,8 +41110,11 @@
       <c r="V327" t="s">
         <v>4362</v>
       </c>
-    </row>
-    <row r="328" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y327" t="s">
+        <v>5037</v>
+      </c>
+    </row>
+    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>326</v>
       </c>
@@ -40189,8 +41172,11 @@
       <c r="V328" t="s">
         <v>4363</v>
       </c>
-    </row>
-    <row r="329" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y328" t="s">
+        <v>5038</v>
+      </c>
+    </row>
+    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>327</v>
       </c>
@@ -40248,8 +41234,11 @@
       <c r="V329" t="s">
         <v>4364</v>
       </c>
-    </row>
-    <row r="330" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y329" t="s">
+        <v>5039</v>
+      </c>
+    </row>
+    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>328</v>
       </c>
@@ -40307,8 +41296,11 @@
       <c r="V330" t="s">
         <v>4365</v>
       </c>
-    </row>
-    <row r="331" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y330" t="s">
+        <v>5040</v>
+      </c>
+    </row>
+    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>329</v>
       </c>
@@ -40366,8 +41358,11 @@
       <c r="V331" t="s">
         <v>4366</v>
       </c>
-    </row>
-    <row r="332" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y331" t="s">
+        <v>5041</v>
+      </c>
+    </row>
+    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>330</v>
       </c>
@@ -40425,8 +41420,11 @@
       <c r="V332" t="s">
         <v>4367</v>
       </c>
-    </row>
-    <row r="333" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y332" t="s">
+        <v>5042</v>
+      </c>
+    </row>
+    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C333" t="s">
         <v>816</v>
       </c>
@@ -40481,8 +41479,11 @@
       <c r="V333" t="s">
         <v>4368</v>
       </c>
-    </row>
-    <row r="334" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y333" t="s">
+        <v>5043</v>
+      </c>
+    </row>
+    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C334" t="s">
         <v>817</v>
       </c>
@@ -40537,8 +41538,11 @@
       <c r="V334" t="s">
         <v>4369</v>
       </c>
-    </row>
-    <row r="335" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y334" t="s">
+        <v>5044</v>
+      </c>
+    </row>
+    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C335" t="s">
         <v>818</v>
       </c>
@@ -40593,8 +41597,11 @@
       <c r="V335" t="s">
         <v>4370</v>
       </c>
-    </row>
-    <row r="336" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y335" t="s">
+        <v>5045</v>
+      </c>
+    </row>
+    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C336" t="s">
         <v>819</v>
       </c>
@@ -40649,8 +41656,11 @@
       <c r="V336" t="s">
         <v>4371</v>
       </c>
-    </row>
-    <row r="337" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y336" t="s">
+        <v>5046</v>
+      </c>
+    </row>
+    <row r="337" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C337" t="s">
         <v>820</v>
       </c>
@@ -40705,8 +41715,11 @@
       <c r="V337" t="s">
         <v>4372</v>
       </c>
-    </row>
-    <row r="338" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y337" t="s">
+        <v>5047</v>
+      </c>
+    </row>
+    <row r="338" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C338" t="s">
         <v>821</v>
       </c>
@@ -40761,8 +41774,11 @@
       <c r="V338" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="339" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y338" t="s">
+        <v>5048</v>
+      </c>
+    </row>
+    <row r="339" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C339" t="s">
         <v>822</v>
       </c>
@@ -40817,8 +41833,11 @@
       <c r="V339" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="340" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y339" t="s">
+        <v>5049</v>
+      </c>
+    </row>
+    <row r="340" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C340" t="s">
         <v>823</v>
       </c>
@@ -40873,8 +41892,11 @@
       <c r="V340" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="341" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y340" t="s">
+        <v>5050</v>
+      </c>
+    </row>
+    <row r="341" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C341" t="s">
         <v>824</v>
       </c>
@@ -40929,8 +41951,11 @@
       <c r="V341" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="342" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y341" t="s">
+        <v>5051</v>
+      </c>
+    </row>
+    <row r="342" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C342" t="s">
         <v>825</v>
       </c>
@@ -40985,8 +42010,11 @@
       <c r="V342" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="343" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y342" t="s">
+        <v>5052</v>
+      </c>
+    </row>
+    <row r="343" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C343" t="s">
         <v>826</v>
       </c>
@@ -41041,8 +42069,11 @@
       <c r="V343" t="s">
         <v>1073</v>
       </c>
-    </row>
-    <row r="344" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y343" t="s">
+        <v>5053</v>
+      </c>
+    </row>
+    <row r="344" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C344" t="s">
         <v>827</v>
       </c>
@@ -41097,8 +42128,11 @@
       <c r="V344" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="345" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y344" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="345" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C345" t="s">
         <v>828</v>
       </c>
@@ -41153,8 +42187,11 @@
       <c r="V345" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="346" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y345" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="346" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C346" t="s">
         <v>829</v>
       </c>
@@ -41209,8 +42246,11 @@
       <c r="V346" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="347" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y346" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="347" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C347" t="s">
         <v>830</v>
       </c>
@@ -41265,8 +42305,11 @@
       <c r="V347" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="348" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y347" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="348" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C348" t="s">
         <v>831</v>
       </c>
@@ -41321,8 +42364,11 @@
       <c r="V348" t="s">
         <v>1068</v>
       </c>
-    </row>
-    <row r="349" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y348" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="349" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C349" t="s">
         <v>832</v>
       </c>
@@ -41377,8 +42423,11 @@
       <c r="V349" t="s">
         <v>1067</v>
       </c>
-    </row>
-    <row r="350" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y349" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="350" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C350" t="s">
         <v>833</v>
       </c>
@@ -41433,8 +42482,11 @@
       <c r="V350" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="351" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y350" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="351" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C351" t="s">
         <v>834</v>
       </c>
@@ -41489,8 +42541,11 @@
       <c r="V351" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="352" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y351" t="s">
+        <v>5054</v>
+      </c>
+    </row>
+    <row r="352" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C352" t="s">
         <v>835</v>
       </c>
@@ -41545,8 +42600,11 @@
       <c r="V352" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="353" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y352" t="s">
+        <v>5055</v>
+      </c>
+    </row>
+    <row r="353" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C353" t="s">
         <v>836</v>
       </c>
@@ -41601,8 +42659,11 @@
       <c r="V353" t="s">
         <v>1063</v>
       </c>
-    </row>
-    <row r="354" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y353" t="s">
+        <v>5056</v>
+      </c>
+    </row>
+    <row r="354" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C354" t="s">
         <v>837</v>
       </c>
@@ -41657,8 +42718,11 @@
       <c r="V354" t="s">
         <v>4373</v>
       </c>
-    </row>
-    <row r="355" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y354" t="s">
+        <v>5057</v>
+      </c>
+    </row>
+    <row r="355" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C355" t="s">
         <v>838</v>
       </c>
@@ -41713,8 +42777,11 @@
       <c r="V355" t="s">
         <v>4374</v>
       </c>
-    </row>
-    <row r="356" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y355" t="s">
+        <v>5058</v>
+      </c>
+    </row>
+    <row r="356" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C356" t="s">
         <v>839</v>
       </c>
@@ -41769,8 +42836,11 @@
       <c r="V356" t="s">
         <v>4375</v>
       </c>
-    </row>
-    <row r="357" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y356" t="s">
+        <v>5059</v>
+      </c>
+    </row>
+    <row r="357" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C357" t="s">
         <v>840</v>
       </c>
@@ -41825,8 +42895,11 @@
       <c r="V357" t="s">
         <v>4376</v>
       </c>
-    </row>
-    <row r="358" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y357" t="s">
+        <v>5060</v>
+      </c>
+    </row>
+    <row r="358" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C358" t="s">
         <v>841</v>
       </c>
@@ -41881,8 +42954,11 @@
       <c r="V358" t="s">
         <v>4377</v>
       </c>
-    </row>
-    <row r="359" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y358" t="s">
+        <v>5061</v>
+      </c>
+    </row>
+    <row r="359" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C359" t="s">
         <v>842</v>
       </c>
@@ -41937,8 +43013,11 @@
       <c r="V359" t="s">
         <v>4378</v>
       </c>
-    </row>
-    <row r="360" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y359" t="s">
+        <v>5062</v>
+      </c>
+    </row>
+    <row r="360" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C360" t="s">
         <v>843</v>
       </c>
@@ -41993,8 +43072,11 @@
       <c r="V360" t="s">
         <v>4379</v>
       </c>
-    </row>
-    <row r="361" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y360" t="s">
+        <v>5063</v>
+      </c>
+    </row>
+    <row r="361" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C361" t="s">
         <v>844</v>
       </c>
@@ -42049,8 +43131,11 @@
       <c r="V361" t="s">
         <v>4380</v>
       </c>
-    </row>
-    <row r="362" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y361" t="s">
+        <v>5064</v>
+      </c>
+    </row>
+    <row r="362" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C362" t="s">
         <v>845</v>
       </c>
@@ -42105,8 +43190,11 @@
       <c r="V362" t="s">
         <v>4381</v>
       </c>
-    </row>
-    <row r="363" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y362" t="s">
+        <v>5065</v>
+      </c>
+    </row>
+    <row r="363" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C363" t="s">
         <v>846</v>
       </c>
@@ -42161,8 +43249,11 @@
       <c r="V363" t="s">
         <v>4382</v>
       </c>
-    </row>
-    <row r="364" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y363" t="s">
+        <v>5066</v>
+      </c>
+    </row>
+    <row r="364" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C364" t="s">
         <v>847</v>
       </c>
@@ -42217,8 +43308,11 @@
       <c r="V364" t="s">
         <v>4383</v>
       </c>
-    </row>
-    <row r="365" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y364" t="s">
+        <v>5067</v>
+      </c>
+    </row>
+    <row r="365" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C365" t="s">
         <v>848</v>
       </c>
@@ -42273,8 +43367,11 @@
       <c r="V365" t="s">
         <v>4384</v>
       </c>
-    </row>
-    <row r="366" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y365" t="s">
+        <v>5068</v>
+      </c>
+    </row>
+    <row r="366" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C366" t="s">
         <v>849</v>
       </c>
@@ -42329,8 +43426,11 @@
       <c r="V366" t="s">
         <v>4385</v>
       </c>
-    </row>
-    <row r="367" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y366" t="s">
+        <v>5069</v>
+      </c>
+    </row>
+    <row r="367" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C367" t="s">
         <v>850</v>
       </c>
@@ -42385,8 +43485,11 @@
       <c r="V367" t="s">
         <v>4386</v>
       </c>
-    </row>
-    <row r="368" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y367" t="s">
+        <v>5070</v>
+      </c>
+    </row>
+    <row r="368" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C368" t="s">
         <v>851</v>
       </c>
@@ -42441,8 +43544,11 @@
       <c r="V368" t="s">
         <v>4387</v>
       </c>
-    </row>
-    <row r="369" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y368" t="s">
+        <v>5071</v>
+      </c>
+    </row>
+    <row r="369" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C369" t="s">
         <v>852</v>
       </c>
@@ -42497,8 +43603,11 @@
       <c r="V369" t="s">
         <v>4388</v>
       </c>
-    </row>
-    <row r="370" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y369" t="s">
+        <v>5072</v>
+      </c>
+    </row>
+    <row r="370" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C370" t="s">
         <v>853</v>
       </c>
@@ -42553,8 +43662,11 @@
       <c r="V370" t="s">
         <v>4389</v>
       </c>
-    </row>
-    <row r="371" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y370" t="s">
+        <v>5073</v>
+      </c>
+    </row>
+    <row r="371" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C371" t="s">
         <v>854</v>
       </c>
@@ -42609,8 +43721,11 @@
       <c r="V371" t="s">
         <v>4390</v>
       </c>
-    </row>
-    <row r="372" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y371" t="s">
+        <v>5074</v>
+      </c>
+    </row>
+    <row r="372" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C372" t="s">
         <v>855</v>
       </c>
@@ -42665,8 +43780,11 @@
       <c r="V372" t="s">
         <v>4391</v>
       </c>
-    </row>
-    <row r="373" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y372" t="s">
+        <v>5075</v>
+      </c>
+    </row>
+    <row r="373" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C373" t="s">
         <v>856</v>
       </c>
@@ -42721,8 +43839,11 @@
       <c r="V373" t="s">
         <v>4392</v>
       </c>
-    </row>
-    <row r="374" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y373" t="s">
+        <v>5076</v>
+      </c>
+    </row>
+    <row r="374" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C374" t="s">
         <v>857</v>
       </c>
@@ -42777,8 +43898,11 @@
       <c r="V374" t="s">
         <v>4393</v>
       </c>
-    </row>
-    <row r="375" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y374" t="s">
+        <v>5077</v>
+      </c>
+    </row>
+    <row r="375" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C375" t="s">
         <v>858</v>
       </c>
@@ -42833,8 +43957,11 @@
       <c r="V375" t="s">
         <v>4394</v>
       </c>
-    </row>
-    <row r="376" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y375" t="s">
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="376" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C376" t="s">
         <v>859</v>
       </c>
@@ -42889,8 +44016,11 @@
       <c r="V376" t="s">
         <v>4395</v>
       </c>
-    </row>
-    <row r="377" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y376" t="s">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="377" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C377" t="s">
         <v>860</v>
       </c>
@@ -42945,8 +44075,11 @@
       <c r="V377" t="s">
         <v>4396</v>
       </c>
-    </row>
-    <row r="378" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y377" t="s">
+        <v>5080</v>
+      </c>
+    </row>
+    <row r="378" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C378" t="s">
         <v>861</v>
       </c>
@@ -43001,8 +44134,11 @@
       <c r="V378" t="s">
         <v>4397</v>
       </c>
-    </row>
-    <row r="379" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y378" t="s">
+        <v>5081</v>
+      </c>
+    </row>
+    <row r="379" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C379" t="s">
         <v>862</v>
       </c>
@@ -43057,8 +44193,11 @@
       <c r="V379" t="s">
         <v>4398</v>
       </c>
-    </row>
-    <row r="380" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y379" t="s">
+        <v>5082</v>
+      </c>
+    </row>
+    <row r="380" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C380" t="s">
         <v>863</v>
       </c>
@@ -43113,8 +44252,11 @@
       <c r="V380" t="s">
         <v>4399</v>
       </c>
-    </row>
-    <row r="381" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y380" t="s">
+        <v>5083</v>
+      </c>
+    </row>
+    <row r="381" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C381" t="s">
         <v>864</v>
       </c>
@@ -43169,8 +44311,11 @@
       <c r="V381" t="s">
         <v>4400</v>
       </c>
-    </row>
-    <row r="382" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y381" t="s">
+        <v>5084</v>
+      </c>
+    </row>
+    <row r="382" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C382" t="s">
         <v>865</v>
       </c>
@@ -43225,8 +44370,11 @@
       <c r="V382" t="s">
         <v>4401</v>
       </c>
-    </row>
-    <row r="383" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y382" t="s">
+        <v>5085</v>
+      </c>
+    </row>
+    <row r="383" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C383" t="s">
         <v>866</v>
       </c>
@@ -43281,8 +44429,11 @@
       <c r="V383" t="s">
         <v>4402</v>
       </c>
-    </row>
-    <row r="384" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y383" t="s">
+        <v>5086</v>
+      </c>
+    </row>
+    <row r="384" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C384" t="s">
         <v>867</v>
       </c>
@@ -43337,8 +44488,11 @@
       <c r="V384" t="s">
         <v>4403</v>
       </c>
-    </row>
-    <row r="385" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y384" t="s">
+        <v>5087</v>
+      </c>
+    </row>
+    <row r="385" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C385" t="s">
         <v>868</v>
       </c>
@@ -43393,8 +44547,11 @@
       <c r="V385" t="s">
         <v>4404</v>
       </c>
-    </row>
-    <row r="386" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y385" t="s">
+        <v>5088</v>
+      </c>
+    </row>
+    <row r="386" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C386" t="s">
         <v>869</v>
       </c>
@@ -43449,8 +44606,11 @@
       <c r="V386" t="s">
         <v>4405</v>
       </c>
-    </row>
-    <row r="387" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y386" t="s">
+        <v>5089</v>
+      </c>
+    </row>
+    <row r="387" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C387" t="s">
         <v>870</v>
       </c>
@@ -43505,8 +44665,11 @@
       <c r="V387" t="s">
         <v>4406</v>
       </c>
-    </row>
-    <row r="388" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y387" t="s">
+        <v>5090</v>
+      </c>
+    </row>
+    <row r="388" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C388" t="s">
         <v>871</v>
       </c>
@@ -43561,8 +44724,11 @@
       <c r="V388" t="s">
         <v>4407</v>
       </c>
-    </row>
-    <row r="389" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y388" t="s">
+        <v>5091</v>
+      </c>
+    </row>
+    <row r="389" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C389" t="s">
         <v>872</v>
       </c>
@@ -43617,8 +44783,11 @@
       <c r="V389" t="s">
         <v>4408</v>
       </c>
-    </row>
-    <row r="390" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y389" t="s">
+        <v>5092</v>
+      </c>
+    </row>
+    <row r="390" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C390" t="s">
         <v>873</v>
       </c>
@@ -43673,8 +44842,11 @@
       <c r="V390" t="s">
         <v>4409</v>
       </c>
-    </row>
-    <row r="391" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y390" t="s">
+        <v>5093</v>
+      </c>
+    </row>
+    <row r="391" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C391" t="s">
         <v>874</v>
       </c>
@@ -43729,8 +44901,11 @@
       <c r="V391" t="s">
         <v>4410</v>
       </c>
-    </row>
-    <row r="392" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y391" t="s">
+        <v>5094</v>
+      </c>
+    </row>
+    <row r="392" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C392" t="s">
         <v>875</v>
       </c>
@@ -43785,8 +44960,11 @@
       <c r="V392" t="s">
         <v>4411</v>
       </c>
-    </row>
-    <row r="393" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y392" t="s">
+        <v>5095</v>
+      </c>
+    </row>
+    <row r="393" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C393" t="s">
         <v>876</v>
       </c>
@@ -43841,8 +45019,11 @@
       <c r="V393" t="s">
         <v>4412</v>
       </c>
-    </row>
-    <row r="394" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y393" t="s">
+        <v>5096</v>
+      </c>
+    </row>
+    <row r="394" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C394" t="s">
         <v>877</v>
       </c>
@@ -43897,8 +45078,11 @@
       <c r="V394" t="s">
         <v>4413</v>
       </c>
-    </row>
-    <row r="395" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y394" t="s">
+        <v>5097</v>
+      </c>
+    </row>
+    <row r="395" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C395" t="s">
         <v>878</v>
       </c>
@@ -43953,8 +45137,11 @@
       <c r="V395" t="s">
         <v>4414</v>
       </c>
-    </row>
-    <row r="396" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y395" t="s">
+        <v>5098</v>
+      </c>
+    </row>
+    <row r="396" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C396" t="s">
         <v>879</v>
       </c>
@@ -44009,8 +45196,11 @@
       <c r="V396" t="s">
         <v>4415</v>
       </c>
-    </row>
-    <row r="397" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y396" t="s">
+        <v>5099</v>
+      </c>
+    </row>
+    <row r="397" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C397" t="s">
         <v>880</v>
       </c>
@@ -44065,8 +45255,11 @@
       <c r="V397" t="s">
         <v>4416</v>
       </c>
-    </row>
-    <row r="398" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y397" t="s">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="398" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C398" t="s">
         <v>881</v>
       </c>
@@ -44121,8 +45314,11 @@
       <c r="V398" t="s">
         <v>4417</v>
       </c>
-    </row>
-    <row r="399" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y398" t="s">
+        <v>5101</v>
+      </c>
+    </row>
+    <row r="399" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C399" t="s">
         <v>882</v>
       </c>
@@ -44177,8 +45373,11 @@
       <c r="V399" t="s">
         <v>4418</v>
       </c>
-    </row>
-    <row r="400" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y399" t="s">
+        <v>5102</v>
+      </c>
+    </row>
+    <row r="400" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C400" t="s">
         <v>883</v>
       </c>
@@ -44233,8 +45432,11 @@
       <c r="V400" t="s">
         <v>4419</v>
       </c>
-    </row>
-    <row r="401" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y400" t="s">
+        <v>5103</v>
+      </c>
+    </row>
+    <row r="401" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C401" t="s">
         <v>884</v>
       </c>
@@ -44289,8 +45491,11 @@
       <c r="V401" t="s">
         <v>4420</v>
       </c>
-    </row>
-    <row r="402" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y401" t="s">
+        <v>5104</v>
+      </c>
+    </row>
+    <row r="402" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C402" t="s">
         <v>885</v>
       </c>
@@ -44345,8 +45550,11 @@
       <c r="V402" t="s">
         <v>4421</v>
       </c>
-    </row>
-    <row r="403" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y402" t="s">
+        <v>5105</v>
+      </c>
+    </row>
+    <row r="403" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C403" t="s">
         <v>886</v>
       </c>
@@ -44401,8 +45609,11 @@
       <c r="V403" t="s">
         <v>4422</v>
       </c>
-    </row>
-    <row r="404" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y403" t="s">
+        <v>5106</v>
+      </c>
+    </row>
+    <row r="404" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C404" t="s">
         <v>887</v>
       </c>
@@ -44457,8 +45668,11 @@
       <c r="V404" t="s">
         <v>4423</v>
       </c>
-    </row>
-    <row r="405" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y404" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="405" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C405" t="s">
         <v>888</v>
       </c>
@@ -44513,8 +45727,11 @@
       <c r="V405" t="s">
         <v>4424</v>
       </c>
-    </row>
-    <row r="406" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y405" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="406" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C406" t="s">
         <v>889</v>
       </c>
@@ -44569,8 +45786,11 @@
       <c r="V406" t="s">
         <v>4425</v>
       </c>
-    </row>
-    <row r="407" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y406" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="407" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C407" t="s">
         <v>890</v>
       </c>
@@ -44625,8 +45845,11 @@
       <c r="V407" t="s">
         <v>4426</v>
       </c>
-    </row>
-    <row r="408" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y407" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="408" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C408" t="s">
         <v>891</v>
       </c>
@@ -44678,8 +45901,11 @@
       <c r="V408" t="s">
         <v>4427</v>
       </c>
-    </row>
-    <row r="409" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="Y408" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="409" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C409" t="s">
         <v>892</v>
       </c>
@@ -44732,7 +45958,7 @@
         <v>4428</v>
       </c>
     </row>
-    <row r="410" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="410" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C410" t="s">
         <v>893</v>
       </c>
@@ -44785,7 +46011,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="411" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="411" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C411" t="s">
         <v>894</v>
       </c>
@@ -44838,7 +46064,7 @@
         <v>4430</v>
       </c>
     </row>
-    <row r="412" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="412" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C412" t="s">
         <v>895</v>
       </c>
@@ -44891,7 +46117,7 @@
         <v>4431</v>
       </c>
     </row>
-    <row r="413" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="413" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C413" t="s">
         <v>896</v>
       </c>
@@ -44944,7 +46170,7 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="414" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="414" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C414" t="s">
         <v>897</v>
       </c>
@@ -44997,7 +46223,7 @@
         <v>4433</v>
       </c>
     </row>
-    <row r="415" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="415" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C415" t="s">
         <v>898</v>
       </c>
@@ -45050,7 +46276,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="416" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="416" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C416" t="s">
         <v>899</v>
       </c>
